--- a/pdf-to-excel/src/sample-output.xlsx
+++ b/pdf-to-excel/src/sample-output.xlsx
@@ -5,9 +5,9 @@
   <sheets>
     <sheet name="Meta" sheetId="1" r:id="rId1"/>
     <sheet name="RC_Beam" sheetId="2" r:id="rId2"/>
-    <sheet name="RC_Column" sheetId="3" r:id="rId3"/>
-    <sheet name="CFT_Column" sheetId="4" r:id="rId4"/>
-    <sheet name="S_Beam" sheetId="5" r:id="rId5"/>
+    <sheet name="S_Beam" sheetId="3" r:id="rId3"/>
+    <sheet name="RC_Column" sheetId="4" r:id="rId4"/>
+    <sheet name="CFT_Column" sheetId="5" r:id="rId5"/>
   </sheets>
 </workbook>
 </file>
@@ -424,7 +424,7 @@
         <v>source_pdf_filename</v>
       </c>
       <c r="B3" t="str">
-        <v>PDF2-p1-RC基礎大梁.pdf</v>
+        <v>PDF2.pdf</v>
       </c>
     </row>
     <row r="4">
@@ -440,7 +440,7 @@
         <v>drawing_name</v>
       </c>
       <c r="B5" t="str">
-        <v>RC基礎大梁リスト</v>
+        <v>RC基礎大梁リスト + S大梁リスト</v>
       </c>
     </row>
     <row r="6">
@@ -448,7 +448,7 @@
         <v>extracted_at</v>
       </c>
       <c r="B6" t="str">
-        <v>2026-05-20T03:51:48.400Z</v>
+        <v>2026-05-20T04:04:08.081Z</v>
       </c>
     </row>
     <row r="7">
@@ -4112,16 +4112,759 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
+  <dimension ref="A1:N17"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>placeholder</v>
+        <v>TypeName</v>
+      </c>
+      <c r="B1" t="str">
+        <v>符号</v>
+      </c>
+      <c r="C1" t="str">
+        <v>断面形式</v>
+      </c>
+      <c r="D1" t="str">
+        <v>成H_mm</v>
+      </c>
+      <c r="E1" t="str">
+        <v>幅B_mm</v>
+      </c>
+      <c r="F1" t="str">
+        <v>ウェブtw_mm</v>
+      </c>
+      <c r="G1" t="str">
+        <v>フランジtf_mm</v>
+      </c>
+      <c r="H1" t="str">
+        <v>スパン_mm</v>
+      </c>
+      <c r="I1" t="str">
+        <v>通り起点</v>
+      </c>
+      <c r="J1" t="str">
+        <v>通り終点</v>
+      </c>
+      <c r="K1" t="str">
+        <v>鋼材グレード</v>
+      </c>
+      <c r="L1" t="str">
+        <v>区分</v>
+      </c>
+      <c r="M1" t="str">
+        <v>原文</v>
+      </c>
+      <c r="N1" t="str">
+        <v>備考</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>SG1</v>
+      </c>
+      <c r="B2" t="str">
+        <v>SG1</v>
+      </c>
+      <c r="C2" t="str">
+        <v>SH</v>
+      </c>
+      <c r="D2">
+        <v>600</v>
+      </c>
+      <c r="E2">
+        <v>200</v>
+      </c>
+      <c r="F2">
+        <v>12</v>
+      </c>
+      <c r="G2">
+        <v>16</v>
+      </c>
+      <c r="H2" t="str">
+        <v>8400;7800;6450;6000</v>
+      </c>
+      <c r="I2" t="str">
+        <v/>
+      </c>
+      <c r="J2" t="str">
+        <v/>
+      </c>
+      <c r="K2" t="str">
+        <v/>
+      </c>
+      <c r="L2" t="str">
+        <v/>
+      </c>
+      <c r="M2" t="str">
+        <v>SH-600×200×12×16</v>
+      </c>
+      <c r="N2" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>SG1A</v>
+      </c>
+      <c r="B3" t="str">
+        <v>SG1A</v>
+      </c>
+      <c r="C3" t="str">
+        <v>SH</v>
+      </c>
+      <c r="D3">
+        <v>600</v>
+      </c>
+      <c r="E3">
+        <v>250</v>
+      </c>
+      <c r="F3">
+        <v>12</v>
+      </c>
+      <c r="G3">
+        <v>28</v>
+      </c>
+      <c r="H3" t="str">
+        <v>6450</v>
+      </c>
+      <c r="I3" t="str">
+        <v>Xd1</v>
+      </c>
+      <c r="J3" t="str">
+        <v>Xd2</v>
+      </c>
+      <c r="K3" t="str">
+        <v/>
+      </c>
+      <c r="L3" t="str">
+        <v/>
+      </c>
+      <c r="M3" t="str">
+        <v>SH-600×250×12×28</v>
+      </c>
+      <c r="N3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>SG2</v>
+      </c>
+      <c r="B4" t="str">
+        <v>SG2</v>
+      </c>
+      <c r="C4" t="str">
+        <v>SH</v>
+      </c>
+      <c r="D4">
+        <v>600</v>
+      </c>
+      <c r="E4">
+        <v>200</v>
+      </c>
+      <c r="F4">
+        <v>12</v>
+      </c>
+      <c r="G4">
+        <v>16</v>
+      </c>
+      <c r="H4" t="str">
+        <v>7800;6450;6000</v>
+      </c>
+      <c r="I4" t="str">
+        <v>Xd1</v>
+      </c>
+      <c r="J4" t="str">
+        <v>Xd9</v>
+      </c>
+      <c r="K4" t="str">
+        <v/>
+      </c>
+      <c r="L4" t="str">
+        <v/>
+      </c>
+      <c r="M4" t="str">
+        <v>SH-600×200×12×16</v>
+      </c>
+      <c r="N4" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>SG2A</v>
+      </c>
+      <c r="B5" t="str">
+        <v>SG2A</v>
+      </c>
+      <c r="C5" t="str">
+        <v>SH</v>
+      </c>
+      <c r="D5">
+        <v>600</v>
+      </c>
+      <c r="E5">
+        <v>250</v>
+      </c>
+      <c r="F5">
+        <v>12</v>
+      </c>
+      <c r="G5">
+        <v>28</v>
+      </c>
+      <c r="H5" t="str">
+        <v>6450</v>
+      </c>
+      <c r="I5" t="str">
+        <v>Xd1</v>
+      </c>
+      <c r="J5" t="str">
+        <v>Xd2</v>
+      </c>
+      <c r="K5" t="str">
+        <v/>
+      </c>
+      <c r="L5" t="str">
+        <v/>
+      </c>
+      <c r="M5" t="str">
+        <v>SH-600×250×12×28</v>
+      </c>
+      <c r="N5" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>SG3</v>
+      </c>
+      <c r="B6" t="str">
+        <v>SG3</v>
+      </c>
+      <c r="C6" t="str">
+        <v>SH</v>
+      </c>
+      <c r="D6">
+        <v>600</v>
+      </c>
+      <c r="E6">
+        <v>200</v>
+      </c>
+      <c r="F6">
+        <v>12</v>
+      </c>
+      <c r="G6">
+        <v>16</v>
+      </c>
+      <c r="H6" t="str">
+        <v>8400;7800</v>
+      </c>
+      <c r="I6" t="str">
+        <v>Xd5</v>
+      </c>
+      <c r="J6" t="str">
+        <v>Xd11</v>
+      </c>
+      <c r="K6" t="str">
+        <v/>
+      </c>
+      <c r="L6" t="str">
+        <v/>
+      </c>
+      <c r="M6" t="str">
+        <v>SH-600×200×12×16</v>
+      </c>
+      <c r="N6" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>SG4</v>
+      </c>
+      <c r="B7" t="str">
+        <v>SG4</v>
+      </c>
+      <c r="C7" t="str">
+        <v>SH</v>
+      </c>
+      <c r="D7">
+        <v>600</v>
+      </c>
+      <c r="E7">
+        <v>250</v>
+      </c>
+      <c r="F7">
+        <v>12</v>
+      </c>
+      <c r="G7">
+        <v>25</v>
+      </c>
+      <c r="H7" t="str">
+        <v>6000</v>
+      </c>
+      <c r="I7" t="str">
+        <v>Xd11</v>
+      </c>
+      <c r="J7" t="str">
+        <v>Xd12</v>
+      </c>
+      <c r="K7" t="str">
+        <v/>
+      </c>
+      <c r="L7" t="str">
+        <v/>
+      </c>
+      <c r="M7" t="str">
+        <v>SH-600×250×12×25</v>
+      </c>
+      <c r="N7" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>SG5</v>
+      </c>
+      <c r="B8" t="str">
+        <v>SG5</v>
+      </c>
+      <c r="C8" t="str">
+        <v>SH</v>
+      </c>
+      <c r="D8">
+        <v>600</v>
+      </c>
+      <c r="E8">
+        <v>250</v>
+      </c>
+      <c r="F8">
+        <v>12</v>
+      </c>
+      <c r="G8">
+        <v>28</v>
+      </c>
+      <c r="H8" t="str">
+        <v>6450</v>
+      </c>
+      <c r="I8" t="str">
+        <v>Xd2</v>
+      </c>
+      <c r="J8" t="str">
+        <v>Xd3</v>
+      </c>
+      <c r="K8" t="str">
+        <v/>
+      </c>
+      <c r="L8" t="str">
+        <v/>
+      </c>
+      <c r="M8" t="str">
+        <v>SH-600×250×12×28</v>
+      </c>
+      <c r="N8" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>SG6</v>
+      </c>
+      <c r="B9" t="str">
+        <v>SG6</v>
+      </c>
+      <c r="C9" t="str">
+        <v>SH</v>
+      </c>
+      <c r="D9">
+        <v>600</v>
+      </c>
+      <c r="E9">
+        <v>300</v>
+      </c>
+      <c r="F9">
+        <v>16</v>
+      </c>
+      <c r="G9">
+        <v>32</v>
+      </c>
+      <c r="H9" t="str">
+        <v>6450</v>
+      </c>
+      <c r="I9" t="str">
+        <v>Xd3</v>
+      </c>
+      <c r="J9" t="str">
+        <v>Xd4</v>
+      </c>
+      <c r="K9" t="str">
+        <v/>
+      </c>
+      <c r="L9" t="str">
+        <v/>
+      </c>
+      <c r="M9" t="str">
+        <v>SH-600×300×16×32</v>
+      </c>
+      <c r="N9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>SG7</v>
+      </c>
+      <c r="B10" t="str">
+        <v>SG7</v>
+      </c>
+      <c r="C10" t="str">
+        <v>SH</v>
+      </c>
+      <c r="D10">
+        <v>600</v>
+      </c>
+      <c r="E10">
+        <v>250</v>
+      </c>
+      <c r="F10">
+        <v>12</v>
+      </c>
+      <c r="G10">
+        <v>28</v>
+      </c>
+      <c r="H10" t="str">
+        <v>7800</v>
+      </c>
+      <c r="I10" t="str">
+        <v>Xd4</v>
+      </c>
+      <c r="J10" t="str">
+        <v>Xd5</v>
+      </c>
+      <c r="K10" t="str">
+        <v/>
+      </c>
+      <c r="L10" t="str">
+        <v/>
+      </c>
+      <c r="M10" t="str">
+        <v>SH-600×250×12×28</v>
+      </c>
+      <c r="N10" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>SG8</v>
+      </c>
+      <c r="B11" t="str">
+        <v>SG8</v>
+      </c>
+      <c r="C11" t="str">
+        <v>SH</v>
+      </c>
+      <c r="D11">
+        <v>800</v>
+      </c>
+      <c r="E11">
+        <v>400</v>
+      </c>
+      <c r="F11">
+        <v>19</v>
+      </c>
+      <c r="G11">
+        <v>36</v>
+      </c>
+      <c r="H11" t="str">
+        <v>14400;8400</v>
+      </c>
+      <c r="I11" t="str">
+        <v>Xd9</v>
+      </c>
+      <c r="J11" t="str">
+        <v>Xd12</v>
+      </c>
+      <c r="K11" t="str">
+        <v/>
+      </c>
+      <c r="L11" t="str">
+        <v/>
+      </c>
+      <c r="M11" t="str">
+        <v>SH-800×400×19×36</v>
+      </c>
+      <c r="N11" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>SG9</v>
+      </c>
+      <c r="B12" t="str">
+        <v>SG9</v>
+      </c>
+      <c r="C12" t="str">
+        <v>BH</v>
+      </c>
+      <c r="D12">
+        <v>800</v>
+      </c>
+      <c r="E12">
+        <v>400</v>
+      </c>
+      <c r="F12">
+        <v>16</v>
+      </c>
+      <c r="G12">
+        <v>32</v>
+      </c>
+      <c r="H12" t="str">
+        <v>3450</v>
+      </c>
+      <c r="I12" t="str">
+        <v>Xd12</v>
+      </c>
+      <c r="J12" t="str">
+        <v>Xd13</v>
+      </c>
+      <c r="K12" t="str">
+        <v/>
+      </c>
+      <c r="L12" t="str">
+        <v/>
+      </c>
+      <c r="M12" t="str">
+        <v>BH-800×400×16×32</v>
+      </c>
+      <c r="N12" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>SG10</v>
+      </c>
+      <c r="B13" t="str">
+        <v>SG10</v>
+      </c>
+      <c r="C13" t="str">
+        <v>SH</v>
+      </c>
+      <c r="D13">
+        <v>600</v>
+      </c>
+      <c r="E13">
+        <v>300</v>
+      </c>
+      <c r="F13">
+        <v>12</v>
+      </c>
+      <c r="G13">
+        <v>28</v>
+      </c>
+      <c r="H13" t="str">
+        <v>7800;6450</v>
+      </c>
+      <c r="I13" t="str">
+        <v>Xd2</v>
+      </c>
+      <c r="J13" t="str">
+        <v>Xd5</v>
+      </c>
+      <c r="K13" t="str">
+        <v/>
+      </c>
+      <c r="L13" t="str">
+        <v/>
+      </c>
+      <c r="M13" t="str">
+        <v>SH-600×300×12×28</v>
+      </c>
+      <c r="N13" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>SG11</v>
+      </c>
+      <c r="B14" t="str">
+        <v>SG11</v>
+      </c>
+      <c r="C14" t="str">
+        <v>BH</v>
+      </c>
+      <c r="D14">
+        <v>600</v>
+      </c>
+      <c r="E14">
+        <v>350</v>
+      </c>
+      <c r="F14">
+        <v>16</v>
+      </c>
+      <c r="G14">
+        <v>36</v>
+      </c>
+      <c r="H14" t="str">
+        <v>6450</v>
+      </c>
+      <c r="I14" t="str">
+        <v>Xd3</v>
+      </c>
+      <c r="J14" t="str">
+        <v>Xd4</v>
+      </c>
+      <c r="K14" t="str">
+        <v/>
+      </c>
+      <c r="L14" t="str">
+        <v/>
+      </c>
+      <c r="M14" t="str">
+        <v>BH-600×350×16×36</v>
+      </c>
+      <c r="N14" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>CSG3</v>
+      </c>
+      <c r="B15" t="str">
+        <v>CSG3</v>
+      </c>
+      <c r="C15" t="str">
+        <v>SH</v>
+      </c>
+      <c r="D15">
+        <v>800</v>
+      </c>
+      <c r="E15">
+        <v>250</v>
+      </c>
+      <c r="F15">
+        <v>14</v>
+      </c>
+      <c r="G15">
+        <v>22</v>
+      </c>
+      <c r="H15" t="str">
+        <v>3450</v>
+      </c>
+      <c r="I15" t="str">
+        <v/>
+      </c>
+      <c r="J15" t="str">
+        <v/>
+      </c>
+      <c r="K15" t="str">
+        <v/>
+      </c>
+      <c r="L15" t="str">
+        <v/>
+      </c>
+      <c r="M15" t="str">
+        <v>SH-800×250×14×22</v>
+      </c>
+      <c r="N15" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>CSG5</v>
+      </c>
+      <c r="B16" t="str">
+        <v>CSG5</v>
+      </c>
+      <c r="C16" t="str">
+        <v>SH</v>
+      </c>
+      <c r="D16">
+        <v>600</v>
+      </c>
+      <c r="E16">
+        <v>250</v>
+      </c>
+      <c r="F16">
+        <v>12</v>
+      </c>
+      <c r="G16">
+        <v>25</v>
+      </c>
+      <c r="H16" t="str">
+        <v>1650</v>
+      </c>
+      <c r="I16" t="str">
+        <v/>
+      </c>
+      <c r="J16" t="str">
+        <v/>
+      </c>
+      <c r="K16" t="str">
+        <v/>
+      </c>
+      <c r="L16" t="str">
+        <v/>
+      </c>
+      <c r="M16" t="str">
+        <v>SH-600×250×12×25</v>
+      </c>
+      <c r="N16" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>CSG6</v>
+      </c>
+      <c r="B17" t="str">
+        <v>CSG6</v>
+      </c>
+      <c r="C17" t="str">
+        <v>SH</v>
+      </c>
+      <c r="D17">
+        <v>600</v>
+      </c>
+      <c r="E17">
+        <v>300</v>
+      </c>
+      <c r="F17">
+        <v>16</v>
+      </c>
+      <c r="G17">
+        <v>32</v>
+      </c>
+      <c r="H17" t="str">
+        <v>4100</v>
+      </c>
+      <c r="I17" t="str">
+        <v/>
+      </c>
+      <c r="J17" t="str">
+        <v/>
+      </c>
+      <c r="K17" t="str">
+        <v/>
+      </c>
+      <c r="L17" t="str">
+        <v/>
+      </c>
+      <c r="M17" t="str">
+        <v>SH-600×300×16×32</v>
+      </c>
+      <c r="N17" t="str">
+        <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:N17"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/pdf-to-excel/src/sample-output.xlsx
+++ b/pdf-to-excel/src/sample-output.xlsx
@@ -4,10 +4,8 @@
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
     <sheet name="Meta" sheetId="1" r:id="rId1"/>
-    <sheet name="RC_Beam" sheetId="2" r:id="rId2"/>
-    <sheet name="S_Beam" sheetId="3" r:id="rId3"/>
-    <sheet name="RC_Column" sheetId="4" r:id="rId4"/>
-    <sheet name="CFT_Column" sheetId="5" r:id="rId5"/>
+    <sheet name="基礎大梁" sheetId="2" r:id="rId2"/>
+    <sheet name="S大梁" sheetId="3" r:id="rId3"/>
   </sheets>
 </workbook>
 </file>
@@ -401,7 +399,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:B6"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -429,48 +427,99 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>drawing_number</v>
+        <v>extracted_at</v>
       </c>
       <c r="B4" t="str">
-        <v/>
+        <v>2026-05-20T04:28:52.877Z</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>drawing_name</v>
+        <v>extracted_by</v>
       </c>
       <c r="B5" t="str">
-        <v>RC基礎大梁リスト + S大梁リスト</v>
+        <v>pdf-to-excel-proto@0.1.0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>extracted_at</v>
+        <v>detected_categories</v>
       </c>
       <c r="B6" t="str">
-        <v>2026-05-20T04:04:08.081Z</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>extracted_by</v>
-      </c>
-      <c r="B7" t="str">
-        <v>pdf-to-excel-proto@0.1.0</v>
+        <v>RC基礎大梁 (20行), S大梁 (16行)</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B7"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B6"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BE21"/>
+  <dimension ref="A1:BE22"/>
+  <cols>
+    <col min="1" max="1" width="10.83203125" customWidth="1"/>
+    <col min="2" max="2" width="10.83203125" customWidth="1"/>
+    <col min="3" max="3" width="12.83203125" customWidth="1"/>
+    <col min="4" max="4" width="12.83203125" customWidth="1"/>
+    <col min="5" max="5" width="12.83203125" customWidth="1"/>
+    <col min="6" max="6" width="12.83203125" customWidth="1"/>
+    <col min="7" max="7" width="12.83203125" customWidth="1"/>
+    <col min="8" max="8" width="8.83203125" customWidth="1"/>
+    <col min="9" max="9" width="8.83203125" customWidth="1"/>
+    <col min="10" max="10" width="8.83203125" customWidth="1"/>
+    <col min="11" max="11" width="8.83203125" customWidth="1"/>
+    <col min="12" max="12" width="8.83203125" customWidth="1"/>
+    <col min="13" max="13" width="8.83203125" customWidth="1"/>
+    <col min="14" max="14" width="8.83203125" customWidth="1"/>
+    <col min="15" max="15" width="8.83203125" customWidth="1"/>
+    <col min="16" max="16" width="8.83203125" customWidth="1"/>
+    <col min="17" max="17" width="24.83203125" customWidth="1"/>
+    <col min="18" max="18" width="8.83203125" customWidth="1"/>
+    <col min="19" max="19" width="8.83203125" customWidth="1"/>
+    <col min="20" max="20" width="8.83203125" customWidth="1"/>
+    <col min="21" max="21" width="8.83203125" customWidth="1"/>
+    <col min="22" max="22" width="8.83203125" customWidth="1"/>
+    <col min="23" max="23" width="8.83203125" customWidth="1"/>
+    <col min="24" max="24" width="8.83203125" customWidth="1"/>
+    <col min="25" max="25" width="8.83203125" customWidth="1"/>
+    <col min="26" max="26" width="8.83203125" customWidth="1"/>
+    <col min="27" max="27" width="24.83203125" customWidth="1"/>
+    <col min="28" max="28" width="8.83203125" customWidth="1"/>
+    <col min="29" max="29" width="8.83203125" customWidth="1"/>
+    <col min="30" max="30" width="8.83203125" customWidth="1"/>
+    <col min="31" max="31" width="8.83203125" customWidth="1"/>
+    <col min="32" max="32" width="8.83203125" customWidth="1"/>
+    <col min="33" max="33" width="8.83203125" customWidth="1"/>
+    <col min="34" max="34" width="8.83203125" customWidth="1"/>
+    <col min="35" max="35" width="8.83203125" customWidth="1"/>
+    <col min="36" max="36" width="8.83203125" customWidth="1"/>
+    <col min="37" max="37" width="24.83203125" customWidth="1"/>
+    <col min="38" max="38" width="8.83203125" customWidth="1"/>
+    <col min="39" max="39" width="8.83203125" customWidth="1"/>
+    <col min="40" max="40" width="8.83203125" customWidth="1"/>
+    <col min="41" max="41" width="8.83203125" customWidth="1"/>
+    <col min="42" max="42" width="8.83203125" customWidth="1"/>
+    <col min="43" max="43" width="8.83203125" customWidth="1"/>
+    <col min="44" max="44" width="8.83203125" customWidth="1"/>
+    <col min="45" max="45" width="8.83203125" customWidth="1"/>
+    <col min="46" max="46" width="8.83203125" customWidth="1"/>
+    <col min="47" max="47" width="24.83203125" customWidth="1"/>
+    <col min="48" max="48" width="8.83203125" customWidth="1"/>
+    <col min="49" max="49" width="8.83203125" customWidth="1"/>
+    <col min="50" max="50" width="8.83203125" customWidth="1"/>
+    <col min="51" max="51" width="8.83203125" customWidth="1"/>
+    <col min="52" max="52" width="8.83203125" customWidth="1"/>
+    <col min="53" max="53" width="8.83203125" customWidth="1"/>
+    <col min="54" max="54" width="8.83203125" customWidth="1"/>
+    <col min="55" max="55" width="8.83203125" customWidth="1"/>
+    <col min="56" max="56" width="8.83203125" customWidth="1"/>
+    <col min="57" max="57" width="24.83203125" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="22" customHeight="1">
       <c r="A1" t="str">
         <v>TypeName</v>
       </c>
@@ -487,177 +536,177 @@
         <v>成D_mm</v>
       </c>
       <c r="F1" t="str">
-        <v>Fc_Nmm2</v>
+        <v>Fc_N/mm²</v>
       </c>
       <c r="G1" t="str">
         <v>備考</v>
       </c>
       <c r="H1" t="str">
-        <v>a_主筋径</v>
+        <v>位置 a</v>
       </c>
       <c r="I1" t="str">
-        <v>a_上_1段</v>
+        <v/>
       </c>
       <c r="J1" t="str">
-        <v>a_上_2段</v>
+        <v/>
       </c>
       <c r="K1" t="str">
-        <v>a_下_1段</v>
+        <v/>
       </c>
       <c r="L1" t="str">
-        <v>a_下_2段</v>
+        <v/>
       </c>
       <c r="M1" t="str">
-        <v>a_あばら径</v>
+        <v/>
       </c>
       <c r="N1" t="str">
-        <v>a_あばら脚数</v>
+        <v/>
       </c>
       <c r="O1" t="str">
-        <v>a_あばらピッチ_mm</v>
+        <v/>
       </c>
       <c r="P1" t="str">
-        <v>a_端あき_mm</v>
+        <v/>
       </c>
       <c r="Q1" t="str">
-        <v>a_原文</v>
+        <v/>
       </c>
       <c r="R1" t="str">
-        <v>b_主筋径</v>
+        <v>位置 b</v>
       </c>
       <c r="S1" t="str">
-        <v>b_上_1段</v>
+        <v/>
       </c>
       <c r="T1" t="str">
-        <v>b_上_2段</v>
+        <v/>
       </c>
       <c r="U1" t="str">
-        <v>b_下_1段</v>
+        <v/>
       </c>
       <c r="V1" t="str">
-        <v>b_下_2段</v>
+        <v/>
       </c>
       <c r="W1" t="str">
-        <v>b_あばら径</v>
+        <v/>
       </c>
       <c r="X1" t="str">
-        <v>b_あばら脚数</v>
+        <v/>
       </c>
       <c r="Y1" t="str">
-        <v>b_あばらピッチ_mm</v>
+        <v/>
       </c>
       <c r="Z1" t="str">
-        <v>b_端あき_mm</v>
+        <v/>
       </c>
       <c r="AA1" t="str">
-        <v>b_原文</v>
+        <v/>
       </c>
       <c r="AB1" t="str">
-        <v>c_主筋径</v>
+        <v>位置 c</v>
       </c>
       <c r="AC1" t="str">
-        <v>c_上_1段</v>
+        <v/>
       </c>
       <c r="AD1" t="str">
-        <v>c_上_2段</v>
+        <v/>
       </c>
       <c r="AE1" t="str">
-        <v>c_下_1段</v>
+        <v/>
       </c>
       <c r="AF1" t="str">
-        <v>c_下_2段</v>
+        <v/>
       </c>
       <c r="AG1" t="str">
-        <v>c_あばら径</v>
+        <v/>
       </c>
       <c r="AH1" t="str">
-        <v>c_あばら脚数</v>
+        <v/>
       </c>
       <c r="AI1" t="str">
-        <v>c_あばらピッチ_mm</v>
+        <v/>
       </c>
       <c r="AJ1" t="str">
-        <v>c_端あき_mm</v>
+        <v/>
       </c>
       <c r="AK1" t="str">
-        <v>c_原文</v>
+        <v/>
       </c>
       <c r="AL1" t="str">
-        <v>d_主筋径</v>
+        <v>位置 d</v>
       </c>
       <c r="AM1" t="str">
-        <v>d_上_1段</v>
+        <v/>
       </c>
       <c r="AN1" t="str">
-        <v>d_上_2段</v>
+        <v/>
       </c>
       <c r="AO1" t="str">
-        <v>d_下_1段</v>
+        <v/>
       </c>
       <c r="AP1" t="str">
-        <v>d_下_2段</v>
+        <v/>
       </c>
       <c r="AQ1" t="str">
-        <v>d_あばら径</v>
+        <v/>
       </c>
       <c r="AR1" t="str">
-        <v>d_あばら脚数</v>
+        <v/>
       </c>
       <c r="AS1" t="str">
-        <v>d_あばらピッチ_mm</v>
+        <v/>
       </c>
       <c r="AT1" t="str">
-        <v>d_端あき_mm</v>
+        <v/>
       </c>
       <c r="AU1" t="str">
-        <v>d_原文</v>
+        <v/>
       </c>
       <c r="AV1" t="str">
-        <v>e_主筋径</v>
+        <v>位置 e</v>
       </c>
       <c r="AW1" t="str">
-        <v>e_上_1段</v>
+        <v/>
       </c>
       <c r="AX1" t="str">
-        <v>e_上_2段</v>
+        <v/>
       </c>
       <c r="AY1" t="str">
-        <v>e_下_1段</v>
+        <v/>
       </c>
       <c r="AZ1" t="str">
-        <v>e_下_2段</v>
+        <v/>
       </c>
       <c r="BA1" t="str">
-        <v>e_あばら径</v>
+        <v/>
       </c>
       <c r="BB1" t="str">
-        <v>e_あばら脚数</v>
+        <v/>
       </c>
       <c r="BC1" t="str">
-        <v>e_あばらピッチ_mm</v>
+        <v/>
       </c>
       <c r="BD1" t="str">
-        <v>e_端あき_mm</v>
+        <v/>
       </c>
       <c r="BE1" t="str">
-        <v>e_原文</v>
-      </c>
-    </row>
-    <row r="2">
+        <v/>
+      </c>
+    </row>
+    <row r="2" ht="22" customHeight="1">
       <c r="A2" t="str">
-        <v>FG1</v>
+        <v/>
       </c>
       <c r="B2" t="str">
-        <v>FG1</v>
-      </c>
-      <c r="C2">
-        <v>6450</v>
-      </c>
-      <c r="D2">
-        <v>640</v>
-      </c>
-      <c r="E2">
-        <v>1500</v>
+        <v/>
+      </c>
+      <c r="C2" t="str">
+        <v/>
+      </c>
+      <c r="D2" t="str">
+        <v/>
+      </c>
+      <c r="E2" t="str">
+        <v/>
       </c>
       <c r="F2" t="str">
         <v/>
@@ -666,162 +715,162 @@
         <v/>
       </c>
       <c r="H2" t="str">
-        <v>D25</v>
-      </c>
-      <c r="I2">
-        <v>6</v>
-      </c>
-      <c r="J2">
-        <v>0</v>
-      </c>
-      <c r="K2">
-        <v>6</v>
-      </c>
-      <c r="L2">
-        <v>2</v>
+        <v>主筋径</v>
+      </c>
+      <c r="I2" t="str">
+        <v>上_1段</v>
+      </c>
+      <c r="J2" t="str">
+        <v>上_2段</v>
+      </c>
+      <c r="K2" t="str">
+        <v>下_1段</v>
+      </c>
+      <c r="L2" t="str">
+        <v>下_2段</v>
       </c>
       <c r="M2" t="str">
-        <v>D13</v>
-      </c>
-      <c r="N2">
-        <v>2</v>
-      </c>
-      <c r="O2">
-        <v>150</v>
-      </c>
-      <c r="P2">
-        <v>2800</v>
+        <v>あばら径</v>
+      </c>
+      <c r="N2" t="str">
+        <v>あばら脚数</v>
+      </c>
+      <c r="O2" t="str">
+        <v>あばらピッチ_mm</v>
+      </c>
+      <c r="P2" t="str">
+        <v>端あき_mm</v>
       </c>
       <c r="Q2" t="str">
-        <v>上=6 下=6+2</v>
+        <v>原文</v>
       </c>
       <c r="R2" t="str">
-        <v>D25</v>
-      </c>
-      <c r="S2">
-        <v>6</v>
-      </c>
-      <c r="T2">
-        <v>0</v>
-      </c>
-      <c r="U2">
-        <v>6</v>
-      </c>
-      <c r="V2">
-        <v>3</v>
+        <v>主筋径</v>
+      </c>
+      <c r="S2" t="str">
+        <v>上_1段</v>
+      </c>
+      <c r="T2" t="str">
+        <v>上_2段</v>
+      </c>
+      <c r="U2" t="str">
+        <v>下_1段</v>
+      </c>
+      <c r="V2" t="str">
+        <v>下_2段</v>
       </c>
       <c r="W2" t="str">
-        <v>D13</v>
-      </c>
-      <c r="X2">
-        <v>2</v>
-      </c>
-      <c r="Y2">
-        <v>150</v>
-      </c>
-      <c r="Z2">
-        <v>2900</v>
+        <v>あばら径</v>
+      </c>
+      <c r="X2" t="str">
+        <v>あばら脚数</v>
+      </c>
+      <c r="Y2" t="str">
+        <v>あばらピッチ_mm</v>
+      </c>
+      <c r="Z2" t="str">
+        <v>端あき_mm</v>
       </c>
       <c r="AA2" t="str">
-        <v>上=6 下=6+3</v>
+        <v>原文</v>
       </c>
       <c r="AB2" t="str">
-        <v>D25</v>
-      </c>
-      <c r="AC2">
-        <v>6</v>
-      </c>
-      <c r="AD2">
-        <v>2</v>
-      </c>
-      <c r="AE2">
-        <v>6</v>
-      </c>
-      <c r="AF2">
-        <v>0</v>
+        <v>主筋径</v>
+      </c>
+      <c r="AC2" t="str">
+        <v>上_1段</v>
+      </c>
+      <c r="AD2" t="str">
+        <v>上_2段</v>
+      </c>
+      <c r="AE2" t="str">
+        <v>下_1段</v>
+      </c>
+      <c r="AF2" t="str">
+        <v>下_2段</v>
       </c>
       <c r="AG2" t="str">
-        <v>D13</v>
-      </c>
-      <c r="AH2">
-        <v>2</v>
-      </c>
-      <c r="AI2">
-        <v>150</v>
-      </c>
-      <c r="AJ2">
-        <v>3800</v>
+        <v>あばら径</v>
+      </c>
+      <c r="AH2" t="str">
+        <v>あばら脚数</v>
+      </c>
+      <c r="AI2" t="str">
+        <v>あばらピッチ_mm</v>
+      </c>
+      <c r="AJ2" t="str">
+        <v>端あき_mm</v>
       </c>
       <c r="AK2" t="str">
-        <v>上=6+2 下=6</v>
+        <v>原文</v>
       </c>
       <c r="AL2" t="str">
-        <v/>
+        <v>主筋径</v>
       </c>
       <c r="AM2" t="str">
-        <v/>
+        <v>上_1段</v>
       </c>
       <c r="AN2" t="str">
-        <v/>
+        <v>上_2段</v>
       </c>
       <c r="AO2" t="str">
-        <v/>
+        <v>下_1段</v>
       </c>
       <c r="AP2" t="str">
-        <v/>
+        <v>下_2段</v>
       </c>
       <c r="AQ2" t="str">
-        <v/>
+        <v>あばら径</v>
       </c>
       <c r="AR2" t="str">
-        <v/>
+        <v>あばら脚数</v>
       </c>
       <c r="AS2" t="str">
-        <v/>
+        <v>あばらピッチ_mm</v>
       </c>
       <c r="AT2" t="str">
-        <v/>
+        <v>端あき_mm</v>
       </c>
       <c r="AU2" t="str">
-        <v/>
+        <v>原文</v>
       </c>
       <c r="AV2" t="str">
-        <v/>
+        <v>主筋径</v>
       </c>
       <c r="AW2" t="str">
-        <v/>
+        <v>上_1段</v>
       </c>
       <c r="AX2" t="str">
-        <v/>
+        <v>上_2段</v>
       </c>
       <c r="AY2" t="str">
-        <v/>
+        <v>下_1段</v>
       </c>
       <c r="AZ2" t="str">
-        <v/>
+        <v>下_2段</v>
       </c>
       <c r="BA2" t="str">
-        <v/>
+        <v>あばら径</v>
       </c>
       <c r="BB2" t="str">
-        <v/>
+        <v>あばら脚数</v>
       </c>
       <c r="BC2" t="str">
-        <v/>
+        <v>あばらピッチ_mm</v>
       </c>
       <c r="BD2" t="str">
-        <v/>
+        <v>端あき_mm</v>
       </c>
       <c r="BE2" t="str">
-        <v/>
+        <v>原文</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>FG2</v>
+        <v>FG1</v>
       </c>
       <c r="B3" t="str">
-        <v>FG2</v>
+        <v>FG1</v>
       </c>
       <c r="C3">
         <v>6450</v>
@@ -832,9 +881,6 @@
       <c r="E3">
         <v>1500</v>
       </c>
-      <c r="F3" t="str">
-        <v/>
-      </c>
       <c r="G3" t="str">
         <v/>
       </c>
@@ -851,7 +897,7 @@
         <v>6</v>
       </c>
       <c r="L3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M3" t="str">
         <v>D13</v>
@@ -863,10 +909,10 @@
         <v>150</v>
       </c>
       <c r="P3">
-        <v>2600</v>
+        <v>2800</v>
       </c>
       <c r="Q3" t="str">
-        <v>上=6 下=6+3</v>
+        <v>上=6 下=6+2</v>
       </c>
       <c r="R3" t="str">
         <v>D25</v>
@@ -881,7 +927,7 @@
         <v>6</v>
       </c>
       <c r="V3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="W3" t="str">
         <v>D13</v>
@@ -893,10 +939,10 @@
         <v>150</v>
       </c>
       <c r="Z3">
-        <v>3000</v>
+        <v>2900</v>
       </c>
       <c r="AA3" t="str">
-        <v>上=6 下=6+5</v>
+        <v>上=6 下=6+3</v>
       </c>
       <c r="AB3" t="str">
         <v>D25</v>
@@ -905,7 +951,7 @@
         <v>6</v>
       </c>
       <c r="AD3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE3">
         <v>6</v>
@@ -926,64 +972,34 @@
         <v>3800</v>
       </c>
       <c r="AK3" t="str">
-        <v>上=6+3 下=6</v>
+        <v>上=6+2 下=6</v>
       </c>
       <c r="AL3" t="str">
-        <v/>
-      </c>
-      <c r="AM3" t="str">
-        <v/>
-      </c>
-      <c r="AN3" t="str">
-        <v/>
-      </c>
-      <c r="AO3" t="str">
-        <v/>
-      </c>
-      <c r="AP3" t="str">
-        <v/>
+        <v>D25</v>
       </c>
       <c r="AQ3" t="str">
-        <v/>
-      </c>
-      <c r="AR3" t="str">
-        <v/>
-      </c>
-      <c r="AS3" t="str">
-        <v/>
-      </c>
-      <c r="AT3" t="str">
-        <v/>
+        <v>D13</v>
+      </c>
+      <c r="AR3">
+        <v>2</v>
+      </c>
+      <c r="AS3">
+        <v>150</v>
       </c>
       <c r="AU3" t="str">
         <v/>
       </c>
       <c r="AV3" t="str">
-        <v/>
-      </c>
-      <c r="AW3" t="str">
-        <v/>
-      </c>
-      <c r="AX3" t="str">
-        <v/>
-      </c>
-      <c r="AY3" t="str">
-        <v/>
-      </c>
-      <c r="AZ3" t="str">
-        <v/>
+        <v>D25</v>
       </c>
       <c r="BA3" t="str">
-        <v/>
-      </c>
-      <c r="BB3" t="str">
-        <v/>
-      </c>
-      <c r="BC3" t="str">
-        <v/>
-      </c>
-      <c r="BD3" t="str">
-        <v/>
+        <v>D13</v>
+      </c>
+      <c r="BB3">
+        <v>2</v>
+      </c>
+      <c r="BC3">
+        <v>150</v>
       </c>
       <c r="BE3" t="str">
         <v/>
@@ -991,23 +1007,20 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>FG3</v>
+        <v>FG2</v>
       </c>
       <c r="B4" t="str">
-        <v>FG3</v>
+        <v>FG2</v>
       </c>
       <c r="C4">
         <v>6450</v>
       </c>
       <c r="D4">
-        <v>800</v>
+        <v>640</v>
       </c>
       <c r="E4">
         <v>1500</v>
       </c>
-      <c r="F4" t="str">
-        <v/>
-      </c>
       <c r="G4" t="str">
         <v/>
       </c>
@@ -1015,13 +1028,13 @@
         <v>D25</v>
       </c>
       <c r="I4">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J4">
         <v>0</v>
       </c>
       <c r="K4">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="L4">
         <v>3</v>
@@ -1030,58 +1043,58 @@
         <v>D13</v>
       </c>
       <c r="N4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O4">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="P4">
         <v>2600</v>
       </c>
       <c r="Q4" t="str">
-        <v>上=8 下=8+3</v>
+        <v>上=6 下=6+3</v>
       </c>
       <c r="R4" t="str">
         <v>D25</v>
       </c>
       <c r="S4">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T4">
         <v>0</v>
       </c>
       <c r="U4">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="V4">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="W4" t="str">
         <v>D13</v>
       </c>
       <c r="X4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y4">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="Z4">
-        <v>2600</v>
+        <v>3000</v>
       </c>
       <c r="AA4" t="str">
-        <v>上=8 下=8+3</v>
+        <v>上=6 下=6+5</v>
       </c>
       <c r="AB4" t="str">
         <v>D25</v>
       </c>
       <c r="AC4">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AD4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AE4">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AF4">
         <v>0</v>
@@ -1090,73 +1103,43 @@
         <v>D13</v>
       </c>
       <c r="AH4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI4">
-        <v>200</v>
-      </c>
-      <c r="AJ4" t="str">
-        <v/>
+        <v>150</v>
+      </c>
+      <c r="AJ4">
+        <v>3800</v>
       </c>
       <c r="AK4" t="str">
-        <v>上=8 下=8</v>
+        <v>上=6+3 下=6</v>
       </c>
       <c r="AL4" t="str">
-        <v/>
-      </c>
-      <c r="AM4" t="str">
-        <v/>
-      </c>
-      <c r="AN4" t="str">
-        <v/>
-      </c>
-      <c r="AO4" t="str">
-        <v/>
-      </c>
-      <c r="AP4" t="str">
-        <v/>
+        <v>D25</v>
       </c>
       <c r="AQ4" t="str">
-        <v/>
-      </c>
-      <c r="AR4" t="str">
-        <v/>
-      </c>
-      <c r="AS4" t="str">
-        <v/>
-      </c>
-      <c r="AT4" t="str">
-        <v/>
+        <v>D13</v>
+      </c>
+      <c r="AR4">
+        <v>2</v>
+      </c>
+      <c r="AS4">
+        <v>150</v>
       </c>
       <c r="AU4" t="str">
         <v/>
       </c>
       <c r="AV4" t="str">
-        <v/>
-      </c>
-      <c r="AW4" t="str">
-        <v/>
-      </c>
-      <c r="AX4" t="str">
-        <v/>
-      </c>
-      <c r="AY4" t="str">
-        <v/>
-      </c>
-      <c r="AZ4" t="str">
-        <v/>
+        <v>D25</v>
       </c>
       <c r="BA4" t="str">
-        <v/>
-      </c>
-      <c r="BB4" t="str">
-        <v/>
-      </c>
-      <c r="BC4" t="str">
-        <v/>
-      </c>
-      <c r="BD4" t="str">
-        <v/>
+        <v>D13</v>
+      </c>
+      <c r="BB4">
+        <v>2</v>
+      </c>
+      <c r="BC4">
+        <v>150</v>
       </c>
       <c r="BE4" t="str">
         <v/>
@@ -1164,23 +1147,20 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>FG4</v>
+        <v>FG3</v>
       </c>
       <c r="B5" t="str">
-        <v>FG4</v>
+        <v>FG3</v>
       </c>
       <c r="C5">
-        <v>7800</v>
+        <v>6450</v>
       </c>
       <c r="D5">
-        <v>640</v>
+        <v>800</v>
       </c>
       <c r="E5">
         <v>1500</v>
       </c>
-      <c r="F5" t="str">
-        <v/>
-      </c>
       <c r="G5" t="str">
         <v/>
       </c>
@@ -1188,43 +1168,43 @@
         <v>D25</v>
       </c>
       <c r="I5">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J5">
         <v>0</v>
       </c>
       <c r="K5">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="L5">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M5" t="str">
         <v>D13</v>
       </c>
       <c r="N5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O5">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="P5">
-        <v>3100</v>
+        <v>2600</v>
       </c>
       <c r="Q5" t="str">
-        <v>上=6 下=6+5</v>
+        <v>上=8 下=8+3</v>
       </c>
       <c r="R5" t="str">
         <v>D25</v>
       </c>
       <c r="S5">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T5">
         <v>0</v>
       </c>
       <c r="U5">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="V5">
         <v>3</v>
@@ -1233,28 +1213,28 @@
         <v>D13</v>
       </c>
       <c r="X5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y5">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="Z5">
-        <v>3100</v>
+        <v>2600</v>
       </c>
       <c r="AA5" t="str">
-        <v>上=6 下=6+3</v>
+        <v>上=8 下=8+3</v>
       </c>
       <c r="AB5" t="str">
         <v>D25</v>
       </c>
       <c r="AC5">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AD5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE5">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AF5">
         <v>0</v>
@@ -1263,73 +1243,40 @@
         <v>D13</v>
       </c>
       <c r="AH5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI5">
-        <v>150</v>
-      </c>
-      <c r="AJ5">
-        <v>4400</v>
+        <v>200</v>
       </c>
       <c r="AK5" t="str">
-        <v>上=6+1 下=6</v>
+        <v>上=8 下=8</v>
       </c>
       <c r="AL5" t="str">
-        <v/>
-      </c>
-      <c r="AM5" t="str">
-        <v/>
-      </c>
-      <c r="AN5" t="str">
-        <v/>
-      </c>
-      <c r="AO5" t="str">
-        <v/>
-      </c>
-      <c r="AP5" t="str">
-        <v/>
+        <v>D25</v>
       </c>
       <c r="AQ5" t="str">
-        <v/>
-      </c>
-      <c r="AR5" t="str">
-        <v/>
-      </c>
-      <c r="AS5" t="str">
-        <v/>
-      </c>
-      <c r="AT5" t="str">
-        <v/>
+        <v>D13</v>
+      </c>
+      <c r="AR5">
+        <v>3</v>
+      </c>
+      <c r="AS5">
+        <v>200</v>
       </c>
       <c r="AU5" t="str">
         <v/>
       </c>
       <c r="AV5" t="str">
-        <v/>
-      </c>
-      <c r="AW5" t="str">
-        <v/>
-      </c>
-      <c r="AX5" t="str">
-        <v/>
-      </c>
-      <c r="AY5" t="str">
-        <v/>
-      </c>
-      <c r="AZ5" t="str">
-        <v/>
+        <v>D25</v>
       </c>
       <c r="BA5" t="str">
-        <v/>
-      </c>
-      <c r="BB5" t="str">
-        <v/>
-      </c>
-      <c r="BC5" t="str">
-        <v/>
-      </c>
-      <c r="BD5" t="str">
-        <v/>
+        <v>D13</v>
+      </c>
+      <c r="BB5">
+        <v>3</v>
+      </c>
+      <c r="BC5">
+        <v>200</v>
       </c>
       <c r="BE5" t="str">
         <v/>
@@ -1337,10 +1284,10 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>FG5</v>
+        <v>FG4</v>
       </c>
       <c r="B6" t="str">
-        <v>FG5</v>
+        <v>FG4</v>
       </c>
       <c r="C6">
         <v>7800</v>
@@ -1351,9 +1298,6 @@
       <c r="E6">
         <v>1500</v>
       </c>
-      <c r="F6" t="str">
-        <v/>
-      </c>
       <c r="G6" t="str">
         <v/>
       </c>
@@ -1370,7 +1314,7 @@
         <v>6</v>
       </c>
       <c r="L6">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M6" t="str">
         <v>D13</v>
@@ -1382,10 +1326,10 @@
         <v>150</v>
       </c>
       <c r="P6">
-        <v>2600</v>
+        <v>3100</v>
       </c>
       <c r="Q6" t="str">
-        <v>上=6 下=6+3</v>
+        <v>上=6 下=6+5</v>
       </c>
       <c r="R6" t="str">
         <v>D25</v>
@@ -1412,7 +1356,7 @@
         <v>150</v>
       </c>
       <c r="Z6">
-        <v>2600</v>
+        <v>3100</v>
       </c>
       <c r="AA6" t="str">
         <v>上=6 下=6+3</v>
@@ -1424,7 +1368,7 @@
         <v>6</v>
       </c>
       <c r="AD6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE6">
         <v>6</v>
@@ -1441,68 +1385,38 @@
       <c r="AI6">
         <v>150</v>
       </c>
-      <c r="AJ6" t="str">
-        <v/>
+      <c r="AJ6">
+        <v>4400</v>
       </c>
       <c r="AK6" t="str">
-        <v>上=6 下=6</v>
+        <v>上=6+1 下=6</v>
       </c>
       <c r="AL6" t="str">
-        <v/>
-      </c>
-      <c r="AM6" t="str">
-        <v/>
-      </c>
-      <c r="AN6" t="str">
-        <v/>
-      </c>
-      <c r="AO6" t="str">
-        <v/>
-      </c>
-      <c r="AP6" t="str">
-        <v/>
+        <v>D25</v>
       </c>
       <c r="AQ6" t="str">
-        <v/>
-      </c>
-      <c r="AR6" t="str">
-        <v/>
-      </c>
-      <c r="AS6" t="str">
-        <v/>
-      </c>
-      <c r="AT6" t="str">
-        <v/>
+        <v>D13</v>
+      </c>
+      <c r="AR6">
+        <v>2</v>
+      </c>
+      <c r="AS6">
+        <v>150</v>
       </c>
       <c r="AU6" t="str">
         <v/>
       </c>
       <c r="AV6" t="str">
-        <v/>
-      </c>
-      <c r="AW6" t="str">
-        <v/>
-      </c>
-      <c r="AX6" t="str">
-        <v/>
-      </c>
-      <c r="AY6" t="str">
-        <v/>
-      </c>
-      <c r="AZ6" t="str">
-        <v/>
+        <v>D25</v>
       </c>
       <c r="BA6" t="str">
-        <v/>
-      </c>
-      <c r="BB6" t="str">
-        <v/>
-      </c>
-      <c r="BC6" t="str">
-        <v/>
-      </c>
-      <c r="BD6" t="str">
-        <v/>
+        <v>D13</v>
+      </c>
+      <c r="BB6">
+        <v>2</v>
+      </c>
+      <c r="BC6">
+        <v>150</v>
       </c>
       <c r="BE6" t="str">
         <v/>
@@ -1510,13 +1424,13 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>FG6</v>
+        <v>FG5</v>
       </c>
       <c r="B7" t="str">
-        <v>FG6</v>
+        <v>FG5</v>
       </c>
       <c r="C7">
-        <v>6000</v>
+        <v>7800</v>
       </c>
       <c r="D7">
         <v>640</v>
@@ -1524,9 +1438,6 @@
       <c r="E7">
         <v>1500</v>
       </c>
-      <c r="F7" t="str">
-        <v/>
-      </c>
       <c r="G7" t="str">
         <v/>
       </c>
@@ -1555,7 +1466,7 @@
         <v>150</v>
       </c>
       <c r="P7">
-        <v>2700</v>
+        <v>2600</v>
       </c>
       <c r="Q7" t="str">
         <v>上=6 下=6+3</v>
@@ -1567,13 +1478,13 @@
         <v>6</v>
       </c>
       <c r="T7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U7">
         <v>6</v>
       </c>
       <c r="V7">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W7" t="str">
         <v>D13</v>
@@ -1585,10 +1496,10 @@
         <v>150</v>
       </c>
       <c r="Z7">
-        <v>2850</v>
+        <v>2600</v>
       </c>
       <c r="AA7" t="str">
-        <v>上=6+2 下=6+2</v>
+        <v>上=6 下=6+3</v>
       </c>
       <c r="AB7" t="str">
         <v>D25</v>
@@ -1597,7 +1508,7 @@
         <v>6</v>
       </c>
       <c r="AD7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AE7">
         <v>6</v>
@@ -1614,68 +1525,35 @@
       <c r="AI7">
         <v>150</v>
       </c>
-      <c r="AJ7" t="str">
-        <v/>
-      </c>
       <c r="AK7" t="str">
-        <v>上=6+2 下=6</v>
+        <v>上=6 下=6</v>
       </c>
       <c r="AL7" t="str">
-        <v/>
-      </c>
-      <c r="AM7" t="str">
-        <v/>
-      </c>
-      <c r="AN7" t="str">
-        <v/>
-      </c>
-      <c r="AO7" t="str">
-        <v/>
-      </c>
-      <c r="AP7" t="str">
-        <v/>
+        <v>D25</v>
       </c>
       <c r="AQ7" t="str">
-        <v/>
-      </c>
-      <c r="AR7" t="str">
-        <v/>
-      </c>
-      <c r="AS7" t="str">
-        <v/>
-      </c>
-      <c r="AT7" t="str">
-        <v/>
+        <v>D13</v>
+      </c>
+      <c r="AR7">
+        <v>2</v>
+      </c>
+      <c r="AS7">
+        <v>150</v>
       </c>
       <c r="AU7" t="str">
         <v/>
       </c>
       <c r="AV7" t="str">
-        <v/>
-      </c>
-      <c r="AW7" t="str">
-        <v/>
-      </c>
-      <c r="AX7" t="str">
-        <v/>
-      </c>
-      <c r="AY7" t="str">
-        <v/>
-      </c>
-      <c r="AZ7" t="str">
-        <v/>
+        <v>D25</v>
       </c>
       <c r="BA7" t="str">
-        <v/>
-      </c>
-      <c r="BB7" t="str">
-        <v/>
-      </c>
-      <c r="BC7" t="str">
-        <v/>
-      </c>
-      <c r="BD7" t="str">
-        <v/>
+        <v>D13</v>
+      </c>
+      <c r="BB7">
+        <v>2</v>
+      </c>
+      <c r="BC7">
+        <v>150</v>
       </c>
       <c r="BE7" t="str">
         <v/>
@@ -1683,13 +1561,13 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>FG7</v>
+        <v>FG6</v>
       </c>
       <c r="B8" t="str">
-        <v>FG7</v>
+        <v>FG6</v>
       </c>
       <c r="C8">
-        <v>8400</v>
+        <v>6000</v>
       </c>
       <c r="D8">
         <v>640</v>
@@ -1697,9 +1575,6 @@
       <c r="E8">
         <v>1500</v>
       </c>
-      <c r="F8" t="str">
-        <v/>
-      </c>
       <c r="G8" t="str">
         <v/>
       </c>
@@ -1728,7 +1603,7 @@
         <v>150</v>
       </c>
       <c r="P8">
-        <v>2600</v>
+        <v>2700</v>
       </c>
       <c r="Q8" t="str">
         <v>上=6 下=6+3</v>
@@ -1740,13 +1615,13 @@
         <v>6</v>
       </c>
       <c r="T8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U8">
         <v>6</v>
       </c>
       <c r="V8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W8" t="str">
         <v>D13</v>
@@ -1758,10 +1633,10 @@
         <v>150</v>
       </c>
       <c r="Z8">
-        <v>2600</v>
+        <v>2850</v>
       </c>
       <c r="AA8" t="str">
-        <v>上=6 下=6+3</v>
+        <v>上=6+2 下=6+2</v>
       </c>
       <c r="AB8" t="str">
         <v>D25</v>
@@ -1770,7 +1645,7 @@
         <v>6</v>
       </c>
       <c r="AD8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE8">
         <v>6</v>
@@ -1787,68 +1662,35 @@
       <c r="AI8">
         <v>150</v>
       </c>
-      <c r="AJ8" t="str">
-        <v/>
-      </c>
       <c r="AK8" t="str">
-        <v>上=6 下=6</v>
+        <v>上=6+2 下=6</v>
       </c>
       <c r="AL8" t="str">
-        <v/>
-      </c>
-      <c r="AM8" t="str">
-        <v/>
-      </c>
-      <c r="AN8" t="str">
-        <v/>
-      </c>
-      <c r="AO8" t="str">
-        <v/>
-      </c>
-      <c r="AP8" t="str">
-        <v/>
+        <v>D25</v>
       </c>
       <c r="AQ8" t="str">
-        <v/>
-      </c>
-      <c r="AR8" t="str">
-        <v/>
-      </c>
-      <c r="AS8" t="str">
-        <v/>
-      </c>
-      <c r="AT8" t="str">
-        <v/>
+        <v>D13</v>
+      </c>
+      <c r="AR8">
+        <v>2</v>
+      </c>
+      <c r="AS8">
+        <v>150</v>
       </c>
       <c r="AU8" t="str">
         <v/>
       </c>
       <c r="AV8" t="str">
-        <v/>
-      </c>
-      <c r="AW8" t="str">
-        <v/>
-      </c>
-      <c r="AX8" t="str">
-        <v/>
-      </c>
-      <c r="AY8" t="str">
-        <v/>
-      </c>
-      <c r="AZ8" t="str">
-        <v/>
+        <v>D25</v>
       </c>
       <c r="BA8" t="str">
-        <v/>
-      </c>
-      <c r="BB8" t="str">
-        <v/>
-      </c>
-      <c r="BC8" t="str">
-        <v/>
-      </c>
-      <c r="BD8" t="str">
-        <v/>
+        <v>D13</v>
+      </c>
+      <c r="BB8">
+        <v>2</v>
+      </c>
+      <c r="BC8">
+        <v>150</v>
       </c>
       <c r="BE8" t="str">
         <v/>
@@ -1856,22 +1698,19 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>FG8</v>
+        <v>FG7</v>
       </c>
       <c r="B9" t="str">
-        <v>FG8</v>
+        <v>FG7</v>
       </c>
       <c r="C9">
-        <v>6450</v>
+        <v>8400</v>
       </c>
       <c r="D9">
-        <v>1000</v>
-      </c>
-      <c r="E9" t="str">
-        <v/>
-      </c>
-      <c r="F9" t="str">
-        <v/>
+        <v>640</v>
+      </c>
+      <c r="E9">
+        <v>1500</v>
       </c>
       <c r="G9" t="str">
         <v/>
@@ -1879,74 +1718,74 @@
       <c r="H9" t="str">
         <v>D25</v>
       </c>
-      <c r="I9" t="str">
-        <v/>
-      </c>
-      <c r="J9" t="str">
-        <v/>
-      </c>
-      <c r="K9" t="str">
-        <v/>
-      </c>
-      <c r="L9" t="str">
-        <v/>
+      <c r="I9">
+        <v>6</v>
+      </c>
+      <c r="J9">
+        <v>0</v>
+      </c>
+      <c r="K9">
+        <v>6</v>
+      </c>
+      <c r="L9">
+        <v>3</v>
       </c>
       <c r="M9" t="str">
         <v>D13</v>
       </c>
       <c r="N9">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O9">
-        <v>200</v>
-      </c>
-      <c r="P9" t="str">
-        <v/>
+        <v>150</v>
+      </c>
+      <c r="P9">
+        <v>2600</v>
       </c>
       <c r="Q9" t="str">
-        <v/>
+        <v>上=6 下=6+3</v>
       </c>
       <c r="R9" t="str">
         <v>D25</v>
       </c>
-      <c r="S9" t="str">
-        <v/>
-      </c>
-      <c r="T9" t="str">
-        <v/>
-      </c>
-      <c r="U9" t="str">
-        <v/>
-      </c>
-      <c r="V9" t="str">
-        <v/>
+      <c r="S9">
+        <v>6</v>
+      </c>
+      <c r="T9">
+        <v>0</v>
+      </c>
+      <c r="U9">
+        <v>6</v>
+      </c>
+      <c r="V9">
+        <v>3</v>
       </c>
       <c r="W9" t="str">
         <v>D13</v>
       </c>
       <c r="X9">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Y9">
-        <v>200</v>
-      </c>
-      <c r="Z9" t="str">
-        <v/>
+        <v>150</v>
+      </c>
+      <c r="Z9">
+        <v>2600</v>
       </c>
       <c r="AA9" t="str">
-        <v/>
+        <v>上=6 下=6+3</v>
       </c>
       <c r="AB9" t="str">
         <v>D25</v>
       </c>
       <c r="AC9">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AD9">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AE9">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AF9">
         <v>0</v>
@@ -1955,73 +1794,40 @@
         <v>D13</v>
       </c>
       <c r="AH9">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AI9">
-        <v>200</v>
-      </c>
-      <c r="AJ9" t="str">
-        <v/>
+        <v>150</v>
       </c>
       <c r="AK9" t="str">
-        <v>上=10+9 下=10</v>
+        <v>上=6 下=6</v>
       </c>
       <c r="AL9" t="str">
-        <v/>
-      </c>
-      <c r="AM9" t="str">
-        <v/>
-      </c>
-      <c r="AN9" t="str">
-        <v/>
-      </c>
-      <c r="AO9" t="str">
-        <v/>
-      </c>
-      <c r="AP9" t="str">
-        <v/>
+        <v>D25</v>
       </c>
       <c r="AQ9" t="str">
-        <v/>
-      </c>
-      <c r="AR9" t="str">
-        <v/>
-      </c>
-      <c r="AS9" t="str">
-        <v/>
-      </c>
-      <c r="AT9" t="str">
-        <v/>
+        <v>D13</v>
+      </c>
+      <c r="AR9">
+        <v>2</v>
+      </c>
+      <c r="AS9">
+        <v>150</v>
       </c>
       <c r="AU9" t="str">
         <v/>
       </c>
       <c r="AV9" t="str">
-        <v/>
-      </c>
-      <c r="AW9" t="str">
-        <v/>
-      </c>
-      <c r="AX9" t="str">
-        <v/>
-      </c>
-      <c r="AY9" t="str">
-        <v/>
-      </c>
-      <c r="AZ9" t="str">
-        <v/>
+        <v>D25</v>
       </c>
       <c r="BA9" t="str">
-        <v/>
-      </c>
-      <c r="BB9" t="str">
-        <v/>
-      </c>
-      <c r="BC9" t="str">
-        <v/>
-      </c>
-      <c r="BD9" t="str">
-        <v/>
+        <v>D13</v>
+      </c>
+      <c r="BB9">
+        <v>2</v>
+      </c>
+      <c r="BC9">
+        <v>150</v>
       </c>
       <c r="BE9" t="str">
         <v/>
@@ -2029,22 +1835,16 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>FG9</v>
+        <v>FG8</v>
       </c>
       <c r="B10" t="str">
-        <v>FG9</v>
+        <v>FG8</v>
       </c>
       <c r="C10">
         <v>6450</v>
       </c>
       <c r="D10">
-        <v>800</v>
-      </c>
-      <c r="E10" t="str">
-        <v/>
-      </c>
-      <c r="F10" t="str">
-        <v/>
+        <v>1000</v>
       </c>
       <c r="G10" t="str">
         <v/>
@@ -2052,60 +1852,30 @@
       <c r="H10" t="str">
         <v>D25</v>
       </c>
-      <c r="I10" t="str">
-        <v/>
-      </c>
-      <c r="J10" t="str">
-        <v/>
-      </c>
-      <c r="K10" t="str">
-        <v/>
-      </c>
-      <c r="L10" t="str">
-        <v/>
-      </c>
       <c r="M10" t="str">
         <v>D13</v>
       </c>
       <c r="N10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O10">
         <v>200</v>
       </c>
-      <c r="P10" t="str">
-        <v/>
-      </c>
       <c r="Q10" t="str">
         <v/>
       </c>
       <c r="R10" t="str">
         <v>D25</v>
       </c>
-      <c r="S10" t="str">
-        <v/>
-      </c>
-      <c r="T10" t="str">
-        <v/>
-      </c>
-      <c r="U10" t="str">
-        <v/>
-      </c>
-      <c r="V10" t="str">
-        <v/>
-      </c>
       <c r="W10" t="str">
         <v>D13</v>
       </c>
       <c r="X10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Y10">
         <v>200</v>
       </c>
-      <c r="Z10" t="str">
-        <v/>
-      </c>
       <c r="AA10" t="str">
         <v/>
       </c>
@@ -2113,13 +1883,13 @@
         <v>D25</v>
       </c>
       <c r="AC10">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AD10">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AE10">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AF10">
         <v>0</v>
@@ -2128,73 +1898,40 @@
         <v>D13</v>
       </c>
       <c r="AH10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AI10">
         <v>200</v>
       </c>
-      <c r="AJ10" t="str">
-        <v/>
-      </c>
       <c r="AK10" t="str">
-        <v>上=8+6 下=8</v>
+        <v>上=10+9 下=10</v>
       </c>
       <c r="AL10" t="str">
-        <v/>
-      </c>
-      <c r="AM10" t="str">
-        <v/>
-      </c>
-      <c r="AN10" t="str">
-        <v/>
-      </c>
-      <c r="AO10" t="str">
-        <v/>
-      </c>
-      <c r="AP10" t="str">
-        <v/>
+        <v>D25</v>
       </c>
       <c r="AQ10" t="str">
-        <v/>
-      </c>
-      <c r="AR10" t="str">
-        <v/>
-      </c>
-      <c r="AS10" t="str">
-        <v/>
-      </c>
-      <c r="AT10" t="str">
-        <v/>
+        <v>D13</v>
+      </c>
+      <c r="AR10">
+        <v>4</v>
+      </c>
+      <c r="AS10">
+        <v>200</v>
       </c>
       <c r="AU10" t="str">
         <v/>
       </c>
       <c r="AV10" t="str">
-        <v/>
-      </c>
-      <c r="AW10" t="str">
-        <v/>
-      </c>
-      <c r="AX10" t="str">
-        <v/>
-      </c>
-      <c r="AY10" t="str">
-        <v/>
-      </c>
-      <c r="AZ10" t="str">
-        <v/>
+        <v>D25</v>
       </c>
       <c r="BA10" t="str">
-        <v/>
-      </c>
-      <c r="BB10" t="str">
-        <v/>
-      </c>
-      <c r="BC10" t="str">
-        <v/>
-      </c>
-      <c r="BD10" t="str">
-        <v/>
+        <v>D13</v>
+      </c>
+      <c r="BB10">
+        <v>4</v>
+      </c>
+      <c r="BC10">
+        <v>200</v>
       </c>
       <c r="BE10" t="str">
         <v/>
@@ -2202,22 +1939,16 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>FG9A</v>
+        <v>FG9</v>
       </c>
       <c r="B11" t="str">
-        <v>FG9A</v>
+        <v>FG9</v>
       </c>
       <c r="C11">
         <v>6450</v>
       </c>
       <c r="D11">
-        <v>1300</v>
-      </c>
-      <c r="E11" t="str">
-        <v/>
-      </c>
-      <c r="F11" t="str">
-        <v/>
+        <v>800</v>
       </c>
       <c r="G11" t="str">
         <v/>
@@ -2225,29 +1956,14 @@
       <c r="H11" t="str">
         <v>D25</v>
       </c>
-      <c r="I11" t="str">
-        <v/>
-      </c>
-      <c r="J11" t="str">
-        <v/>
-      </c>
-      <c r="K11" t="str">
-        <v/>
-      </c>
-      <c r="L11" t="str">
-        <v/>
-      </c>
       <c r="M11" t="str">
         <v>D13</v>
       </c>
       <c r="N11">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O11">
-        <v>150</v>
-      </c>
-      <c r="P11" t="str">
-        <v/>
+        <v>200</v>
       </c>
       <c r="Q11" t="str">
         <v/>
@@ -2255,29 +1971,14 @@
       <c r="R11" t="str">
         <v>D25</v>
       </c>
-      <c r="S11" t="str">
-        <v/>
-      </c>
-      <c r="T11" t="str">
-        <v/>
-      </c>
-      <c r="U11" t="str">
-        <v/>
-      </c>
-      <c r="V11" t="str">
-        <v/>
-      </c>
       <c r="W11" t="str">
         <v>D13</v>
       </c>
       <c r="X11">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Y11">
-        <v>150</v>
-      </c>
-      <c r="Z11" t="str">
-        <v/>
+        <v>200</v>
       </c>
       <c r="AA11" t="str">
         <v/>
@@ -2286,13 +1987,13 @@
         <v>D25</v>
       </c>
       <c r="AC11">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="AD11">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="AE11">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="AF11">
         <v>0</v>
@@ -2301,73 +2002,40 @@
         <v>D13</v>
       </c>
       <c r="AH11">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AI11">
-        <v>150</v>
-      </c>
-      <c r="AJ11" t="str">
-        <v/>
+        <v>200</v>
       </c>
       <c r="AK11" t="str">
-        <v>上=13+11 下=13</v>
+        <v>上=8+6 下=8</v>
       </c>
       <c r="AL11" t="str">
-        <v/>
-      </c>
-      <c r="AM11" t="str">
-        <v/>
-      </c>
-      <c r="AN11" t="str">
-        <v/>
-      </c>
-      <c r="AO11" t="str">
-        <v/>
-      </c>
-      <c r="AP11" t="str">
-        <v/>
+        <v>D25</v>
       </c>
       <c r="AQ11" t="str">
-        <v/>
-      </c>
-      <c r="AR11" t="str">
-        <v/>
-      </c>
-      <c r="AS11" t="str">
-        <v/>
-      </c>
-      <c r="AT11" t="str">
-        <v/>
+        <v>D13</v>
+      </c>
+      <c r="AR11">
+        <v>3</v>
+      </c>
+      <c r="AS11">
+        <v>200</v>
       </c>
       <c r="AU11" t="str">
         <v/>
       </c>
       <c r="AV11" t="str">
-        <v/>
-      </c>
-      <c r="AW11" t="str">
-        <v/>
-      </c>
-      <c r="AX11" t="str">
-        <v/>
-      </c>
-      <c r="AY11" t="str">
-        <v/>
-      </c>
-      <c r="AZ11" t="str">
-        <v/>
+        <v>D25</v>
       </c>
       <c r="BA11" t="str">
-        <v/>
-      </c>
-      <c r="BB11" t="str">
-        <v/>
-      </c>
-      <c r="BC11" t="str">
-        <v/>
-      </c>
-      <c r="BD11" t="str">
-        <v/>
+        <v>D13</v>
+      </c>
+      <c r="BB11">
+        <v>3</v>
+      </c>
+      <c r="BC11">
+        <v>200</v>
       </c>
       <c r="BE11" t="str">
         <v/>
@@ -2375,40 +2043,22 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>FG10</v>
+        <v>FG9A</v>
       </c>
       <c r="B12" t="str">
-        <v>FG10</v>
+        <v>FG9A</v>
       </c>
       <c r="C12">
-        <v>8500</v>
+        <v>6450</v>
       </c>
       <c r="D12">
-        <v>1000</v>
-      </c>
-      <c r="E12">
-        <v>1500</v>
-      </c>
-      <c r="F12" t="str">
-        <v/>
+        <v>1300</v>
       </c>
       <c r="G12" t="str">
         <v/>
       </c>
       <c r="H12" t="str">
         <v>D25</v>
-      </c>
-      <c r="I12">
-        <v>8</v>
-      </c>
-      <c r="J12">
-        <v>8</v>
-      </c>
-      <c r="K12">
-        <v>10</v>
-      </c>
-      <c r="L12">
-        <v>0</v>
       </c>
       <c r="M12" t="str">
         <v>D13</v>
@@ -2417,28 +2067,13 @@
         <v>4</v>
       </c>
       <c r="O12">
-        <v>200</v>
-      </c>
-      <c r="P12" t="str">
-        <v/>
+        <v>150</v>
       </c>
       <c r="Q12" t="str">
-        <v>上=8+8 下=10</v>
+        <v/>
       </c>
       <c r="R12" t="str">
         <v>D25</v>
-      </c>
-      <c r="S12">
-        <v>8</v>
-      </c>
-      <c r="T12">
-        <v>8</v>
-      </c>
-      <c r="U12">
-        <v>10</v>
-      </c>
-      <c r="V12">
-        <v>0</v>
       </c>
       <c r="W12" t="str">
         <v>D13</v>
@@ -2447,25 +2082,22 @@
         <v>4</v>
       </c>
       <c r="Y12">
-        <v>200</v>
-      </c>
-      <c r="Z12" t="str">
-        <v/>
+        <v>150</v>
       </c>
       <c r="AA12" t="str">
-        <v>上=8+8 下=10</v>
+        <v/>
       </c>
       <c r="AB12" t="str">
         <v>D25</v>
       </c>
       <c r="AC12">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AD12">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AE12">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AF12">
         <v>0</v>
@@ -2477,70 +2109,37 @@
         <v>4</v>
       </c>
       <c r="AI12">
-        <v>200</v>
-      </c>
-      <c r="AJ12">
-        <v>4500</v>
+        <v>150</v>
       </c>
       <c r="AK12" t="str">
-        <v>上=10+10 下=10</v>
+        <v>上=13+11 下=13</v>
       </c>
       <c r="AL12" t="str">
-        <v/>
-      </c>
-      <c r="AM12" t="str">
-        <v/>
-      </c>
-      <c r="AN12" t="str">
-        <v/>
-      </c>
-      <c r="AO12" t="str">
-        <v/>
-      </c>
-      <c r="AP12" t="str">
-        <v/>
+        <v>D25</v>
       </c>
       <c r="AQ12" t="str">
-        <v/>
-      </c>
-      <c r="AR12" t="str">
-        <v/>
-      </c>
-      <c r="AS12" t="str">
-        <v/>
-      </c>
-      <c r="AT12" t="str">
-        <v/>
+        <v>D13</v>
+      </c>
+      <c r="AR12">
+        <v>4</v>
+      </c>
+      <c r="AS12">
+        <v>150</v>
       </c>
       <c r="AU12" t="str">
         <v/>
       </c>
       <c r="AV12" t="str">
-        <v/>
-      </c>
-      <c r="AW12" t="str">
-        <v/>
-      </c>
-      <c r="AX12" t="str">
-        <v/>
-      </c>
-      <c r="AY12" t="str">
-        <v/>
-      </c>
-      <c r="AZ12" t="str">
-        <v/>
+        <v>D25</v>
       </c>
       <c r="BA12" t="str">
-        <v/>
-      </c>
-      <c r="BB12" t="str">
-        <v/>
-      </c>
-      <c r="BC12" t="str">
-        <v/>
-      </c>
-      <c r="BD12" t="str">
-        <v/>
+        <v>D13</v>
+      </c>
+      <c r="BB12">
+        <v>4</v>
+      </c>
+      <c r="BC12">
+        <v>150</v>
       </c>
       <c r="BE12" t="str">
         <v/>
@@ -2548,23 +2147,20 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>FG11</v>
+        <v>FG10</v>
       </c>
       <c r="B13" t="str">
-        <v>FG11</v>
+        <v>FG10</v>
       </c>
       <c r="C13">
-        <v>8600</v>
+        <v>8500</v>
       </c>
       <c r="D13">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="E13">
         <v>1500</v>
       </c>
-      <c r="F13" t="str">
-        <v/>
-      </c>
       <c r="G13" t="str">
         <v/>
       </c>
@@ -2572,73 +2168,67 @@
         <v>D25</v>
       </c>
       <c r="I13">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J13">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="K13">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="L13">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M13" t="str">
         <v>D13</v>
       </c>
       <c r="N13">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O13">
         <v>200</v>
       </c>
-      <c r="P13">
-        <v>2800</v>
-      </c>
       <c r="Q13" t="str">
-        <v>上=7+3 下=7+3</v>
+        <v>上=8+8 下=10</v>
       </c>
       <c r="R13" t="str">
         <v>D25</v>
       </c>
       <c r="S13">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T13">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="U13">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="V13">
+        <v>0</v>
+      </c>
+      <c r="W13" t="str">
+        <v>D13</v>
+      </c>
+      <c r="X13">
         <v>4</v>
       </c>
-      <c r="W13" t="str">
-        <v>D13</v>
-      </c>
-      <c r="X13">
-        <v>3</v>
-      </c>
       <c r="Y13">
         <v>200</v>
       </c>
-      <c r="Z13">
-        <v>2500</v>
-      </c>
       <c r="AA13" t="str">
-        <v>上=7+1 下=7+4</v>
+        <v>上=8+8 下=10</v>
       </c>
       <c r="AB13" t="str">
         <v>D25</v>
       </c>
       <c r="AC13">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AD13">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="AE13">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AF13">
         <v>0</v>
@@ -2647,73 +2237,43 @@
         <v>D13</v>
       </c>
       <c r="AH13">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AI13">
         <v>200</v>
       </c>
-      <c r="AJ13" t="str">
-        <v/>
+      <c r="AJ13">
+        <v>4500</v>
       </c>
       <c r="AK13" t="str">
-        <v>上=7+3 下=7</v>
+        <v>上=10+10 下=10</v>
       </c>
       <c r="AL13" t="str">
-        <v/>
-      </c>
-      <c r="AM13" t="str">
-        <v/>
-      </c>
-      <c r="AN13" t="str">
-        <v/>
-      </c>
-      <c r="AO13" t="str">
-        <v/>
-      </c>
-      <c r="AP13" t="str">
-        <v/>
+        <v>D25</v>
       </c>
       <c r="AQ13" t="str">
-        <v/>
-      </c>
-      <c r="AR13" t="str">
-        <v/>
-      </c>
-      <c r="AS13" t="str">
-        <v/>
-      </c>
-      <c r="AT13" t="str">
-        <v/>
+        <v>D13</v>
+      </c>
+      <c r="AR13">
+        <v>4</v>
+      </c>
+      <c r="AS13">
+        <v>200</v>
       </c>
       <c r="AU13" t="str">
         <v/>
       </c>
       <c r="AV13" t="str">
-        <v/>
-      </c>
-      <c r="AW13" t="str">
-        <v/>
-      </c>
-      <c r="AX13" t="str">
-        <v/>
-      </c>
-      <c r="AY13" t="str">
-        <v/>
-      </c>
-      <c r="AZ13" t="str">
-        <v/>
+        <v>D25</v>
       </c>
       <c r="BA13" t="str">
-        <v/>
-      </c>
-      <c r="BB13" t="str">
-        <v/>
-      </c>
-      <c r="BC13" t="str">
-        <v/>
-      </c>
-      <c r="BD13" t="str">
-        <v/>
+        <v>D13</v>
+      </c>
+      <c r="BB13">
+        <v>4</v>
+      </c>
+      <c r="BC13">
+        <v>200</v>
       </c>
       <c r="BE13" t="str">
         <v/>
@@ -2721,22 +2281,19 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>FG12</v>
+        <v>FG11</v>
       </c>
       <c r="B14" t="str">
-        <v>FG12</v>
+        <v>FG11</v>
       </c>
       <c r="C14">
-        <v>8500</v>
+        <v>8600</v>
       </c>
       <c r="D14">
         <v>800</v>
       </c>
-      <c r="E14" t="str">
-        <v/>
-      </c>
-      <c r="F14" t="str">
-        <v/>
+      <c r="E14">
+        <v>1500</v>
       </c>
       <c r="G14" t="str">
         <v/>
@@ -2744,17 +2301,17 @@
       <c r="H14" t="str">
         <v>D25</v>
       </c>
-      <c r="I14" t="str">
-        <v/>
-      </c>
-      <c r="J14" t="str">
-        <v/>
-      </c>
-      <c r="K14" t="str">
-        <v/>
-      </c>
-      <c r="L14" t="str">
-        <v/>
+      <c r="I14">
+        <v>7</v>
+      </c>
+      <c r="J14">
+        <v>3</v>
+      </c>
+      <c r="K14">
+        <v>7</v>
+      </c>
+      <c r="L14">
+        <v>3</v>
       </c>
       <c r="M14" t="str">
         <v>D13</v>
@@ -2765,26 +2322,26 @@
       <c r="O14">
         <v>200</v>
       </c>
-      <c r="P14" t="str">
-        <v/>
+      <c r="P14">
+        <v>2800</v>
       </c>
       <c r="Q14" t="str">
-        <v/>
+        <v>上=7+3 下=7+3</v>
       </c>
       <c r="R14" t="str">
         <v>D25</v>
       </c>
-      <c r="S14" t="str">
-        <v/>
-      </c>
-      <c r="T14" t="str">
-        <v/>
-      </c>
-      <c r="U14" t="str">
-        <v/>
-      </c>
-      <c r="V14" t="str">
-        <v/>
+      <c r="S14">
+        <v>7</v>
+      </c>
+      <c r="T14">
+        <v>1</v>
+      </c>
+      <c r="U14">
+        <v>7</v>
+      </c>
+      <c r="V14">
+        <v>4</v>
       </c>
       <c r="W14" t="str">
         <v>D13</v>
@@ -2795,11 +2352,11 @@
       <c r="Y14">
         <v>200</v>
       </c>
-      <c r="Z14" t="str">
-        <v/>
+      <c r="Z14">
+        <v>2500</v>
       </c>
       <c r="AA14" t="str">
-        <v/>
+        <v>上=7+1 下=7+4</v>
       </c>
       <c r="AB14" t="str">
         <v>D25</v>
@@ -2808,13 +2365,13 @@
         <v>7</v>
       </c>
       <c r="AD14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE14">
         <v>7</v>
       </c>
       <c r="AF14">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="str">
         <v>D13</v>
@@ -2825,68 +2382,35 @@
       <c r="AI14">
         <v>200</v>
       </c>
-      <c r="AJ14" t="str">
-        <v/>
-      </c>
       <c r="AK14" t="str">
-        <v>上=7+1 下=7+4</v>
+        <v>上=7+3 下=7</v>
       </c>
       <c r="AL14" t="str">
-        <v/>
-      </c>
-      <c r="AM14" t="str">
-        <v/>
-      </c>
-      <c r="AN14" t="str">
-        <v/>
-      </c>
-      <c r="AO14" t="str">
-        <v/>
-      </c>
-      <c r="AP14" t="str">
-        <v/>
+        <v>D25</v>
       </c>
       <c r="AQ14" t="str">
-        <v/>
-      </c>
-      <c r="AR14" t="str">
-        <v/>
-      </c>
-      <c r="AS14" t="str">
-        <v/>
-      </c>
-      <c r="AT14" t="str">
-        <v/>
+        <v>D13</v>
+      </c>
+      <c r="AR14">
+        <v>3</v>
+      </c>
+      <c r="AS14">
+        <v>200</v>
       </c>
       <c r="AU14" t="str">
         <v/>
       </c>
       <c r="AV14" t="str">
-        <v/>
-      </c>
-      <c r="AW14" t="str">
-        <v/>
-      </c>
-      <c r="AX14" t="str">
-        <v/>
-      </c>
-      <c r="AY14" t="str">
-        <v/>
-      </c>
-      <c r="AZ14" t="str">
-        <v/>
+        <v>D25</v>
       </c>
       <c r="BA14" t="str">
-        <v/>
-      </c>
-      <c r="BB14" t="str">
-        <v/>
-      </c>
-      <c r="BC14" t="str">
-        <v/>
-      </c>
-      <c r="BD14" t="str">
-        <v/>
+        <v>D13</v>
+      </c>
+      <c r="BB14">
+        <v>3</v>
+      </c>
+      <c r="BC14">
+        <v>200</v>
       </c>
       <c r="BE14" t="str">
         <v/>
@@ -2894,41 +2418,23 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>FG13</v>
+        <v>FG12</v>
       </c>
       <c r="B15" t="str">
-        <v>FG13</v>
+        <v>FG12</v>
       </c>
       <c r="C15">
-        <v>11900</v>
+        <v>8500</v>
       </c>
       <c r="D15">
         <v>800</v>
       </c>
-      <c r="E15">
-        <v>1500</v>
-      </c>
-      <c r="F15" t="str">
-        <v/>
-      </c>
       <c r="G15" t="str">
         <v/>
       </c>
       <c r="H15" t="str">
         <v>D25</v>
       </c>
-      <c r="I15">
-        <v>7</v>
-      </c>
-      <c r="J15">
-        <v>1</v>
-      </c>
-      <c r="K15">
-        <v>7</v>
-      </c>
-      <c r="L15">
-        <v>4</v>
-      </c>
       <c r="M15" t="str">
         <v>D13</v>
       </c>
@@ -2938,27 +2444,12 @@
       <c r="O15">
         <v>200</v>
       </c>
-      <c r="P15">
-        <v>3200</v>
-      </c>
       <c r="Q15" t="str">
-        <v>上=7+1 下=7+4</v>
+        <v/>
       </c>
       <c r="R15" t="str">
         <v>D25</v>
       </c>
-      <c r="S15">
-        <v>7</v>
-      </c>
-      <c r="T15">
-        <v>7</v>
-      </c>
-      <c r="U15">
-        <v>7</v>
-      </c>
-      <c r="V15">
-        <v>3</v>
-      </c>
       <c r="W15" t="str">
         <v>D13</v>
       </c>
@@ -2968,11 +2459,8 @@
       <c r="Y15">
         <v>200</v>
       </c>
-      <c r="Z15">
-        <v>3200</v>
-      </c>
       <c r="AA15" t="str">
-        <v>上=7+7 下=7+3</v>
+        <v/>
       </c>
       <c r="AB15" t="str">
         <v>D25</v>
@@ -2981,13 +2469,13 @@
         <v>7</v>
       </c>
       <c r="AD15">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="AE15">
         <v>7</v>
       </c>
       <c r="AF15">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AG15" t="str">
         <v>D13</v>
@@ -2998,68 +2486,35 @@
       <c r="AI15">
         <v>200</v>
       </c>
-      <c r="AJ15" t="str">
-        <v/>
-      </c>
       <c r="AK15" t="str">
-        <v>上=7+7 下=7</v>
+        <v>上=7+1 下=7+4</v>
       </c>
       <c r="AL15" t="str">
-        <v/>
-      </c>
-      <c r="AM15" t="str">
-        <v/>
-      </c>
-      <c r="AN15" t="str">
-        <v/>
-      </c>
-      <c r="AO15" t="str">
-        <v/>
-      </c>
-      <c r="AP15" t="str">
-        <v/>
+        <v>D25</v>
       </c>
       <c r="AQ15" t="str">
-        <v/>
-      </c>
-      <c r="AR15" t="str">
-        <v/>
-      </c>
-      <c r="AS15" t="str">
-        <v/>
-      </c>
-      <c r="AT15" t="str">
-        <v/>
+        <v>D13</v>
+      </c>
+      <c r="AR15">
+        <v>3</v>
+      </c>
+      <c r="AS15">
+        <v>200</v>
       </c>
       <c r="AU15" t="str">
         <v/>
       </c>
       <c r="AV15" t="str">
-        <v/>
-      </c>
-      <c r="AW15" t="str">
-        <v/>
-      </c>
-      <c r="AX15" t="str">
-        <v/>
-      </c>
-      <c r="AY15" t="str">
-        <v/>
-      </c>
-      <c r="AZ15" t="str">
-        <v/>
+        <v>D25</v>
       </c>
       <c r="BA15" t="str">
-        <v/>
-      </c>
-      <c r="BB15" t="str">
-        <v/>
-      </c>
-      <c r="BC15" t="str">
-        <v/>
-      </c>
-      <c r="BD15" t="str">
-        <v/>
+        <v>D13</v>
+      </c>
+      <c r="BB15">
+        <v>3</v>
+      </c>
+      <c r="BC15">
+        <v>200</v>
       </c>
       <c r="BE15" t="str">
         <v/>
@@ -3067,22 +2522,19 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>FG14</v>
+        <v>FG13</v>
       </c>
       <c r="B16" t="str">
-        <v>FG14</v>
+        <v>FG13</v>
       </c>
       <c r="C16">
-        <v>8600</v>
-      </c>
-      <c r="D16" t="str">
-        <v/>
+        <v>11900</v>
+      </c>
+      <c r="D16">
+        <v>800</v>
       </c>
       <c r="E16">
-        <v>1200</v>
-      </c>
-      <c r="F16" t="str">
-        <v/>
+        <v>1500</v>
       </c>
       <c r="G16" t="str">
         <v/>
@@ -3091,16 +2543,16 @@
         <v>D25</v>
       </c>
       <c r="I16">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J16">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K16">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L16">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M16" t="str">
         <v>D13</v>
@@ -3112,22 +2564,22 @@
         <v>200</v>
       </c>
       <c r="P16">
-        <v>2700</v>
+        <v>3200</v>
       </c>
       <c r="Q16" t="str">
-        <v>上=6+3 下=6+3</v>
+        <v>上=7+1 下=7+4</v>
       </c>
       <c r="R16" t="str">
         <v>D25</v>
       </c>
       <c r="S16">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T16">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="U16">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V16">
         <v>3</v>
@@ -3142,22 +2594,22 @@
         <v>200</v>
       </c>
       <c r="Z16">
-        <v>2700</v>
+        <v>3200</v>
       </c>
       <c r="AA16" t="str">
-        <v>上=6+3 下=6+3</v>
+        <v>上=7+7 下=7+3</v>
       </c>
       <c r="AB16" t="str">
         <v>D25</v>
       </c>
       <c r="AC16">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AD16">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AE16">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AF16">
         <v>0</v>
@@ -3171,68 +2623,35 @@
       <c r="AI16">
         <v>200</v>
       </c>
-      <c r="AJ16" t="str">
-        <v/>
-      </c>
       <c r="AK16" t="str">
-        <v>上=6 下=6</v>
+        <v>上=7+7 下=7</v>
       </c>
       <c r="AL16" t="str">
-        <v/>
-      </c>
-      <c r="AM16" t="str">
-        <v/>
-      </c>
-      <c r="AN16" t="str">
-        <v/>
-      </c>
-      <c r="AO16" t="str">
-        <v/>
-      </c>
-      <c r="AP16" t="str">
-        <v/>
+        <v>D25</v>
       </c>
       <c r="AQ16" t="str">
-        <v/>
-      </c>
-      <c r="AR16" t="str">
-        <v/>
-      </c>
-      <c r="AS16" t="str">
-        <v/>
-      </c>
-      <c r="AT16" t="str">
-        <v/>
+        <v>D13</v>
+      </c>
+      <c r="AR16">
+        <v>3</v>
+      </c>
+      <c r="AS16">
+        <v>200</v>
       </c>
       <c r="AU16" t="str">
         <v/>
       </c>
       <c r="AV16" t="str">
-        <v/>
-      </c>
-      <c r="AW16" t="str">
-        <v/>
-      </c>
-      <c r="AX16" t="str">
-        <v/>
-      </c>
-      <c r="AY16" t="str">
-        <v/>
-      </c>
-      <c r="AZ16" t="str">
-        <v/>
+        <v>D25</v>
       </c>
       <c r="BA16" t="str">
-        <v/>
-      </c>
-      <c r="BB16" t="str">
-        <v/>
-      </c>
-      <c r="BC16" t="str">
-        <v/>
-      </c>
-      <c r="BD16" t="str">
-        <v/>
+        <v>D13</v>
+      </c>
+      <c r="BB16">
+        <v>3</v>
+      </c>
+      <c r="BC16">
+        <v>200</v>
       </c>
       <c r="BE16" t="str">
         <v/>
@@ -3240,23 +2659,17 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>FG15</v>
+        <v>FG14</v>
       </c>
       <c r="B17" t="str">
-        <v>FG15</v>
+        <v>FG14</v>
       </c>
       <c r="C17">
-        <v>8400</v>
-      </c>
-      <c r="D17">
+        <v>8600</v>
+      </c>
+      <c r="E17">
         <v>1200</v>
       </c>
-      <c r="E17">
-        <v>1500</v>
-      </c>
-      <c r="F17" t="str">
-        <v/>
-      </c>
       <c r="G17" t="str">
         <v/>
       </c>
@@ -3264,73 +2677,73 @@
         <v>D25</v>
       </c>
       <c r="I17">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="J17">
         <v>3</v>
       </c>
       <c r="K17">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="L17">
+        <v>3</v>
+      </c>
+      <c r="M17" t="str">
+        <v>D13</v>
+      </c>
+      <c r="N17">
+        <v>3</v>
+      </c>
+      <c r="O17">
+        <v>200</v>
+      </c>
+      <c r="P17">
+        <v>2700</v>
+      </c>
+      <c r="Q17" t="str">
+        <v>上=6+3 下=6+3</v>
+      </c>
+      <c r="R17" t="str">
+        <v>D25</v>
+      </c>
+      <c r="S17">
+        <v>6</v>
+      </c>
+      <c r="T17">
+        <v>3</v>
+      </c>
+      <c r="U17">
+        <v>6</v>
+      </c>
+      <c r="V17">
+        <v>3</v>
+      </c>
+      <c r="W17" t="str">
+        <v>D13</v>
+      </c>
+      <c r="X17">
+        <v>3</v>
+      </c>
+      <c r="Y17">
+        <v>200</v>
+      </c>
+      <c r="Z17">
+        <v>2700</v>
+      </c>
+      <c r="AA17" t="str">
+        <v>上=6+3 下=6+3</v>
+      </c>
+      <c r="AB17" t="str">
+        <v>D25</v>
+      </c>
+      <c r="AC17">
+        <v>6</v>
+      </c>
+      <c r="AD17">
         <v>0</v>
       </c>
-      <c r="M17" t="str">
-        <v>D13</v>
-      </c>
-      <c r="N17">
-        <v>4</v>
-      </c>
-      <c r="O17">
-        <v>200</v>
-      </c>
-      <c r="P17" t="str">
-        <v/>
-      </c>
-      <c r="Q17" t="str">
-        <v>上=12+3 下=12</v>
-      </c>
-      <c r="R17" t="str">
-        <v>D25</v>
-      </c>
-      <c r="S17">
-        <v>12</v>
-      </c>
-      <c r="T17">
-        <v>3</v>
-      </c>
-      <c r="U17">
-        <v>12</v>
-      </c>
-      <c r="V17">
-        <v>11</v>
-      </c>
-      <c r="W17" t="str">
-        <v>D13</v>
-      </c>
-      <c r="X17">
-        <v>4</v>
-      </c>
-      <c r="Y17">
-        <v>200</v>
-      </c>
-      <c r="Z17">
-        <v>3200</v>
-      </c>
-      <c r="AA17" t="str">
-        <v>上=12+3 下=12+11</v>
-      </c>
-      <c r="AB17" t="str">
-        <v>D25</v>
-      </c>
-      <c r="AC17">
-        <v>12</v>
-      </c>
-      <c r="AD17">
-        <v>3</v>
-      </c>
       <c r="AE17">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="AF17">
         <v>0</v>
@@ -3339,73 +2752,40 @@
         <v>D13</v>
       </c>
       <c r="AH17">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AI17">
         <v>200</v>
       </c>
-      <c r="AJ17" t="str">
-        <v/>
-      </c>
       <c r="AK17" t="str">
-        <v>上=12+3 下=12</v>
+        <v>上=6 下=6</v>
       </c>
       <c r="AL17" t="str">
-        <v/>
-      </c>
-      <c r="AM17" t="str">
-        <v/>
-      </c>
-      <c r="AN17" t="str">
-        <v/>
-      </c>
-      <c r="AO17" t="str">
-        <v/>
-      </c>
-      <c r="AP17" t="str">
-        <v/>
+        <v>D25</v>
       </c>
       <c r="AQ17" t="str">
-        <v/>
-      </c>
-      <c r="AR17" t="str">
-        <v/>
-      </c>
-      <c r="AS17" t="str">
-        <v/>
-      </c>
-      <c r="AT17" t="str">
-        <v/>
+        <v>D13</v>
+      </c>
+      <c r="AR17">
+        <v>3</v>
+      </c>
+      <c r="AS17">
+        <v>200</v>
       </c>
       <c r="AU17" t="str">
         <v/>
       </c>
       <c r="AV17" t="str">
-        <v/>
-      </c>
-      <c r="AW17" t="str">
-        <v/>
-      </c>
-      <c r="AX17" t="str">
-        <v/>
-      </c>
-      <c r="AY17" t="str">
-        <v/>
-      </c>
-      <c r="AZ17" t="str">
-        <v/>
+        <v>D25</v>
       </c>
       <c r="BA17" t="str">
-        <v/>
-      </c>
-      <c r="BB17" t="str">
-        <v/>
-      </c>
-      <c r="BC17" t="str">
-        <v/>
-      </c>
-      <c r="BD17" t="str">
-        <v/>
+        <v>D13</v>
+      </c>
+      <c r="BB17">
+        <v>3</v>
+      </c>
+      <c r="BC17">
+        <v>200</v>
       </c>
       <c r="BE17" t="str">
         <v/>
@@ -3413,13 +2793,13 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>FG16</v>
+        <v>FG15</v>
       </c>
       <c r="B18" t="str">
-        <v>FG16</v>
+        <v>FG15</v>
       </c>
       <c r="C18">
-        <v>6000</v>
+        <v>8400</v>
       </c>
       <c r="D18">
         <v>1200</v>
@@ -3427,9 +2807,6 @@
       <c r="E18">
         <v>1500</v>
       </c>
-      <c r="F18" t="str">
-        <v/>
-      </c>
       <c r="G18" t="str">
         <v/>
       </c>
@@ -3440,13 +2817,13 @@
         <v>12</v>
       </c>
       <c r="J18">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K18">
         <v>12</v>
       </c>
       <c r="L18">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M18" t="str">
         <v>D13</v>
@@ -3457,26 +2834,23 @@
       <c r="O18">
         <v>200</v>
       </c>
-      <c r="P18">
-        <v>3200</v>
-      </c>
       <c r="Q18" t="str">
-        <v>上=12 下=12+10</v>
+        <v>上=12+3 下=12</v>
       </c>
       <c r="R18" t="str">
         <v>D25</v>
       </c>
-      <c r="S18" t="str">
-        <v/>
-      </c>
-      <c r="T18" t="str">
-        <v/>
-      </c>
-      <c r="U18" t="str">
-        <v/>
-      </c>
-      <c r="V18" t="str">
-        <v/>
+      <c r="S18">
+        <v>12</v>
+      </c>
+      <c r="T18">
+        <v>3</v>
+      </c>
+      <c r="U18">
+        <v>12</v>
+      </c>
+      <c r="V18">
+        <v>11</v>
       </c>
       <c r="W18" t="str">
         <v>D13</v>
@@ -3487,26 +2861,26 @@
       <c r="Y18">
         <v>200</v>
       </c>
-      <c r="Z18" t="str">
-        <v/>
+      <c r="Z18">
+        <v>3200</v>
       </c>
       <c r="AA18" t="str">
-        <v/>
+        <v>上=12+3 下=12+11</v>
       </c>
       <c r="AB18" t="str">
         <v>D25</v>
       </c>
-      <c r="AC18" t="str">
-        <v/>
-      </c>
-      <c r="AD18" t="str">
-        <v/>
-      </c>
-      <c r="AE18" t="str">
-        <v/>
-      </c>
-      <c r="AF18" t="str">
-        <v/>
+      <c r="AC18">
+        <v>12</v>
+      </c>
+      <c r="AD18">
+        <v>3</v>
+      </c>
+      <c r="AE18">
+        <v>12</v>
+      </c>
+      <c r="AF18">
+        <v>0</v>
       </c>
       <c r="AG18" t="str">
         <v>D13</v>
@@ -3517,68 +2891,35 @@
       <c r="AI18">
         <v>200</v>
       </c>
-      <c r="AJ18" t="str">
-        <v/>
-      </c>
       <c r="AK18" t="str">
-        <v/>
+        <v>上=12+3 下=12</v>
       </c>
       <c r="AL18" t="str">
-        <v/>
-      </c>
-      <c r="AM18" t="str">
-        <v/>
-      </c>
-      <c r="AN18" t="str">
-        <v/>
-      </c>
-      <c r="AO18" t="str">
-        <v/>
-      </c>
-      <c r="AP18" t="str">
-        <v/>
+        <v>D25</v>
       </c>
       <c r="AQ18" t="str">
-        <v/>
-      </c>
-      <c r="AR18" t="str">
-        <v/>
-      </c>
-      <c r="AS18" t="str">
-        <v/>
-      </c>
-      <c r="AT18" t="str">
-        <v/>
+        <v>D13</v>
+      </c>
+      <c r="AR18">
+        <v>4</v>
+      </c>
+      <c r="AS18">
+        <v>200</v>
       </c>
       <c r="AU18" t="str">
         <v/>
       </c>
       <c r="AV18" t="str">
-        <v/>
-      </c>
-      <c r="AW18" t="str">
-        <v/>
-      </c>
-      <c r="AX18" t="str">
-        <v/>
-      </c>
-      <c r="AY18" t="str">
-        <v/>
-      </c>
-      <c r="AZ18" t="str">
-        <v/>
+        <v>D25</v>
       </c>
       <c r="BA18" t="str">
-        <v/>
-      </c>
-      <c r="BB18" t="str">
-        <v/>
-      </c>
-      <c r="BC18" t="str">
-        <v/>
-      </c>
-      <c r="BD18" t="str">
-        <v/>
+        <v>D13</v>
+      </c>
+      <c r="BB18">
+        <v>4</v>
+      </c>
+      <c r="BC18">
+        <v>200</v>
       </c>
       <c r="BE18" t="str">
         <v/>
@@ -3586,172 +2927,109 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>FG17</v>
+        <v>FG16</v>
       </c>
       <c r="B19" t="str">
-        <v>FG17</v>
+        <v>FG16</v>
       </c>
       <c r="C19">
-        <v>84006000</v>
-      </c>
-      <c r="D19" t="str">
-        <v/>
-      </c>
-      <c r="E19" t="str">
-        <v/>
-      </c>
-      <c r="F19" t="str">
-        <v/>
+        <v>6000</v>
+      </c>
+      <c r="D19">
+        <v>1200</v>
+      </c>
+      <c r="E19">
+        <v>1500</v>
       </c>
       <c r="G19" t="str">
         <v/>
       </c>
       <c r="H19" t="str">
-        <v/>
+        <v>D25</v>
       </c>
       <c r="I19">
+        <v>12</v>
+      </c>
+      <c r="J19">
+        <v>0</v>
+      </c>
+      <c r="K19">
+        <v>12</v>
+      </c>
+      <c r="L19">
+        <v>10</v>
+      </c>
+      <c r="M19" t="str">
+        <v>D13</v>
+      </c>
+      <c r="N19">
         <v>4</v>
       </c>
-      <c r="J19">
-        <v>2</v>
-      </c>
-      <c r="K19">
+      <c r="O19">
+        <v>200</v>
+      </c>
+      <c r="P19">
+        <v>3200</v>
+      </c>
+      <c r="Q19" t="str">
+        <v>上=12 下=12+10</v>
+      </c>
+      <c r="R19" t="str">
+        <v>D25</v>
+      </c>
+      <c r="W19" t="str">
+        <v>D13</v>
+      </c>
+      <c r="X19">
         <v>4</v>
       </c>
-      <c r="L19">
-        <v>2</v>
-      </c>
-      <c r="M19" t="str">
-        <v>D13</v>
-      </c>
-      <c r="N19">
-        <v>2</v>
-      </c>
-      <c r="O19">
-        <v>200</v>
-      </c>
-      <c r="P19" t="str">
-        <v/>
-      </c>
-      <c r="Q19" t="str">
-        <v>上=4+2(4+4) 下=4+2(4+4)</v>
-      </c>
-      <c r="R19" t="str">
-        <v/>
-      </c>
-      <c r="S19">
+      <c r="Y19">
+        <v>200</v>
+      </c>
+      <c r="AA19" t="str">
+        <v/>
+      </c>
+      <c r="AB19" t="str">
+        <v>D25</v>
+      </c>
+      <c r="AG19" t="str">
+        <v>D13</v>
+      </c>
+      <c r="AH19">
         <v>4</v>
       </c>
-      <c r="T19">
-        <v>2</v>
-      </c>
-      <c r="U19">
+      <c r="AI19">
+        <v>200</v>
+      </c>
+      <c r="AK19" t="str">
+        <v/>
+      </c>
+      <c r="AL19" t="str">
+        <v>D25</v>
+      </c>
+      <c r="AQ19" t="str">
+        <v>D13</v>
+      </c>
+      <c r="AR19">
         <v>4</v>
       </c>
-      <c r="V19">
-        <v>2</v>
-      </c>
-      <c r="W19" t="str">
-        <v>D13</v>
-      </c>
-      <c r="X19">
-        <v>2</v>
-      </c>
-      <c r="Y19">
-        <v>200</v>
-      </c>
-      <c r="Z19" t="str">
-        <v/>
-      </c>
-      <c r="AA19" t="str">
-        <v>上=4+2(4+4) 下=4+2(4+4)</v>
-      </c>
-      <c r="AB19" t="str">
-        <v/>
-      </c>
-      <c r="AC19" t="str">
-        <v/>
-      </c>
-      <c r="AD19" t="str">
-        <v/>
-      </c>
-      <c r="AE19" t="str">
-        <v/>
-      </c>
-      <c r="AF19" t="str">
-        <v/>
-      </c>
-      <c r="AG19" t="str">
-        <v>D13</v>
-      </c>
-      <c r="AH19">
-        <v>2</v>
-      </c>
-      <c r="AI19">
-        <v>200</v>
-      </c>
-      <c r="AJ19" t="str">
-        <v/>
-      </c>
-      <c r="AK19" t="str">
-        <v/>
-      </c>
-      <c r="AL19" t="str">
-        <v/>
-      </c>
-      <c r="AM19" t="str">
-        <v/>
-      </c>
-      <c r="AN19" t="str">
-        <v/>
-      </c>
-      <c r="AO19" t="str">
-        <v/>
-      </c>
-      <c r="AP19" t="str">
-        <v/>
-      </c>
-      <c r="AQ19" t="str">
-        <v/>
-      </c>
-      <c r="AR19" t="str">
-        <v/>
-      </c>
-      <c r="AS19" t="str">
-        <v/>
-      </c>
-      <c r="AT19" t="str">
-        <v/>
+      <c r="AS19">
+        <v>200</v>
       </c>
       <c r="AU19" t="str">
         <v/>
       </c>
       <c r="AV19" t="str">
-        <v/>
-      </c>
-      <c r="AW19" t="str">
-        <v/>
-      </c>
-      <c r="AX19" t="str">
-        <v/>
-      </c>
-      <c r="AY19" t="str">
-        <v/>
-      </c>
-      <c r="AZ19" t="str">
-        <v/>
+        <v>D25</v>
       </c>
       <c r="BA19" t="str">
-        <v/>
-      </c>
-      <c r="BB19" t="str">
-        <v/>
-      </c>
-      <c r="BC19" t="str">
-        <v/>
-      </c>
-      <c r="BD19" t="str">
-        <v/>
+        <v>D13</v>
+      </c>
+      <c r="BB19">
+        <v>4</v>
+      </c>
+      <c r="BC19">
+        <v>200</v>
       </c>
       <c r="BE19" t="str">
         <v/>
@@ -3759,27 +3037,15 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>FG18</v>
+        <v>FG17</v>
       </c>
       <c r="B20" t="str">
-        <v>FG18</v>
+        <v>FG17</v>
       </c>
       <c r="C20">
         <v>84006000</v>
       </c>
-      <c r="D20" t="str">
-        <v/>
-      </c>
-      <c r="E20" t="str">
-        <v/>
-      </c>
-      <c r="F20" t="str">
-        <v/>
-      </c>
       <c r="G20" t="str">
-        <v/>
-      </c>
-      <c r="H20" t="str">
         <v/>
       </c>
       <c r="I20">
@@ -3803,15 +3069,9 @@
       <c r="O20">
         <v>200</v>
       </c>
-      <c r="P20" t="str">
-        <v/>
-      </c>
       <c r="Q20" t="str">
         <v>上=4+2(4+4) 下=4+2(4+4)</v>
       </c>
-      <c r="R20" t="str">
-        <v/>
-      </c>
       <c r="S20">
         <v>4</v>
       </c>
@@ -3833,27 +3093,9 @@
       <c r="Y20">
         <v>200</v>
       </c>
-      <c r="Z20" t="str">
-        <v/>
-      </c>
       <c r="AA20" t="str">
         <v>上=4+2(4+4) 下=4+2(4+4)</v>
       </c>
-      <c r="AB20" t="str">
-        <v/>
-      </c>
-      <c r="AC20" t="str">
-        <v/>
-      </c>
-      <c r="AD20" t="str">
-        <v/>
-      </c>
-      <c r="AE20" t="str">
-        <v/>
-      </c>
-      <c r="AF20" t="str">
-        <v/>
-      </c>
       <c r="AG20" t="str">
         <v>D13</v>
       </c>
@@ -3863,68 +3105,29 @@
       <c r="AI20">
         <v>200</v>
       </c>
-      <c r="AJ20" t="str">
-        <v/>
-      </c>
       <c r="AK20" t="str">
         <v/>
       </c>
-      <c r="AL20" t="str">
-        <v/>
-      </c>
-      <c r="AM20" t="str">
-        <v/>
-      </c>
-      <c r="AN20" t="str">
-        <v/>
-      </c>
-      <c r="AO20" t="str">
-        <v/>
-      </c>
-      <c r="AP20" t="str">
-        <v/>
-      </c>
       <c r="AQ20" t="str">
-        <v/>
-      </c>
-      <c r="AR20" t="str">
-        <v/>
-      </c>
-      <c r="AS20" t="str">
-        <v/>
-      </c>
-      <c r="AT20" t="str">
-        <v/>
+        <v>D13</v>
+      </c>
+      <c r="AR20">
+        <v>2</v>
+      </c>
+      <c r="AS20">
+        <v>200</v>
       </c>
       <c r="AU20" t="str">
         <v/>
       </c>
-      <c r="AV20" t="str">
-        <v/>
-      </c>
-      <c r="AW20" t="str">
-        <v/>
-      </c>
-      <c r="AX20" t="str">
-        <v/>
-      </c>
-      <c r="AY20" t="str">
-        <v/>
-      </c>
-      <c r="AZ20" t="str">
-        <v/>
-      </c>
       <c r="BA20" t="str">
-        <v/>
-      </c>
-      <c r="BB20" t="str">
-        <v/>
-      </c>
-      <c r="BC20" t="str">
-        <v/>
-      </c>
-      <c r="BD20" t="str">
-        <v/>
+        <v>D13</v>
+      </c>
+      <c r="BB20">
+        <v>2</v>
+      </c>
+      <c r="BC20">
+        <v>200</v>
       </c>
       <c r="BE20" t="str">
         <v/>
@@ -3932,27 +3135,15 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>FG19</v>
+        <v>FG18</v>
       </c>
       <c r="B21" t="str">
-        <v>FG19</v>
+        <v>FG18</v>
       </c>
       <c r="C21">
         <v>84006000</v>
       </c>
-      <c r="D21" t="str">
-        <v/>
-      </c>
-      <c r="E21" t="str">
-        <v/>
-      </c>
-      <c r="F21" t="str">
-        <v/>
-      </c>
       <c r="G21" t="str">
-        <v/>
-      </c>
-      <c r="H21" t="str">
         <v/>
       </c>
       <c r="I21">
@@ -3976,15 +3167,9 @@
       <c r="O21">
         <v>200</v>
       </c>
-      <c r="P21" t="str">
-        <v/>
-      </c>
       <c r="Q21" t="str">
         <v>上=4+2(4+4) 下=4+2(4+4)</v>
       </c>
-      <c r="R21" t="str">
-        <v/>
-      </c>
       <c r="S21">
         <v>4</v>
       </c>
@@ -4006,27 +3191,9 @@
       <c r="Y21">
         <v>200</v>
       </c>
-      <c r="Z21" t="str">
-        <v/>
-      </c>
       <c r="AA21" t="str">
         <v>上=4+2(4+4) 下=4+2(4+4)</v>
       </c>
-      <c r="AB21" t="str">
-        <v/>
-      </c>
-      <c r="AC21" t="str">
-        <v/>
-      </c>
-      <c r="AD21" t="str">
-        <v/>
-      </c>
-      <c r="AE21" t="str">
-        <v/>
-      </c>
-      <c r="AF21" t="str">
-        <v/>
-      </c>
       <c r="AG21" t="str">
         <v>D13</v>
       </c>
@@ -4036,85 +3203,174 @@
       <c r="AI21">
         <v>200</v>
       </c>
-      <c r="AJ21" t="str">
-        <v/>
-      </c>
       <c r="AK21" t="str">
         <v/>
       </c>
-      <c r="AL21" t="str">
-        <v/>
-      </c>
-      <c r="AM21" t="str">
-        <v/>
-      </c>
-      <c r="AN21" t="str">
-        <v/>
-      </c>
-      <c r="AO21" t="str">
-        <v/>
-      </c>
-      <c r="AP21" t="str">
-        <v/>
-      </c>
       <c r="AQ21" t="str">
-        <v/>
-      </c>
-      <c r="AR21" t="str">
-        <v/>
-      </c>
-      <c r="AS21" t="str">
-        <v/>
-      </c>
-      <c r="AT21" t="str">
-        <v/>
+        <v>D13</v>
+      </c>
+      <c r="AR21">
+        <v>2</v>
+      </c>
+      <c r="AS21">
+        <v>200</v>
       </c>
       <c r="AU21" t="str">
         <v/>
       </c>
-      <c r="AV21" t="str">
-        <v/>
-      </c>
-      <c r="AW21" t="str">
-        <v/>
-      </c>
-      <c r="AX21" t="str">
-        <v/>
-      </c>
-      <c r="AY21" t="str">
-        <v/>
-      </c>
-      <c r="AZ21" t="str">
-        <v/>
-      </c>
       <c r="BA21" t="str">
-        <v/>
-      </c>
-      <c r="BB21" t="str">
-        <v/>
-      </c>
-      <c r="BC21" t="str">
-        <v/>
-      </c>
-      <c r="BD21" t="str">
-        <v/>
+        <v>D13</v>
+      </c>
+      <c r="BB21">
+        <v>2</v>
+      </c>
+      <c r="BC21">
+        <v>200</v>
       </c>
       <c r="BE21" t="str">
         <v/>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>FG19</v>
+      </c>
+      <c r="B22" t="str">
+        <v>FG19</v>
+      </c>
+      <c r="C22">
+        <v>84006000</v>
+      </c>
+      <c r="G22" t="str">
+        <v/>
+      </c>
+      <c r="I22">
+        <v>4</v>
+      </c>
+      <c r="J22">
+        <v>2</v>
+      </c>
+      <c r="K22">
+        <v>4</v>
+      </c>
+      <c r="L22">
+        <v>2</v>
+      </c>
+      <c r="M22" t="str">
+        <v>D13</v>
+      </c>
+      <c r="N22">
+        <v>2</v>
+      </c>
+      <c r="O22">
+        <v>200</v>
+      </c>
+      <c r="Q22" t="str">
+        <v>上=4+2(4+4) 下=4+2(4+4)</v>
+      </c>
+      <c r="S22">
+        <v>4</v>
+      </c>
+      <c r="T22">
+        <v>2</v>
+      </c>
+      <c r="U22">
+        <v>4</v>
+      </c>
+      <c r="V22">
+        <v>2</v>
+      </c>
+      <c r="W22" t="str">
+        <v>D13</v>
+      </c>
+      <c r="X22">
+        <v>2</v>
+      </c>
+      <c r="Y22">
+        <v>200</v>
+      </c>
+      <c r="AA22" t="str">
+        <v>上=4+2(4+4) 下=4+2(4+4)</v>
+      </c>
+      <c r="AG22" t="str">
+        <v>D13</v>
+      </c>
+      <c r="AH22">
+        <v>2</v>
+      </c>
+      <c r="AI22">
+        <v>200</v>
+      </c>
+      <c r="AK22" t="str">
+        <v/>
+      </c>
+      <c r="AQ22" t="str">
+        <v>D13</v>
+      </c>
+      <c r="AR22">
+        <v>2</v>
+      </c>
+      <c r="AS22">
+        <v>200</v>
+      </c>
+      <c r="AU22" t="str">
+        <v/>
+      </c>
+      <c r="BA22" t="str">
+        <v>D13</v>
+      </c>
+      <c r="BB22">
+        <v>2</v>
+      </c>
+      <c r="BC22">
+        <v>200</v>
+      </c>
+      <c r="BE22" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
+  <mergeCells count="12">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="H1:Q1"/>
+    <mergeCell ref="R1:AA1"/>
+    <mergeCell ref="AB1:AK1"/>
+    <mergeCell ref="AL1:AU1"/>
+    <mergeCell ref="AV1:BE1"/>
+  </mergeCells>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:BE21"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:BE22"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N17"/>
+  <dimension ref="A1:N18"/>
+  <cols>
+    <col min="1" max="1" width="10.83203125" customWidth="1"/>
+    <col min="2" max="2" width="10.83203125" customWidth="1"/>
+    <col min="3" max="3" width="10.83203125" customWidth="1"/>
+    <col min="4" max="4" width="10.83203125" customWidth="1"/>
+    <col min="5" max="5" width="10.83203125" customWidth="1"/>
+    <col min="6" max="6" width="10.83203125" customWidth="1"/>
+    <col min="7" max="7" width="13.83203125" customWidth="1"/>
+    <col min="8" max="8" width="16.83203125" customWidth="1"/>
+    <col min="9" max="9" width="10.83203125" customWidth="1"/>
+    <col min="10" max="10" width="10.83203125" customWidth="1"/>
+    <col min="11" max="11" width="10.83203125" customWidth="1"/>
+    <col min="12" max="12" width="10.83203125" customWidth="1"/>
+    <col min="13" max="13" width="10.83203125" customWidth="1"/>
+    <col min="14" max="14" width="10.83203125" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="22" customHeight="1">
       <c r="A1" t="str">
         <v>TypeName</v>
       </c>
@@ -4122,28 +3378,28 @@
         <v>符号</v>
       </c>
       <c r="C1" t="str">
-        <v>断面形式</v>
+        <v>断面</v>
       </c>
       <c r="D1" t="str">
-        <v>成H_mm</v>
+        <v/>
       </c>
       <c r="E1" t="str">
-        <v>幅B_mm</v>
+        <v/>
       </c>
       <c r="F1" t="str">
-        <v>ウェブtw_mm</v>
+        <v/>
       </c>
       <c r="G1" t="str">
-        <v>フランジtf_mm</v>
+        <v/>
       </c>
       <c r="H1" t="str">
-        <v>スパン_mm</v>
+        <v>スパン_mm (CSV)</v>
       </c>
       <c r="I1" t="str">
-        <v>通り起点</v>
+        <v>通り</v>
       </c>
       <c r="J1" t="str">
-        <v>通り終点</v>
+        <v/>
       </c>
       <c r="K1" t="str">
         <v>鋼材グレード</v>
@@ -4158,36 +3414,36 @@
         <v>備考</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" ht="22" customHeight="1">
       <c r="A2" t="str">
-        <v>SG1</v>
+        <v/>
       </c>
       <c r="B2" t="str">
-        <v>SG1</v>
+        <v/>
       </c>
       <c r="C2" t="str">
-        <v>SH</v>
-      </c>
-      <c r="D2">
-        <v>600</v>
-      </c>
-      <c r="E2">
-        <v>200</v>
-      </c>
-      <c r="F2">
-        <v>12</v>
-      </c>
-      <c r="G2">
-        <v>16</v>
+        <v>形式</v>
+      </c>
+      <c r="D2" t="str">
+        <v>成H_mm</v>
+      </c>
+      <c r="E2" t="str">
+        <v>幅B_mm</v>
+      </c>
+      <c r="F2" t="str">
+        <v>ウェブtw_mm</v>
+      </c>
+      <c r="G2" t="str">
+        <v>フランジtf_mm</v>
       </c>
       <c r="H2" t="str">
-        <v>8400;7800;6450;6000</v>
+        <v/>
       </c>
       <c r="I2" t="str">
-        <v/>
+        <v>起点</v>
       </c>
       <c r="J2" t="str">
-        <v/>
+        <v>終点</v>
       </c>
       <c r="K2" t="str">
         <v/>
@@ -4196,7 +3452,7 @@
         <v/>
       </c>
       <c r="M2" t="str">
-        <v>SH-600×200×12×16</v>
+        <v/>
       </c>
       <c r="N2" t="str">
         <v/>
@@ -4204,10 +3460,10 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>SG1A</v>
+        <v>SG1</v>
       </c>
       <c r="B3" t="str">
-        <v>SG1A</v>
+        <v>SG1</v>
       </c>
       <c r="C3" t="str">
         <v>SH</v>
@@ -4216,22 +3472,22 @@
         <v>600</v>
       </c>
       <c r="E3">
-        <v>250</v>
+        <v>200</v>
       </c>
       <c r="F3">
         <v>12</v>
       </c>
       <c r="G3">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="H3" t="str">
-        <v>6450</v>
+        <v>8400;7800;6450;6000</v>
       </c>
       <c r="I3" t="str">
-        <v>Xd1</v>
+        <v/>
       </c>
       <c r="J3" t="str">
-        <v>Xd2</v>
+        <v/>
       </c>
       <c r="K3" t="str">
         <v/>
@@ -4240,7 +3496,7 @@
         <v/>
       </c>
       <c r="M3" t="str">
-        <v>SH-600×250×12×28</v>
+        <v>SH-600×200×12×16</v>
       </c>
       <c r="N3" t="str">
         <v/>
@@ -4248,10 +3504,10 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>SG2</v>
+        <v>SG1A</v>
       </c>
       <c r="B4" t="str">
-        <v>SG2</v>
+        <v>SG1A</v>
       </c>
       <c r="C4" t="str">
         <v>SH</v>
@@ -4260,22 +3516,22 @@
         <v>600</v>
       </c>
       <c r="E4">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="F4">
         <v>12</v>
       </c>
       <c r="G4">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="H4" t="str">
-        <v>7800;6450;6000</v>
+        <v>6450</v>
       </c>
       <c r="I4" t="str">
         <v>Xd1</v>
       </c>
       <c r="J4" t="str">
-        <v>Xd9</v>
+        <v>Xd2</v>
       </c>
       <c r="K4" t="str">
         <v/>
@@ -4284,7 +3540,7 @@
         <v/>
       </c>
       <c r="M4" t="str">
-        <v>SH-600×200×12×16</v>
+        <v>SH-600×250×12×28</v>
       </c>
       <c r="N4" t="str">
         <v/>
@@ -4292,10 +3548,10 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>SG2A</v>
+        <v>SG2</v>
       </c>
       <c r="B5" t="str">
-        <v>SG2A</v>
+        <v>SG2</v>
       </c>
       <c r="C5" t="str">
         <v>SH</v>
@@ -4304,22 +3560,22 @@
         <v>600</v>
       </c>
       <c r="E5">
-        <v>250</v>
+        <v>200</v>
       </c>
       <c r="F5">
         <v>12</v>
       </c>
       <c r="G5">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="H5" t="str">
-        <v>6450</v>
+        <v>7800;6450;6000</v>
       </c>
       <c r="I5" t="str">
         <v>Xd1</v>
       </c>
       <c r="J5" t="str">
-        <v>Xd2</v>
+        <v>Xd9</v>
       </c>
       <c r="K5" t="str">
         <v/>
@@ -4328,7 +3584,7 @@
         <v/>
       </c>
       <c r="M5" t="str">
-        <v>SH-600×250×12×28</v>
+        <v>SH-600×200×12×16</v>
       </c>
       <c r="N5" t="str">
         <v/>
@@ -4336,10 +3592,10 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>SG3</v>
+        <v>SG2A</v>
       </c>
       <c r="B6" t="str">
-        <v>SG3</v>
+        <v>SG2A</v>
       </c>
       <c r="C6" t="str">
         <v>SH</v>
@@ -4348,22 +3604,22 @@
         <v>600</v>
       </c>
       <c r="E6">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="F6">
         <v>12</v>
       </c>
       <c r="G6">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="H6" t="str">
-        <v>8400;7800</v>
+        <v>6450</v>
       </c>
       <c r="I6" t="str">
-        <v>Xd5</v>
+        <v>Xd1</v>
       </c>
       <c r="J6" t="str">
-        <v>Xd11</v>
+        <v>Xd2</v>
       </c>
       <c r="K6" t="str">
         <v/>
@@ -4372,7 +3628,7 @@
         <v/>
       </c>
       <c r="M6" t="str">
-        <v>SH-600×200×12×16</v>
+        <v>SH-600×250×12×28</v>
       </c>
       <c r="N6" t="str">
         <v/>
@@ -4380,10 +3636,10 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>SG4</v>
+        <v>SG3</v>
       </c>
       <c r="B7" t="str">
-        <v>SG4</v>
+        <v>SG3</v>
       </c>
       <c r="C7" t="str">
         <v>SH</v>
@@ -4392,23 +3648,23 @@
         <v>600</v>
       </c>
       <c r="E7">
-        <v>250</v>
+        <v>200</v>
       </c>
       <c r="F7">
         <v>12</v>
       </c>
       <c r="G7">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="H7" t="str">
-        <v>6000</v>
+        <v>8400;7800</v>
       </c>
       <c r="I7" t="str">
+        <v>Xd5</v>
+      </c>
+      <c r="J7" t="str">
         <v>Xd11</v>
       </c>
-      <c r="J7" t="str">
-        <v>Xd12</v>
-      </c>
       <c r="K7" t="str">
         <v/>
       </c>
@@ -4416,7 +3672,7 @@
         <v/>
       </c>
       <c r="M7" t="str">
-        <v>SH-600×250×12×25</v>
+        <v>SH-600×200×12×16</v>
       </c>
       <c r="N7" t="str">
         <v/>
@@ -4424,10 +3680,10 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>SG5</v>
+        <v>SG4</v>
       </c>
       <c r="B8" t="str">
-        <v>SG5</v>
+        <v>SG4</v>
       </c>
       <c r="C8" t="str">
         <v>SH</v>
@@ -4442,16 +3698,16 @@
         <v>12</v>
       </c>
       <c r="G8">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="H8" t="str">
-        <v>6450</v>
+        <v>6000</v>
       </c>
       <c r="I8" t="str">
-        <v>Xd2</v>
+        <v>Xd11</v>
       </c>
       <c r="J8" t="str">
-        <v>Xd3</v>
+        <v>Xd12</v>
       </c>
       <c r="K8" t="str">
         <v/>
@@ -4460,7 +3716,7 @@
         <v/>
       </c>
       <c r="M8" t="str">
-        <v>SH-600×250×12×28</v>
+        <v>SH-600×250×12×25</v>
       </c>
       <c r="N8" t="str">
         <v/>
@@ -4468,10 +3724,10 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>SG6</v>
+        <v>SG5</v>
       </c>
       <c r="B9" t="str">
-        <v>SG6</v>
+        <v>SG5</v>
       </c>
       <c r="C9" t="str">
         <v>SH</v>
@@ -4480,23 +3736,23 @@
         <v>600</v>
       </c>
       <c r="E9">
-        <v>300</v>
+        <v>250</v>
       </c>
       <c r="F9">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="G9">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="H9" t="str">
         <v>6450</v>
       </c>
       <c r="I9" t="str">
+        <v>Xd2</v>
+      </c>
+      <c r="J9" t="str">
         <v>Xd3</v>
       </c>
-      <c r="J9" t="str">
-        <v>Xd4</v>
-      </c>
       <c r="K9" t="str">
         <v/>
       </c>
@@ -4504,7 +3760,7 @@
         <v/>
       </c>
       <c r="M9" t="str">
-        <v>SH-600×300×16×32</v>
+        <v>SH-600×250×12×28</v>
       </c>
       <c r="N9" t="str">
         <v/>
@@ -4512,10 +3768,10 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>SG7</v>
+        <v>SG6</v>
       </c>
       <c r="B10" t="str">
-        <v>SG7</v>
+        <v>SG6</v>
       </c>
       <c r="C10" t="str">
         <v>SH</v>
@@ -4524,23 +3780,23 @@
         <v>600</v>
       </c>
       <c r="E10">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="F10">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G10">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="H10" t="str">
-        <v>7800</v>
+        <v>6450</v>
       </c>
       <c r="I10" t="str">
+        <v>Xd3</v>
+      </c>
+      <c r="J10" t="str">
         <v>Xd4</v>
       </c>
-      <c r="J10" t="str">
-        <v>Xd5</v>
-      </c>
       <c r="K10" t="str">
         <v/>
       </c>
@@ -4548,7 +3804,7 @@
         <v/>
       </c>
       <c r="M10" t="str">
-        <v>SH-600×250×12×28</v>
+        <v>SH-600×300×16×32</v>
       </c>
       <c r="N10" t="str">
         <v/>
@@ -4556,34 +3812,34 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>SG8</v>
+        <v>SG7</v>
       </c>
       <c r="B11" t="str">
-        <v>SG8</v>
+        <v>SG7</v>
       </c>
       <c r="C11" t="str">
         <v>SH</v>
       </c>
       <c r="D11">
-        <v>800</v>
+        <v>600</v>
       </c>
       <c r="E11">
-        <v>400</v>
+        <v>250</v>
       </c>
       <c r="F11">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="G11">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="H11" t="str">
-        <v>14400;8400</v>
+        <v>7800</v>
       </c>
       <c r="I11" t="str">
-        <v>Xd9</v>
+        <v>Xd4</v>
       </c>
       <c r="J11" t="str">
-        <v>Xd12</v>
+        <v>Xd5</v>
       </c>
       <c r="K11" t="str">
         <v/>
@@ -4592,7 +3848,7 @@
         <v/>
       </c>
       <c r="M11" t="str">
-        <v>SH-800×400×19×36</v>
+        <v>SH-600×250×12×28</v>
       </c>
       <c r="N11" t="str">
         <v/>
@@ -4600,13 +3856,13 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>SG9</v>
+        <v>SG8</v>
       </c>
       <c r="B12" t="str">
-        <v>SG9</v>
+        <v>SG8</v>
       </c>
       <c r="C12" t="str">
-        <v>BH</v>
+        <v>SH</v>
       </c>
       <c r="D12">
         <v>800</v>
@@ -4615,20 +3871,20 @@
         <v>400</v>
       </c>
       <c r="F12">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G12">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="H12" t="str">
-        <v>3450</v>
+        <v>14400;8400</v>
       </c>
       <c r="I12" t="str">
+        <v>Xd9</v>
+      </c>
+      <c r="J12" t="str">
         <v>Xd12</v>
       </c>
-      <c r="J12" t="str">
-        <v>Xd13</v>
-      </c>
       <c r="K12" t="str">
         <v/>
       </c>
@@ -4636,7 +3892,7 @@
         <v/>
       </c>
       <c r="M12" t="str">
-        <v>BH-800×400×16×32</v>
+        <v>SH-800×400×19×36</v>
       </c>
       <c r="N12" t="str">
         <v/>
@@ -4644,34 +3900,34 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>SG10</v>
+        <v>SG9</v>
       </c>
       <c r="B13" t="str">
-        <v>SG10</v>
+        <v>SG9</v>
       </c>
       <c r="C13" t="str">
-        <v>SH</v>
+        <v>BH</v>
       </c>
       <c r="D13">
-        <v>600</v>
+        <v>800</v>
       </c>
       <c r="E13">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="F13">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G13">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="H13" t="str">
-        <v>7800;6450</v>
+        <v>3450</v>
       </c>
       <c r="I13" t="str">
-        <v>Xd2</v>
+        <v>Xd12</v>
       </c>
       <c r="J13" t="str">
-        <v>Xd5</v>
+        <v>Xd13</v>
       </c>
       <c r="K13" t="str">
         <v/>
@@ -4680,7 +3936,7 @@
         <v/>
       </c>
       <c r="M13" t="str">
-        <v>SH-600×300×12×28</v>
+        <v>BH-800×400×16×32</v>
       </c>
       <c r="N13" t="str">
         <v/>
@@ -4688,34 +3944,34 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>SG11</v>
+        <v>SG10</v>
       </c>
       <c r="B14" t="str">
-        <v>SG11</v>
+        <v>SG10</v>
       </c>
       <c r="C14" t="str">
-        <v>BH</v>
+        <v>SH</v>
       </c>
       <c r="D14">
         <v>600</v>
       </c>
       <c r="E14">
-        <v>350</v>
+        <v>300</v>
       </c>
       <c r="F14">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="G14">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="H14" t="str">
-        <v>6450</v>
+        <v>7800;6450</v>
       </c>
       <c r="I14" t="str">
-        <v>Xd3</v>
+        <v>Xd2</v>
       </c>
       <c r="J14" t="str">
-        <v>Xd4</v>
+        <v>Xd5</v>
       </c>
       <c r="K14" t="str">
         <v/>
@@ -4724,7 +3980,7 @@
         <v/>
       </c>
       <c r="M14" t="str">
-        <v>BH-600×350×16×36</v>
+        <v>SH-600×300×12×28</v>
       </c>
       <c r="N14" t="str">
         <v/>
@@ -4732,34 +3988,34 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>CSG3</v>
+        <v>SG11</v>
       </c>
       <c r="B15" t="str">
-        <v>CSG3</v>
+        <v>SG11</v>
       </c>
       <c r="C15" t="str">
-        <v>SH</v>
+        <v>BH</v>
       </c>
       <c r="D15">
-        <v>800</v>
+        <v>600</v>
       </c>
       <c r="E15">
-        <v>250</v>
+        <v>350</v>
       </c>
       <c r="F15">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G15">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="H15" t="str">
-        <v>3450</v>
+        <v>6450</v>
       </c>
       <c r="I15" t="str">
-        <v/>
+        <v>Xd3</v>
       </c>
       <c r="J15" t="str">
-        <v/>
+        <v>Xd4</v>
       </c>
       <c r="K15" t="str">
         <v/>
@@ -4768,7 +4024,7 @@
         <v/>
       </c>
       <c r="M15" t="str">
-        <v>SH-800×250×14×22</v>
+        <v>BH-600×350×16×36</v>
       </c>
       <c r="N15" t="str">
         <v/>
@@ -4776,28 +4032,28 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>CSG5</v>
+        <v>CSG3</v>
       </c>
       <c r="B16" t="str">
-        <v>CSG5</v>
+        <v>CSG3</v>
       </c>
       <c r="C16" t="str">
         <v>SH</v>
       </c>
       <c r="D16">
-        <v>600</v>
+        <v>800</v>
       </c>
       <c r="E16">
         <v>250</v>
       </c>
       <c r="F16">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G16">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="H16" t="str">
-        <v>1650</v>
+        <v>3450</v>
       </c>
       <c r="I16" t="str">
         <v/>
@@ -4812,7 +4068,7 @@
         <v/>
       </c>
       <c r="M16" t="str">
-        <v>SH-600×250×12×25</v>
+        <v>SH-800×250×14×22</v>
       </c>
       <c r="N16" t="str">
         <v/>
@@ -4820,10 +4076,10 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>CSG6</v>
+        <v>CSG5</v>
       </c>
       <c r="B17" t="str">
-        <v>CSG6</v>
+        <v>CSG5</v>
       </c>
       <c r="C17" t="str">
         <v>SH</v>
@@ -4832,71 +4088,94 @@
         <v>600</v>
       </c>
       <c r="E17">
+        <v>250</v>
+      </c>
+      <c r="F17">
+        <v>12</v>
+      </c>
+      <c r="G17">
+        <v>25</v>
+      </c>
+      <c r="H17" t="str">
+        <v>1650</v>
+      </c>
+      <c r="I17" t="str">
+        <v/>
+      </c>
+      <c r="J17" t="str">
+        <v/>
+      </c>
+      <c r="K17" t="str">
+        <v/>
+      </c>
+      <c r="L17" t="str">
+        <v/>
+      </c>
+      <c r="M17" t="str">
+        <v>SH-600×250×12×25</v>
+      </c>
+      <c r="N17" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>CSG6</v>
+      </c>
+      <c r="B18" t="str">
+        <v>CSG6</v>
+      </c>
+      <c r="C18" t="str">
+        <v>SH</v>
+      </c>
+      <c r="D18">
+        <v>600</v>
+      </c>
+      <c r="E18">
         <v>300</v>
       </c>
-      <c r="F17">
+      <c r="F18">
         <v>16</v>
       </c>
-      <c r="G17">
+      <c r="G18">
         <v>32</v>
       </c>
-      <c r="H17" t="str">
+      <c r="H18" t="str">
         <v>4100</v>
       </c>
-      <c r="I17" t="str">
-        <v/>
-      </c>
-      <c r="J17" t="str">
-        <v/>
-      </c>
-      <c r="K17" t="str">
-        <v/>
-      </c>
-      <c r="L17" t="str">
-        <v/>
-      </c>
-      <c r="M17" t="str">
+      <c r="I18" t="str">
+        <v/>
+      </c>
+      <c r="J18" t="str">
+        <v/>
+      </c>
+      <c r="K18" t="str">
+        <v/>
+      </c>
+      <c r="L18" t="str">
+        <v/>
+      </c>
+      <c r="M18" t="str">
         <v>SH-600×300×16×32</v>
       </c>
-      <c r="N17" t="str">
+      <c r="N18" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:G1"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:J1"/>
+    <mergeCell ref="K1:K2"/>
+    <mergeCell ref="L1:L2"/>
+    <mergeCell ref="M1:M2"/>
+    <mergeCell ref="N1:N2"/>
+  </mergeCells>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:N17"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>placeholder</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>placeholder</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:N18"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/pdf-to-excel/src/sample-output.xlsx
+++ b/pdf-to-excel/src/sample-output.xlsx
@@ -6,6 +6,7 @@
     <sheet name="Meta" sheetId="1" r:id="rId1"/>
     <sheet name="基礎大梁" sheetId="2" r:id="rId2"/>
     <sheet name="S大梁" sheetId="3" r:id="rId3"/>
+    <sheet name="柱" sheetId="4" r:id="rId4"/>
   </sheets>
 </workbook>
 </file>
@@ -430,7 +431,7 @@
         <v>extracted_at</v>
       </c>
       <c r="B4" t="str">
-        <v>2026-05-20T04:28:52.877Z</v>
+        <v>2026-05-20T04:34:18.220Z</v>
       </c>
     </row>
     <row r="5">
@@ -446,7 +447,7 @@
         <v>detected_categories</v>
       </c>
       <c r="B6" t="str">
-        <v>RC基礎大梁 (20行), S大梁 (16行)</v>
+        <v>RC基礎大梁 (20行), S大梁 (16行), S柱 (6行) ※OCR</v>
       </c>
     </row>
   </sheetData>
@@ -4178,4 +4179,216 @@
     <ignoredError numberStoredAsText="1" sqref="A1:N18"/>
   </ignoredErrors>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:G8"/>
+  <cols>
+    <col min="1" max="1" width="12.83203125" customWidth="1"/>
+    <col min="2" max="2" width="12.83203125" customWidth="1"/>
+    <col min="3" max="3" width="30.83203125" customWidth="1"/>
+    <col min="4" max="4" width="12.83203125" customWidth="1"/>
+    <col min="5" max="5" width="12.83203125" customWidth="1"/>
+    <col min="6" max="6" width="30.83203125" customWidth="1"/>
+    <col min="7" max="7" width="30.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" t="str">
+        <v>TypeName</v>
+      </c>
+      <c r="B1" t="str">
+        <v>符号</v>
+      </c>
+      <c r="C1" t="str">
+        <v>断面</v>
+      </c>
+      <c r="D1" t="str">
+        <v/>
+      </c>
+      <c r="E1" t="str">
+        <v>鋼材グレード</v>
+      </c>
+      <c r="F1" t="str">
+        <v>原文</v>
+      </c>
+      <c r="G1" t="str">
+        <v>備考</v>
+      </c>
+    </row>
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" t="str">
+        <v/>
+      </c>
+      <c r="B2" t="str">
+        <v/>
+      </c>
+      <c r="C2" t="str">
+        <v>断面リスト</v>
+      </c>
+      <c r="D2" t="str">
+        <v>区分数</v>
+      </c>
+      <c r="E2" t="str">
+        <v/>
+      </c>
+      <c r="F2" t="str">
+        <v/>
+      </c>
+      <c r="G2" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>SC1</v>
+      </c>
+      <c r="B3" t="str">
+        <v>SC1</v>
+      </c>
+      <c r="C3" t="str">
+        <v>-700x700x25;-700x700x28;-750x750x28;-800x800x28</v>
+      </c>
+      <c r="D3">
+        <v>4</v>
+      </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
+      <c r="F3" t="str">
+        <v>-700x700x25 / -700x700x28 / -750x750x28 / -800x800x28</v>
+      </c>
+      <c r="G3" t="str">
+        <v>OCR抽出 (低精度) — 元PDFがグリフ難読化のためOCRフォールバック</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>SC2</v>
+      </c>
+      <c r="B4" t="str">
+        <v>SC2</v>
+      </c>
+      <c r="C4" t="str">
+        <v>-700x700x25;-700x700x28;-750x750x28;-800x800x28</v>
+      </c>
+      <c r="D4">
+        <v>4</v>
+      </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4" t="str">
+        <v>-700x700x25 / -700x700x28 / -750x750x28 / -800x800x28</v>
+      </c>
+      <c r="G4" t="str">
+        <v>OCR抽出 (低精度) — 元PDFがグリフ難読化のためOCRフォールバック</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>SC3</v>
+      </c>
+      <c r="B5" t="str">
+        <v>SC3</v>
+      </c>
+      <c r="C5" t="str">
+        <v>-450x450x28</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="E5" t="str">
+        <v/>
+      </c>
+      <c r="F5" t="str">
+        <v>-450x450x28</v>
+      </c>
+      <c r="G5" t="str">
+        <v>OCR抽出 (低精度) — 元PDFがグリフ難読化のためOCRフォールバック</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>SC4</v>
+      </c>
+      <c r="B6" t="str">
+        <v>SC4</v>
+      </c>
+      <c r="C6" t="str">
+        <v>-400x400x22</v>
+      </c>
+      <c r="D6">
+        <v>1</v>
+      </c>
+      <c r="E6" t="str">
+        <v/>
+      </c>
+      <c r="F6" t="str">
+        <v>-400x400x22</v>
+      </c>
+      <c r="G6" t="str">
+        <v>OCR抽出 (低精度) — 元PDFがグリフ難読化のためOCRフォールバック</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>SC5</v>
+      </c>
+      <c r="B7" t="str">
+        <v>SC5</v>
+      </c>
+      <c r="C7" t="str">
+        <v>SH-700x350x16x25;SH-700x350x16x28;SH-700x350x16x36</v>
+      </c>
+      <c r="D7">
+        <v>3</v>
+      </c>
+      <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7" t="str">
+        <v>SH-700x350x16x25 / SH-700x350x16x28 / SH-700x350x16x36</v>
+      </c>
+      <c r="G7" t="str">
+        <v>OCR抽出 (低精度) — 元PDFがグリフ難読化のためOCRフォールバック</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>SC6</v>
+      </c>
+      <c r="B8" t="str">
+        <v>SC6</v>
+      </c>
+      <c r="C8" t="str">
+        <v/>
+      </c>
+      <c r="D8">
+        <v>0</v>
+      </c>
+      <c r="E8" t="str">
+        <v/>
+      </c>
+      <c r="F8" t="str">
+        <v/>
+      </c>
+      <c r="G8" t="str">
+        <v>OCR抽出 (低精度) — 元PDFがグリフ難読化のためOCRフォールバック</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="G1:G2"/>
+  </mergeCells>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:G8"/>
+  </ignoredErrors>
+</worksheet>
 </file>
--- a/pdf-to-excel/src/sample-output.xlsx
+++ b/pdf-to-excel/src/sample-output.xlsx
@@ -5,17 +5,17 @@
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
     <sheet sheetId="1" name="Meta" state="visible" r:id="rId4"/>
-    <sheet sheetId="2" name="基礎大梁" state="visible" r:id="rId5"/>
-    <sheet sheetId="3" name="大梁" state="visible" r:id="rId6"/>
-    <sheet sheetId="4" name="小梁" state="visible" r:id="rId7"/>
-    <sheet sheetId="5" name="柱" state="visible" r:id="rId8"/>
+    <sheet sheetId="2" name="基礎大梁 (RC)" state="visible" r:id="rId5"/>
+    <sheet sheetId="3" name="大梁 (S)" state="visible" r:id="rId6"/>
+    <sheet sheetId="4" name="小梁 (S)" state="visible" r:id="rId7"/>
+    <sheet sheetId="5" name="柱 (S)" state="visible" r:id="rId8"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="990" uniqueCount="231">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="995" uniqueCount="231">
   <si>
     <t>key</t>
   </si>
@@ -38,7 +38,7 @@
     <t>extracted_at</t>
   </si>
   <si>
-    <t>2026-05-20T05:35:13.137Z</t>
+    <t>2026-05-20T06:04:49.286Z</t>
   </si>
   <si>
     <t>extracted_by</t>
@@ -71,22 +71,31 @@
     <t>備考</t>
   </si>
   <si>
-    <t>位置 a</t>
-  </si>
-  <si>
-    <t>位置 b</t>
-  </si>
-  <si>
-    <t>位置 c</t>
-  </si>
-  <si>
-    <t>位置 d</t>
-  </si>
-  <si>
-    <t>位置 e</t>
-  </si>
-  <si>
-    <t>主筋径</t>
+    <t>左端</t>
+  </si>
+  <si>
+    <t>中央</t>
+  </si>
+  <si>
+    <t>右端</t>
+  </si>
+  <si>
+    <t>中間 (d)</t>
+  </si>
+  <si>
+    <t>中間 (e)</t>
+  </si>
+  <si>
+    <t>主筋</t>
+  </si>
+  <si>
+    <t>あばら筋</t>
+  </si>
+  <si>
+    <t>原文</t>
+  </si>
+  <si>
+    <t>径</t>
   </si>
   <si>
     <t>上_1段</t>
@@ -101,19 +110,10 @@
     <t>下_2段</t>
   </si>
   <si>
-    <t>あばら径</t>
-  </si>
-  <si>
-    <t>あばら脚数</t>
-  </si>
-  <si>
-    <t>あばらピッチ</t>
-  </si>
-  <si>
-    <t>端あき</t>
-  </si>
-  <si>
-    <t>原文</t>
+    <t>脚数</t>
+  </si>
+  <si>
+    <t>ピッチ</t>
   </si>
   <si>
     <t>FG1</t>
@@ -131,21 +131,21 @@
     <t>上=6 下=6+2</t>
   </si>
   <si>
+    <t>上=6+2 下=6</t>
+  </si>
+  <si>
     <t>上=6 下=6+3</t>
   </si>
   <si>
-    <t>上=6+2 下=6</t>
-  </si>
-  <si>
     <t>FG2</t>
   </si>
   <si>
+    <t>上=6+3 下=6</t>
+  </si>
+  <si>
     <t>上=6 下=6+5</t>
   </si>
   <si>
-    <t>上=6+3 下=6</t>
-  </si>
-  <si>
     <t>FG3</t>
   </si>
   <si>
@@ -209,24 +209,24 @@
     <t>上=7+3 下=7+3</t>
   </si>
   <si>
+    <t>上=7+3 下=7</t>
+  </si>
+  <si>
     <t>上=7+1 下=7+4</t>
   </si>
   <si>
-    <t>上=7+3 下=7</t>
-  </si>
-  <si>
     <t>FG12</t>
   </si>
   <si>
     <t>FG13</t>
   </si>
   <si>
+    <t>上=7+7 下=7</t>
+  </si>
+  <si>
     <t>上=7+7 下=7+3</t>
   </si>
   <si>
-    <t>上=7+7 下=7</t>
-  </si>
-  <si>
     <t>FG14</t>
   </si>
   <si>
@@ -401,7 +401,7 @@
     <t>構造</t>
   </si>
   <si>
-    <t>SB19</t>
+    <t>sb19</t>
   </si>
   <si>
     <t>S</t>
@@ -416,253 +416,253 @@
     <t>OCR抽出</t>
   </si>
   <si>
-    <t>SB20</t>
+    <t>sb20</t>
   </si>
   <si>
     <t>H-200x100x5.5x8</t>
   </si>
   <si>
-    <t>SB24</t>
+    <t>sb24</t>
   </si>
   <si>
     <t>H-248x124x5x8</t>
   </si>
   <si>
-    <t>CSB24</t>
-  </si>
-  <si>
-    <t>SB25</t>
+    <t>csb24</t>
+  </si>
+  <si>
+    <t>sb25</t>
   </si>
   <si>
     <t>H-250x125x6x9</t>
   </si>
   <si>
-    <t>SB29</t>
+    <t>sb29</t>
   </si>
   <si>
     <t>H-298x149x5.5x8</t>
   </si>
   <si>
-    <t>SB30</t>
+    <t>sb30</t>
   </si>
   <si>
     <t>H-300x150x6.5x9</t>
   </si>
   <si>
-    <t>SB34</t>
+    <t>sb34</t>
   </si>
   <si>
     <t>H-346x174x6x9</t>
   </si>
   <si>
-    <t>CSB34</t>
-  </si>
-  <si>
-    <t>SB35</t>
+    <t>csb34</t>
+  </si>
+  <si>
+    <t>sb35</t>
   </si>
   <si>
     <t>H-350x175x7x11</t>
   </si>
   <si>
-    <t>SB39</t>
+    <t>sb39</t>
   </si>
   <si>
     <t>H-396x199x7x11</t>
   </si>
   <si>
-    <t>SB40</t>
+    <t>sb40</t>
   </si>
   <si>
     <t>H-400x200x8x13</t>
   </si>
   <si>
-    <t>SB44</t>
+    <t>sb44</t>
   </si>
   <si>
     <t>H-446x199x8x12</t>
   </si>
   <si>
-    <t>CSB44</t>
-  </si>
-  <si>
-    <t>SB45</t>
+    <t>csb44</t>
+  </si>
+  <si>
+    <t>sb45</t>
   </si>
   <si>
     <t>H-450X200X9x14</t>
   </si>
   <si>
-    <t>SB49</t>
+    <t>sb49</t>
   </si>
   <si>
     <t>H-496X199X9x14</t>
   </si>
   <si>
-    <t>SB50</t>
+    <t>sb50</t>
   </si>
   <si>
     <t>H-500x200x10x16</t>
   </si>
   <si>
-    <t>SB59</t>
+    <t>sb59</t>
   </si>
   <si>
     <t>H-596x199x10x15</t>
   </si>
   <si>
-    <t>SB60</t>
+    <t>sb60</t>
   </si>
   <si>
     <t>H-600x200x11x17</t>
   </si>
   <si>
-    <t>CSB60</t>
-  </si>
-  <si>
-    <t>SB14M</t>
+    <t>csb60</t>
+  </si>
+  <si>
+    <t>sb14m</t>
   </si>
   <si>
     <t>H-148x100x6x9</t>
   </si>
   <si>
-    <t>SB19M</t>
+    <t>sb19m</t>
   </si>
   <si>
     <t>H-194x150x6x9</t>
   </si>
   <si>
-    <t>SB24M</t>
+    <t>sb24m</t>
   </si>
   <si>
     <t>H-244x175x7x11</t>
   </si>
   <si>
-    <t>SB29M</t>
-  </si>
-  <si>
-    <t>SB34M</t>
+    <t>sb29m</t>
+  </si>
+  <si>
+    <t>sb34m</t>
   </si>
   <si>
     <t>H-340X250X9x14</t>
   </si>
   <si>
-    <t>SB39M</t>
+    <t>sb39m</t>
   </si>
   <si>
     <t>H-390x300x10x16</t>
   </si>
   <si>
-    <t>SB44M</t>
+    <t>sb44m</t>
   </si>
   <si>
     <t>H-440x300x11x18</t>
   </si>
   <si>
-    <t>SB42M</t>
+    <t>sb42m</t>
   </si>
   <si>
     <t>H-482x300x11x15</t>
   </si>
   <si>
-    <t>SB48M</t>
+    <t>sb48m</t>
   </si>
   <si>
     <t>H-488x300x11x18</t>
   </si>
   <si>
-    <t>SB52M</t>
+    <t>sb52m</t>
   </si>
   <si>
     <t>H-582x300x12x17</t>
   </si>
   <si>
-    <t>CSB52M</t>
-  </si>
-  <si>
-    <t>SB58M</t>
+    <t>csb52m</t>
+  </si>
+  <si>
+    <t>sb58m</t>
   </si>
   <si>
     <t>H-588x300x12x20</t>
   </si>
   <si>
-    <t>SB69M</t>
-  </si>
-  <si>
-    <t>SB70M</t>
+    <t>sb69m</t>
+  </si>
+  <si>
+    <t>sb70m</t>
   </si>
   <si>
     <t>H-700x300x13x24</t>
   </si>
   <si>
-    <t>SB79M</t>
+    <t>sb79m</t>
   </si>
   <si>
     <t>H-792x300x14x22</t>
   </si>
   <si>
-    <t>SB80M</t>
+    <t>sb80m</t>
   </si>
   <si>
     <t>H-800x300x14x26</t>
   </si>
   <si>
-    <t>SB90M</t>
+    <t>sb90m</t>
   </si>
   <si>
     <t>H-900x300x16x28</t>
   </si>
   <si>
-    <t>SB24MS</t>
-  </si>
-  <si>
-    <t>SB10W</t>
-  </si>
-  <si>
-    <t>SB12W</t>
+    <t>sb24ms</t>
+  </si>
+  <si>
+    <t>sb10w</t>
+  </si>
+  <si>
+    <t>sb12w</t>
   </si>
   <si>
     <t>H-125x125x6.5x9</t>
   </si>
   <si>
-    <t>SB15W</t>
+    <t>sb15w</t>
   </si>
   <si>
     <t>H-150x150x7x10</t>
   </si>
   <si>
-    <t>SB17W</t>
+    <t>sb17w</t>
   </si>
   <si>
     <t>H-175x175x7.5x11</t>
   </si>
   <si>
-    <t>SB20W</t>
-  </si>
-  <si>
-    <t>SB25W</t>
-  </si>
-  <si>
-    <t>CSB25W</t>
-  </si>
-  <si>
-    <t>SB30W</t>
+    <t>sb20w</t>
+  </si>
+  <si>
+    <t>sb25w</t>
+  </si>
+  <si>
+    <t>csb25w</t>
+  </si>
+  <si>
+    <t>sb30w</t>
   </si>
   <si>
     <t>H-300x300x10x15</t>
   </si>
   <si>
-    <t>SB35W</t>
+    <t>sb35w</t>
   </si>
   <si>
     <t>H-350x350x12x19</t>
   </si>
   <si>
-    <t>SB40W</t>
+    <t>sb40w</t>
   </si>
   <si>
     <t>H-400x400x13x21</t>
   </si>
   <si>
-    <t>SB80H</t>
+    <t>sb80h</t>
   </si>
   <si>
     <t>SN490B</t>
@@ -1193,41 +1193,26 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:BD22"/>
+  <dimension ref="A1:AY23"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
-    <col min="2" max="6" width="6" customWidth="1"/>
-    <col min="7" max="11" width="8" customWidth="1"/>
-    <col min="12" max="12" width="10" customWidth="1"/>
-    <col min="13" max="13" width="12" customWidth="1"/>
-    <col min="14" max="14" width="14" customWidth="1"/>
-    <col min="15" max="15" width="8" customWidth="1"/>
-    <col min="16" max="16" width="25" customWidth="1"/>
-    <col min="17" max="21" width="8" customWidth="1"/>
-    <col min="22" max="22" width="10" customWidth="1"/>
-    <col min="23" max="23" width="12" customWidth="1"/>
-    <col min="24" max="24" width="14" customWidth="1"/>
-    <col min="25" max="25" width="8" customWidth="1"/>
-    <col min="26" max="26" width="25" customWidth="1"/>
-    <col min="27" max="31" width="8" customWidth="1"/>
-    <col min="32" max="32" width="10" customWidth="1"/>
-    <col min="33" max="33" width="12" customWidth="1"/>
-    <col min="34" max="34" width="14" customWidth="1"/>
-    <col min="35" max="35" width="8" customWidth="1"/>
-    <col min="36" max="36" width="16" customWidth="1"/>
-    <col min="37" max="41" width="8" customWidth="1"/>
-    <col min="42" max="42" width="10" customWidth="1"/>
-    <col min="43" max="43" width="12" customWidth="1"/>
-    <col min="44" max="44" width="14" customWidth="1"/>
-    <col min="45" max="51" width="8" customWidth="1"/>
-    <col min="52" max="52" width="10" customWidth="1"/>
-    <col min="53" max="53" width="12" customWidth="1"/>
-    <col min="54" max="54" width="14" customWidth="1"/>
-    <col min="55" max="56" width="8" customWidth="1"/>
+    <col min="2" max="7" width="6" customWidth="1"/>
+    <col min="8" max="11" width="8" customWidth="1"/>
+    <col min="12" max="14" width="10" customWidth="1"/>
+    <col min="15" max="15" width="25" customWidth="1"/>
+    <col min="16" max="16" width="6" customWidth="1"/>
+    <col min="17" max="20" width="8" customWidth="1"/>
+    <col min="21" max="23" width="10" customWidth="1"/>
+    <col min="24" max="24" width="16" customWidth="1"/>
+    <col min="25" max="25" width="6" customWidth="1"/>
+    <col min="26" max="29" width="8" customWidth="1"/>
+    <col min="30" max="32" width="10" customWidth="1"/>
+    <col min="33" max="33" width="25" customWidth="1"/>
+    <col min="34" max="51" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="1" ht="22" customHeight="1" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>12</v>
       </c>
@@ -1257,10 +1242,10 @@
       <c r="M1" s="1"/>
       <c r="N1" s="1"/>
       <c r="O1" s="1"/>
-      <c r="P1" s="1"/>
-      <c r="Q1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>19</v>
       </c>
+      <c r="Q1" s="1"/>
       <c r="R1" s="1"/>
       <c r="S1" s="1"/>
       <c r="T1" s="1"/>
@@ -1268,46 +1253,41 @@
       <c r="V1" s="1"/>
       <c r="W1" s="1"/>
       <c r="X1" s="1"/>
-      <c r="Y1" s="1"/>
+      <c r="Y1" s="1" t="s">
+        <v>20</v>
+      </c>
       <c r="Z1" s="1"/>
-      <c r="AA1" s="1" t="s">
-        <v>20</v>
-      </c>
+      <c r="AA1" s="1"/>
       <c r="AB1" s="1"/>
       <c r="AC1" s="1"/>
       <c r="AD1" s="1"/>
       <c r="AE1" s="1"/>
       <c r="AF1" s="1"/>
       <c r="AG1" s="1"/>
-      <c r="AH1" s="1"/>
+      <c r="AH1" s="1" t="s">
+        <v>21</v>
+      </c>
       <c r="AI1" s="1"/>
       <c r="AJ1" s="1"/>
-      <c r="AK1" s="1" t="s">
-        <v>21</v>
-      </c>
+      <c r="AK1" s="1"/>
       <c r="AL1" s="1"/>
       <c r="AM1" s="1"/>
       <c r="AN1" s="1"/>
       <c r="AO1" s="1"/>
       <c r="AP1" s="1"/>
-      <c r="AQ1" s="1"/>
+      <c r="AQ1" s="1" t="s">
+        <v>22</v>
+      </c>
       <c r="AR1" s="1"/>
       <c r="AS1" s="1"/>
       <c r="AT1" s="1"/>
-      <c r="AU1" s="1" t="s">
-        <v>22</v>
-      </c>
+      <c r="AU1" s="1"/>
       <c r="AV1" s="1"/>
       <c r="AW1" s="1"/>
       <c r="AX1" s="1"/>
       <c r="AY1" s="1"/>
-      <c r="AZ1" s="1"/>
-      <c r="BA1" s="1"/>
-      <c r="BB1" s="1"/>
-      <c r="BC1" s="1"/>
-      <c r="BD1" s="1"/>
-    </row>
-    <row r="2" ht="22" customHeight="1" spans="1:56" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" ht="22" customHeight="1" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1317,308 +1297,218 @@
       <c r="G2" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="M2" s="1"/>
+      <c r="N2" s="1"/>
+      <c r="O2" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="J2" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="N2" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="O2" s="1" t="s">
-        <v>31</v>
-      </c>
       <c r="P2" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q2" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="R2" s="1" t="s">
+      <c r="Q2" s="1"/>
+      <c r="R2" s="1"/>
+      <c r="S2" s="1"/>
+      <c r="T2" s="1"/>
+      <c r="U2" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="S2" s="1" t="s">
+      <c r="V2" s="1"/>
+      <c r="W2" s="1"/>
+      <c r="X2" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="T2" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="U2" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="V2" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="W2" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="X2" s="1" t="s">
-        <v>30</v>
-      </c>
       <c r="Y2" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="Z2" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="AA2" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="AB2" s="1" t="s">
+      <c r="Z2" s="1"/>
+      <c r="AA2" s="1"/>
+      <c r="AB2" s="1"/>
+      <c r="AC2" s="1"/>
+      <c r="AD2" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="AC2" s="1" t="s">
+      <c r="AE2" s="1"/>
+      <c r="AF2" s="1"/>
+      <c r="AG2" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="AD2" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AE2" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="AF2" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="AG2" s="1" t="s">
-        <v>29</v>
-      </c>
       <c r="AH2" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="AI2" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="AJ2" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="AK2" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="AL2" s="1" t="s">
+      <c r="AI2" s="1"/>
+      <c r="AJ2" s="1"/>
+      <c r="AK2" s="1"/>
+      <c r="AL2" s="1"/>
+      <c r="AM2" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="AM2" s="1" t="s">
+      <c r="AN2" s="1"/>
+      <c r="AO2" s="1"/>
+      <c r="AP2" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="AN2" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AO2" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="AP2" s="1" t="s">
-        <v>28</v>
-      </c>
       <c r="AQ2" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="AR2" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="AS2" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="AT2" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="AU2" s="1" t="s">
         <v>23</v>
       </c>
+      <c r="AR2" s="1"/>
+      <c r="AS2" s="1"/>
+      <c r="AT2" s="1"/>
+      <c r="AU2" s="1"/>
       <c r="AV2" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="AW2" s="1" t="s">
+      <c r="AW2" s="1"/>
+      <c r="AX2" s="1"/>
+      <c r="AY2" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="AX2" s="1" t="s">
+    </row>
+    <row r="3" ht="22" customHeight="1" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="A3" s="1"/>
+      <c r="B3" s="1"/>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AY2" s="1" t="s">
+      <c r="H3" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="AZ2" s="1" t="s">
+      <c r="I3" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="BA2" s="1" t="s">
+      <c r="J3" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="BB2" s="1" t="s">
+      <c r="K3" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="BC2" s="1" t="s">
+      <c r="L3" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M3" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="BD2" s="1" t="s">
+      <c r="N3" s="1" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="3" spans="1:56" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
+      <c r="O3" s="1"/>
+      <c r="P3" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q3" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="R3" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="S3" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="T3" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="U3" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="V3" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="W3" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="X3" s="1"/>
+      <c r="Y3" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Z3" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA3" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="AB3" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AC3" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="AD3" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AE3" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="AF3" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="AG3" s="1"/>
+      <c r="AH3" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AI3" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AJ3" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="AK3" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AL3" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="AM3" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AN3" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="AO3" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="AP3" s="1"/>
+      <c r="AQ3" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AR3" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AS3" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="AT3" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AU3" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="AV3" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AW3" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="AX3" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="AY3" s="1"/>
+    </row>
+    <row r="4" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B4" s="2" t="s">
         <v>33</v>
-      </c>
-      <c r="C3" s="2">
-        <v>640</v>
-      </c>
-      <c r="D3" s="2">
-        <v>1500</v>
-      </c>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="H3" s="2">
-        <v>6</v>
-      </c>
-      <c r="I3" s="2">
-        <v>0</v>
-      </c>
-      <c r="J3" s="2">
-        <v>6</v>
-      </c>
-      <c r="K3" s="2">
-        <v>2</v>
-      </c>
-      <c r="L3" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="M3" s="2">
-        <v>2</v>
-      </c>
-      <c r="N3" s="2">
-        <v>150</v>
-      </c>
-      <c r="O3" s="2">
-        <v>2800</v>
-      </c>
-      <c r="P3" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="Q3" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="R3" s="2">
-        <v>6</v>
-      </c>
-      <c r="S3" s="2">
-        <v>0</v>
-      </c>
-      <c r="T3" s="2">
-        <v>6</v>
-      </c>
-      <c r="U3" s="2">
-        <v>3</v>
-      </c>
-      <c r="V3" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="W3" s="2">
-        <v>2</v>
-      </c>
-      <c r="X3" s="2">
-        <v>150</v>
-      </c>
-      <c r="Y3" s="2">
-        <v>2900</v>
-      </c>
-      <c r="Z3" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="AA3" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="AB3" s="2">
-        <v>6</v>
-      </c>
-      <c r="AC3" s="2">
-        <v>2</v>
-      </c>
-      <c r="AD3" s="2">
-        <v>6</v>
-      </c>
-      <c r="AE3" s="2">
-        <v>0</v>
-      </c>
-      <c r="AF3" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="AG3" s="2">
-        <v>2</v>
-      </c>
-      <c r="AH3" s="2">
-        <v>150</v>
-      </c>
-      <c r="AI3" s="2">
-        <v>3800</v>
-      </c>
-      <c r="AJ3" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="AK3" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="AL3" s="2"/>
-      <c r="AM3" s="2"/>
-      <c r="AN3" s="2"/>
-      <c r="AO3" s="2"/>
-      <c r="AP3" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="AQ3" s="2">
-        <v>2</v>
-      </c>
-      <c r="AR3" s="2">
-        <v>150</v>
-      </c>
-      <c r="AS3" s="2"/>
-      <c r="AT3" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="AU3" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="AV3" s="2"/>
-      <c r="AW3" s="2"/>
-      <c r="AX3" s="2"/>
-      <c r="AY3" s="2"/>
-      <c r="AZ3" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="BA3" s="2">
-        <v>2</v>
-      </c>
-      <c r="BB3" s="2">
-        <v>150</v>
-      </c>
-      <c r="BC3" s="2"/>
-      <c r="BD3" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="4" spans="1:56" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>40</v>
       </c>
       <c r="C4" s="2">
         <v>640</v>
@@ -1643,7 +1533,7 @@
         <v>6</v>
       </c>
       <c r="K4" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L4" s="2" t="s">
         <v>36</v>
@@ -1654,44 +1544,44 @@
       <c r="N4" s="2">
         <v>150</v>
       </c>
-      <c r="O4" s="2">
-        <v>2600</v>
+      <c r="O4" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="P4" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q4" s="2">
+        <v>6</v>
+      </c>
+      <c r="R4" s="2">
+        <v>2</v>
+      </c>
+      <c r="S4" s="2">
+        <v>6</v>
+      </c>
+      <c r="T4" s="2">
+        <v>0</v>
+      </c>
+      <c r="U4" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="V4" s="2">
+        <v>2</v>
+      </c>
+      <c r="W4" s="2">
+        <v>150</v>
+      </c>
+      <c r="X4" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="Q4" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="R4" s="2">
+      <c r="Y4" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="Z4" s="2">
         <v>6</v>
       </c>
-      <c r="S4" s="2">
+      <c r="AA4" s="2">
         <v>0</v>
-      </c>
-      <c r="T4" s="2">
-        <v>6</v>
-      </c>
-      <c r="U4" s="2">
-        <v>5</v>
-      </c>
-      <c r="V4" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="W4" s="2">
-        <v>2</v>
-      </c>
-      <c r="X4" s="2">
-        <v>150</v>
-      </c>
-      <c r="Y4" s="2">
-        <v>3000</v>
-      </c>
-      <c r="Z4" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="AA4" s="2" t="s">
-        <v>35</v>
       </c>
       <c r="AB4" s="2">
         <v>6</v>
@@ -1699,77 +1589,66 @@
       <c r="AC4" s="2">
         <v>3</v>
       </c>
-      <c r="AD4" s="2">
-        <v>6</v>
+      <c r="AD4" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="AE4" s="2">
-        <v>0</v>
-      </c>
-      <c r="AF4" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="AG4" s="2">
         <v>2</v>
       </c>
-      <c r="AH4" s="2">
+      <c r="AF4" s="2">
         <v>150</v>
       </c>
-      <c r="AI4" s="2">
-        <v>3800</v>
-      </c>
-      <c r="AJ4" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="AK4" s="2" t="s">
-        <v>35</v>
-      </c>
+      <c r="AG4" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="AH4" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="AI4" s="2"/>
+      <c r="AJ4" s="2"/>
+      <c r="AK4" s="2"/>
       <c r="AL4" s="2"/>
-      <c r="AM4" s="2"/>
-      <c r="AN4" s="2"/>
-      <c r="AO4" s="2"/>
+      <c r="AM4" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="AN4" s="2">
+        <v>2</v>
+      </c>
+      <c r="AO4" s="2">
+        <v>150</v>
+      </c>
       <c r="AP4" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="AQ4" s="2">
+        <v>34</v>
+      </c>
+      <c r="AQ4" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="AR4" s="2"/>
+      <c r="AS4" s="2"/>
+      <c r="AT4" s="2"/>
+      <c r="AU4" s="2"/>
+      <c r="AV4" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="AW4" s="2">
         <v>2</v>
       </c>
-      <c r="AR4" s="2">
+      <c r="AX4" s="2">
         <v>150</v>
       </c>
-      <c r="AS4" s="2"/>
-      <c r="AT4" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="AU4" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="AV4" s="2"/>
-      <c r="AW4" s="2"/>
-      <c r="AX4" s="2"/>
-      <c r="AY4" s="2"/>
-      <c r="AZ4" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="BA4" s="2">
-        <v>2</v>
-      </c>
-      <c r="BB4" s="2">
-        <v>150</v>
-      </c>
-      <c r="BC4" s="2"/>
-      <c r="BD4" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="5" spans="1:56" x14ac:dyDescent="0.25">
+      <c r="AY4" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="5" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="C5" s="2">
-        <v>800</v>
+        <v>640</v>
       </c>
       <c r="D5" s="2">
         <v>1500</v>
@@ -1782,13 +1661,13 @@
         <v>35</v>
       </c>
       <c r="H5" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I5" s="2">
         <v>0</v>
       </c>
       <c r="J5" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="K5" s="2">
         <v>3</v>
@@ -1797,125 +1676,116 @@
         <v>36</v>
       </c>
       <c r="M5" s="2">
+        <v>2</v>
+      </c>
+      <c r="N5" s="2">
+        <v>150</v>
+      </c>
+      <c r="O5" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="P5" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q5" s="2">
+        <v>6</v>
+      </c>
+      <c r="R5" s="2">
         <v>3</v>
       </c>
-      <c r="N5" s="2">
-        <v>200</v>
-      </c>
-      <c r="O5" s="2">
-        <v>2600</v>
-      </c>
-      <c r="P5" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="Q5" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="R5" s="2">
-        <v>8</v>
-      </c>
       <c r="S5" s="2">
+        <v>6</v>
+      </c>
+      <c r="T5" s="2">
         <v>0</v>
       </c>
-      <c r="T5" s="2">
-        <v>8</v>
-      </c>
-      <c r="U5" s="2">
-        <v>3</v>
-      </c>
-      <c r="V5" s="2" t="s">
-        <v>36</v>
+      <c r="U5" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="V5" s="2">
+        <v>2</v>
       </c>
       <c r="W5" s="2">
-        <v>3</v>
-      </c>
-      <c r="X5" s="2">
-        <v>200</v>
-      </c>
-      <c r="Y5" s="2">
-        <v>2600</v>
-      </c>
-      <c r="Z5" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="AA5" s="2" t="s">
-        <v>35</v>
+        <v>150</v>
+      </c>
+      <c r="X5" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="Y5" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="Z5" s="2">
+        <v>6</v>
+      </c>
+      <c r="AA5" s="2">
+        <v>0</v>
       </c>
       <c r="AB5" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AC5" s="2">
-        <v>0</v>
-      </c>
-      <c r="AD5" s="2">
-        <v>8</v>
+        <v>5</v>
+      </c>
+      <c r="AD5" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="AE5" s="2">
-        <v>0</v>
-      </c>
-      <c r="AF5" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="AG5" s="2">
-        <v>3</v>
-      </c>
-      <c r="AH5" s="2">
-        <v>200</v>
+        <v>2</v>
+      </c>
+      <c r="AF5" s="2">
+        <v>150</v>
+      </c>
+      <c r="AG5" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="AH5" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="AI5" s="2"/>
-      <c r="AJ5" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="AK5" s="2" t="s">
-        <v>35</v>
-      </c>
+      <c r="AJ5" s="2"/>
+      <c r="AK5" s="2"/>
       <c r="AL5" s="2"/>
-      <c r="AM5" s="2"/>
-      <c r="AN5" s="2"/>
-      <c r="AO5" s="2"/>
+      <c r="AM5" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="AN5" s="2">
+        <v>2</v>
+      </c>
+      <c r="AO5" s="2">
+        <v>150</v>
+      </c>
       <c r="AP5" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="AQ5" s="2">
-        <v>3</v>
-      </c>
-      <c r="AR5" s="2">
-        <v>200</v>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="AQ5" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="AR5" s="2"/>
       <c r="AS5" s="2"/>
-      <c r="AT5" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="AU5" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="AV5" s="2"/>
-      <c r="AW5" s="2"/>
-      <c r="AX5" s="2"/>
-      <c r="AY5" s="2"/>
-      <c r="AZ5" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="BA5" s="2">
-        <v>3</v>
-      </c>
-      <c r="BB5" s="2">
-        <v>200</v>
-      </c>
-      <c r="BC5" s="2"/>
-      <c r="BD5" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="6" spans="1:56" x14ac:dyDescent="0.25">
+      <c r="AT5" s="2"/>
+      <c r="AU5" s="2"/>
+      <c r="AV5" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="AW5" s="2">
+        <v>2</v>
+      </c>
+      <c r="AX5" s="2">
+        <v>150</v>
+      </c>
+      <c r="AY5" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="6" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C6" s="2">
-        <v>640</v>
+        <v>800</v>
       </c>
       <c r="D6" s="2">
         <v>1500</v>
@@ -1928,139 +1798,128 @@
         <v>35</v>
       </c>
       <c r="H6" s="2">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I6" s="2">
         <v>0</v>
       </c>
       <c r="J6" s="2">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K6" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L6" s="2" t="s">
         <v>36</v>
       </c>
       <c r="M6" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N6" s="2">
-        <v>150</v>
-      </c>
-      <c r="O6" s="2">
-        <v>3100</v>
+        <v>200</v>
+      </c>
+      <c r="O6" s="2" t="s">
+        <v>44</v>
       </c>
       <c r="P6" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="Q6" s="2" t="s">
-        <v>35</v>
+        <v>35</v>
+      </c>
+      <c r="Q6" s="2">
+        <v>8</v>
       </c>
       <c r="R6" s="2">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="S6" s="2">
+        <v>8</v>
+      </c>
+      <c r="T6" s="2">
         <v>0</v>
       </c>
-      <c r="T6" s="2">
-        <v>6</v>
-      </c>
-      <c r="U6" s="2">
+      <c r="U6" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="V6" s="2">
         <v>3</v>
       </c>
-      <c r="V6" s="2" t="s">
-        <v>36</v>
-      </c>
       <c r="W6" s="2">
-        <v>2</v>
-      </c>
-      <c r="X6" s="2">
-        <v>150</v>
-      </c>
-      <c r="Y6" s="2">
-        <v>3100</v>
-      </c>
-      <c r="Z6" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="AA6" s="2" t="s">
-        <v>35</v>
+        <v>200</v>
+      </c>
+      <c r="X6" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y6" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="Z6" s="2">
+        <v>8</v>
+      </c>
+      <c r="AA6" s="2">
+        <v>0</v>
       </c>
       <c r="AB6" s="2">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AC6" s="2">
-        <v>1</v>
-      </c>
-      <c r="AD6" s="2">
-        <v>6</v>
+        <v>3</v>
+      </c>
+      <c r="AD6" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="AE6" s="2">
-        <v>0</v>
-      </c>
-      <c r="AF6" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="AG6" s="2">
-        <v>2</v>
-      </c>
-      <c r="AH6" s="2">
-        <v>150</v>
-      </c>
-      <c r="AI6" s="2">
-        <v>4400</v>
-      </c>
-      <c r="AJ6" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="AK6" s="2" t="s">
-        <v>35</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="AF6" s="2">
+        <v>200</v>
+      </c>
+      <c r="AG6" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="AH6" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="AI6" s="2"/>
+      <c r="AJ6" s="2"/>
+      <c r="AK6" s="2"/>
       <c r="AL6" s="2"/>
-      <c r="AM6" s="2"/>
-      <c r="AN6" s="2"/>
-      <c r="AO6" s="2"/>
+      <c r="AM6" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="AN6" s="2">
+        <v>3</v>
+      </c>
+      <c r="AO6" s="2">
+        <v>200</v>
+      </c>
       <c r="AP6" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="AQ6" s="2">
-        <v>2</v>
-      </c>
-      <c r="AR6" s="2">
-        <v>150</v>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="AQ6" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="AR6" s="2"/>
       <c r="AS6" s="2"/>
-      <c r="AT6" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="AU6" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="AV6" s="2"/>
-      <c r="AW6" s="2"/>
-      <c r="AX6" s="2"/>
-      <c r="AY6" s="2"/>
-      <c r="AZ6" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="BA6" s="2">
-        <v>2</v>
-      </c>
-      <c r="BB6" s="2">
-        <v>150</v>
-      </c>
-      <c r="BC6" s="2"/>
-      <c r="BD6" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="7" spans="1:56" x14ac:dyDescent="0.25">
+      <c r="AT6" s="2"/>
+      <c r="AU6" s="2"/>
+      <c r="AV6" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="AW6" s="2">
+        <v>3</v>
+      </c>
+      <c r="AX6" s="2">
+        <v>200</v>
+      </c>
+      <c r="AY6" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="7" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C7" s="2">
         <v>640</v>
@@ -2085,7 +1944,7 @@
         <v>6</v>
       </c>
       <c r="K7" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L7" s="2" t="s">
         <v>36</v>
@@ -2096,117 +1955,108 @@
       <c r="N7" s="2">
         <v>150</v>
       </c>
-      <c r="O7" s="2">
-        <v>2600</v>
+      <c r="O7" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="P7" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q7" s="2" t="s">
-        <v>35</v>
+        <v>35</v>
+      </c>
+      <c r="Q7" s="2">
+        <v>6</v>
       </c>
       <c r="R7" s="2">
+        <v>1</v>
+      </c>
+      <c r="S7" s="2">
         <v>6</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>0</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="V7" s="2">
+        <v>2</v>
+      </c>
+      <c r="W7" s="2">
+        <v>150</v>
+      </c>
+      <c r="X7" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="Y7" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="Z7" s="2">
         <v>6</v>
       </c>
-      <c r="U7" s="2">
-        <v>3</v>
-      </c>
-      <c r="V7" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="W7" s="2">
-        <v>2</v>
-      </c>
-      <c r="X7" s="2">
-        <v>150</v>
-      </c>
-      <c r="Y7" s="2">
-        <v>2600</v>
-      </c>
-      <c r="Z7" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="AA7" s="2" t="s">
-        <v>35</v>
+      <c r="AA7" s="2">
+        <v>0</v>
       </c>
       <c r="AB7" s="2">
         <v>6</v>
       </c>
       <c r="AC7" s="2">
-        <v>0</v>
-      </c>
-      <c r="AD7" s="2">
-        <v>6</v>
+        <v>3</v>
+      </c>
+      <c r="AD7" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="AE7" s="2">
-        <v>0</v>
-      </c>
-      <c r="AF7" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="AG7" s="2">
         <v>2</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AF7" s="2">
         <v>150</v>
       </c>
+      <c r="AG7" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="AH7" s="2" t="s">
+        <v>35</v>
+      </c>
       <c r="AI7" s="2"/>
-      <c r="AJ7" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="AK7" s="2" t="s">
-        <v>35</v>
-      </c>
+      <c r="AJ7" s="2"/>
+      <c r="AK7" s="2"/>
       <c r="AL7" s="2"/>
-      <c r="AM7" s="2"/>
-      <c r="AN7" s="2"/>
-      <c r="AO7" s="2"/>
+      <c r="AM7" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="AN7" s="2">
+        <v>2</v>
+      </c>
+      <c r="AO7" s="2">
+        <v>150</v>
+      </c>
       <c r="AP7" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="AQ7" s="2">
+        <v>34</v>
+      </c>
+      <c r="AQ7" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="AR7" s="2"/>
+      <c r="AS7" s="2"/>
+      <c r="AT7" s="2"/>
+      <c r="AU7" s="2"/>
+      <c r="AV7" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="AW7" s="2">
         <v>2</v>
       </c>
-      <c r="AR7" s="2">
+      <c r="AX7" s="2">
         <v>150</v>
       </c>
-      <c r="AS7" s="2"/>
-      <c r="AT7" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="AU7" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="AV7" s="2"/>
-      <c r="AW7" s="2"/>
-      <c r="AX7" s="2"/>
-      <c r="AY7" s="2"/>
-      <c r="AZ7" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="BA7" s="2">
-        <v>2</v>
-      </c>
-      <c r="BB7" s="2">
-        <v>150</v>
-      </c>
-      <c r="BC7" s="2"/>
-      <c r="BD7" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="8" spans="1:56" x14ac:dyDescent="0.25">
+      <c r="AY7" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="8" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C8" s="2">
         <v>640</v>
@@ -2242,117 +2092,108 @@
       <c r="N8" s="2">
         <v>150</v>
       </c>
-      <c r="O8" s="2">
-        <v>2700</v>
+      <c r="O8" s="2" t="s">
+        <v>39</v>
       </c>
       <c r="P8" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q8" s="2" t="s">
-        <v>35</v>
+        <v>35</v>
+      </c>
+      <c r="Q8" s="2">
+        <v>6</v>
       </c>
       <c r="R8" s="2">
+        <v>0</v>
+      </c>
+      <c r="S8" s="2">
         <v>6</v>
       </c>
-      <c r="S8" s="2">
+      <c r="T8" s="2">
+        <v>0</v>
+      </c>
+      <c r="U8" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="V8" s="2">
         <v>2</v>
       </c>
-      <c r="T8" s="2">
+      <c r="W8" s="2">
+        <v>150</v>
+      </c>
+      <c r="X8" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="Y8" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="Z8" s="2">
         <v>6</v>
       </c>
-      <c r="U8" s="2">
-        <v>2</v>
-      </c>
-      <c r="V8" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="W8" s="2">
-        <v>2</v>
-      </c>
-      <c r="X8" s="2">
-        <v>150</v>
-      </c>
-      <c r="Y8" s="2">
-        <v>2850</v>
-      </c>
-      <c r="Z8" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="AA8" s="2" t="s">
-        <v>35</v>
+      <c r="AA8" s="2">
+        <v>0</v>
       </c>
       <c r="AB8" s="2">
         <v>6</v>
       </c>
       <c r="AC8" s="2">
+        <v>3</v>
+      </c>
+      <c r="AD8" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="AE8" s="2">
         <v>2</v>
       </c>
-      <c r="AD8" s="2">
-        <v>6</v>
-      </c>
-      <c r="AE8" s="2">
-        <v>0</v>
-      </c>
-      <c r="AF8" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="AG8" s="2">
+      <c r="AF8" s="2">
+        <v>150</v>
+      </c>
+      <c r="AG8" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="AH8" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="AI8" s="2"/>
+      <c r="AJ8" s="2"/>
+      <c r="AK8" s="2"/>
+      <c r="AL8" s="2"/>
+      <c r="AM8" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="AN8" s="2">
         <v>2</v>
       </c>
-      <c r="AH8" s="2">
+      <c r="AO8" s="2">
         <v>150</v>
       </c>
-      <c r="AI8" s="2"/>
-      <c r="AJ8" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="AK8" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="AL8" s="2"/>
-      <c r="AM8" s="2"/>
-      <c r="AN8" s="2"/>
-      <c r="AO8" s="2"/>
       <c r="AP8" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="AQ8" s="2">
+        <v>34</v>
+      </c>
+      <c r="AQ8" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="AR8" s="2"/>
+      <c r="AS8" s="2"/>
+      <c r="AT8" s="2"/>
+      <c r="AU8" s="2"/>
+      <c r="AV8" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="AW8" s="2">
         <v>2</v>
       </c>
-      <c r="AR8" s="2">
+      <c r="AX8" s="2">
         <v>150</v>
       </c>
-      <c r="AS8" s="2"/>
-      <c r="AT8" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="AU8" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="AV8" s="2"/>
-      <c r="AW8" s="2"/>
-      <c r="AX8" s="2"/>
-      <c r="AY8" s="2"/>
-      <c r="AZ8" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="BA8" s="2">
-        <v>2</v>
-      </c>
-      <c r="BB8" s="2">
-        <v>150</v>
-      </c>
-      <c r="BC8" s="2"/>
-      <c r="BD8" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="9" spans="1:56" x14ac:dyDescent="0.25">
+      <c r="AY8" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="9" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C9" s="2">
         <v>640</v>
@@ -2388,122 +2229,115 @@
       <c r="N9" s="2">
         <v>150</v>
       </c>
-      <c r="O9" s="2">
-        <v>2600</v>
+      <c r="O9" s="2" t="s">
+        <v>39</v>
       </c>
       <c r="P9" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q9" s="2">
+        <v>6</v>
+      </c>
+      <c r="R9" s="2">
+        <v>2</v>
+      </c>
+      <c r="S9" s="2">
+        <v>6</v>
+      </c>
+      <c r="T9" s="2">
+        <v>0</v>
+      </c>
+      <c r="U9" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="V9" s="2">
+        <v>2</v>
+      </c>
+      <c r="W9" s="2">
+        <v>150</v>
+      </c>
+      <c r="X9" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="Q9" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="R9" s="2">
+      <c r="Y9" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="Z9" s="2">
         <v>6</v>
       </c>
-      <c r="S9" s="2">
-        <v>0</v>
-      </c>
-      <c r="T9" s="2">
-        <v>6</v>
-      </c>
-      <c r="U9" s="2">
-        <v>3</v>
-      </c>
-      <c r="V9" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="W9" s="2">
+      <c r="AA9" s="2">
         <v>2</v>
-      </c>
-      <c r="X9" s="2">
-        <v>150</v>
-      </c>
-      <c r="Y9" s="2">
-        <v>2600</v>
-      </c>
-      <c r="Z9" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="AA9" s="2" t="s">
-        <v>35</v>
       </c>
       <c r="AB9" s="2">
         <v>6</v>
       </c>
       <c r="AC9" s="2">
-        <v>0</v>
-      </c>
-      <c r="AD9" s="2">
-        <v>6</v>
+        <v>2</v>
+      </c>
+      <c r="AD9" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="AE9" s="2">
-        <v>0</v>
-      </c>
-      <c r="AF9" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="AG9" s="2">
         <v>2</v>
       </c>
-      <c r="AH9" s="2">
+      <c r="AF9" s="2">
         <v>150</v>
       </c>
+      <c r="AG9" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="AH9" s="2" t="s">
+        <v>35</v>
+      </c>
       <c r="AI9" s="2"/>
-      <c r="AJ9" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="AK9" s="2" t="s">
-        <v>35</v>
-      </c>
+      <c r="AJ9" s="2"/>
+      <c r="AK9" s="2"/>
       <c r="AL9" s="2"/>
-      <c r="AM9" s="2"/>
-      <c r="AN9" s="2"/>
-      <c r="AO9" s="2"/>
+      <c r="AM9" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="AN9" s="2">
+        <v>2</v>
+      </c>
+      <c r="AO9" s="2">
+        <v>150</v>
+      </c>
       <c r="AP9" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="AQ9" s="2">
+        <v>34</v>
+      </c>
+      <c r="AQ9" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="AR9" s="2"/>
+      <c r="AS9" s="2"/>
+      <c r="AT9" s="2"/>
+      <c r="AU9" s="2"/>
+      <c r="AV9" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="AW9" s="2">
         <v>2</v>
       </c>
-      <c r="AR9" s="2">
+      <c r="AX9" s="2">
         <v>150</v>
       </c>
-      <c r="AS9" s="2"/>
-      <c r="AT9" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="AU9" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="AV9" s="2"/>
-      <c r="AW9" s="2"/>
-      <c r="AX9" s="2"/>
-      <c r="AY9" s="2"/>
-      <c r="AZ9" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="BA9" s="2">
-        <v>2</v>
-      </c>
-      <c r="BB9" s="2">
-        <v>150</v>
-      </c>
-      <c r="BC9" s="2"/>
-      <c r="BD9" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="10" spans="1:56" x14ac:dyDescent="0.25">
+      <c r="AY9" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="10" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C10" s="2">
-        <v>1000</v>
-      </c>
-      <c r="D10" s="2"/>
+        <v>640</v>
+      </c>
+      <c r="D10" s="2">
+        <v>1500</v>
+      </c>
       <c r="E10" s="2"/>
       <c r="F10" s="2" t="s">
         <v>34</v>
@@ -2511,121 +2345,132 @@
       <c r="G10" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="H10" s="2"/>
-      <c r="I10" s="2"/>
-      <c r="J10" s="2"/>
-      <c r="K10" s="2"/>
+      <c r="H10" s="2">
+        <v>6</v>
+      </c>
+      <c r="I10" s="2">
+        <v>0</v>
+      </c>
+      <c r="J10" s="2">
+        <v>6</v>
+      </c>
+      <c r="K10" s="2">
+        <v>3</v>
+      </c>
       <c r="L10" s="2" t="s">
         <v>36</v>
       </c>
       <c r="M10" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N10" s="2">
-        <v>200</v>
-      </c>
-      <c r="O10" s="2"/>
+        <v>150</v>
+      </c>
+      <c r="O10" s="2" t="s">
+        <v>39</v>
+      </c>
       <c r="P10" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q10" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="R10" s="2"/>
-      <c r="S10" s="2"/>
-      <c r="T10" s="2"/>
-      <c r="U10" s="2"/>
-      <c r="V10" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
+      </c>
+      <c r="Q10" s="2">
+        <v>6</v>
+      </c>
+      <c r="R10" s="2">
+        <v>0</v>
+      </c>
+      <c r="S10" s="2">
+        <v>6</v>
+      </c>
+      <c r="T10" s="2">
+        <v>0</v>
+      </c>
+      <c r="U10" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="V10" s="2">
+        <v>2</v>
       </c>
       <c r="W10" s="2">
-        <v>4</v>
-      </c>
-      <c r="X10" s="2">
-        <v>200</v>
-      </c>
-      <c r="Y10" s="2"/>
-      <c r="Z10" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="AA10" s="2" t="s">
-        <v>35</v>
+        <v>150</v>
+      </c>
+      <c r="X10" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="Y10" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="Z10" s="2">
+        <v>6</v>
+      </c>
+      <c r="AA10" s="2">
+        <v>0</v>
       </c>
       <c r="AB10" s="2">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AC10" s="2">
-        <v>9</v>
-      </c>
-      <c r="AD10" s="2">
-        <v>10</v>
+        <v>3</v>
+      </c>
+      <c r="AD10" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="AE10" s="2">
-        <v>0</v>
-      </c>
-      <c r="AF10" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="AG10" s="2">
-        <v>4</v>
-      </c>
-      <c r="AH10" s="2">
-        <v>200</v>
+        <v>2</v>
+      </c>
+      <c r="AF10" s="2">
+        <v>150</v>
+      </c>
+      <c r="AG10" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="AH10" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="AI10" s="2"/>
-      <c r="AJ10" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="AK10" s="2" t="s">
-        <v>35</v>
-      </c>
+      <c r="AJ10" s="2"/>
+      <c r="AK10" s="2"/>
       <c r="AL10" s="2"/>
-      <c r="AM10" s="2"/>
-      <c r="AN10" s="2"/>
-      <c r="AO10" s="2"/>
+      <c r="AM10" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="AN10" s="2">
+        <v>2</v>
+      </c>
+      <c r="AO10" s="2">
+        <v>150</v>
+      </c>
       <c r="AP10" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="AQ10" s="2">
-        <v>4</v>
-      </c>
-      <c r="AR10" s="2">
-        <v>200</v>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="AQ10" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="AR10" s="2"/>
       <c r="AS10" s="2"/>
-      <c r="AT10" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="AU10" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="AV10" s="2"/>
-      <c r="AW10" s="2"/>
-      <c r="AX10" s="2"/>
-      <c r="AY10" s="2"/>
-      <c r="AZ10" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="BA10" s="2">
-        <v>4</v>
-      </c>
-      <c r="BB10" s="2">
-        <v>200</v>
-      </c>
-      <c r="BC10" s="2"/>
-      <c r="BD10" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="11" spans="1:56" x14ac:dyDescent="0.25">
+      <c r="AT10" s="2"/>
+      <c r="AU10" s="2"/>
+      <c r="AV10" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="AW10" s="2">
+        <v>2</v>
+      </c>
+      <c r="AX10" s="2">
+        <v>150</v>
+      </c>
+      <c r="AY10" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="11" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C11" s="2">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="D11" s="2"/>
       <c r="E11" s="2"/>
@@ -2643,113 +2488,108 @@
         <v>36</v>
       </c>
       <c r="M11" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N11" s="2">
         <v>200</v>
       </c>
-      <c r="O11" s="2"/>
+      <c r="O11" s="2" t="s">
+        <v>34</v>
+      </c>
       <c r="P11" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q11" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="R11" s="2"/>
-      <c r="S11" s="2"/>
-      <c r="T11" s="2"/>
-      <c r="U11" s="2"/>
-      <c r="V11" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
+      </c>
+      <c r="Q11" s="2">
+        <v>10</v>
+      </c>
+      <c r="R11" s="2">
+        <v>9</v>
+      </c>
+      <c r="S11" s="2">
+        <v>10</v>
+      </c>
+      <c r="T11" s="2">
+        <v>0</v>
+      </c>
+      <c r="U11" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="V11" s="2">
+        <v>4</v>
       </c>
       <c r="W11" s="2">
-        <v>3</v>
-      </c>
-      <c r="X11" s="2">
-        <v>200</v>
-      </c>
-      <c r="Y11" s="2"/>
-      <c r="Z11" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="AA11" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="AB11" s="2">
-        <v>8</v>
-      </c>
-      <c r="AC11" s="2">
-        <v>6</v>
-      </c>
-      <c r="AD11" s="2">
-        <v>8</v>
+        <v>200</v>
+      </c>
+      <c r="X11" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="Y11" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="Z11" s="2"/>
+      <c r="AA11" s="2"/>
+      <c r="AB11" s="2"/>
+      <c r="AC11" s="2"/>
+      <c r="AD11" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="AE11" s="2">
-        <v>0</v>
-      </c>
-      <c r="AF11" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="AG11" s="2">
-        <v>3</v>
-      </c>
-      <c r="AH11" s="2">
-        <v>200</v>
+        <v>4</v>
+      </c>
+      <c r="AF11" s="2">
+        <v>200</v>
+      </c>
+      <c r="AG11" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="AH11" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="AI11" s="2"/>
-      <c r="AJ11" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="AK11" s="2" t="s">
-        <v>35</v>
-      </c>
+      <c r="AJ11" s="2"/>
+      <c r="AK11" s="2"/>
       <c r="AL11" s="2"/>
-      <c r="AM11" s="2"/>
-      <c r="AN11" s="2"/>
-      <c r="AO11" s="2"/>
+      <c r="AM11" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="AN11" s="2">
+        <v>4</v>
+      </c>
+      <c r="AO11" s="2">
+        <v>200</v>
+      </c>
       <c r="AP11" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="AQ11" s="2">
-        <v>3</v>
-      </c>
-      <c r="AR11" s="2">
-        <v>200</v>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="AQ11" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="AR11" s="2"/>
       <c r="AS11" s="2"/>
-      <c r="AT11" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="AU11" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="AV11" s="2"/>
-      <c r="AW11" s="2"/>
-      <c r="AX11" s="2"/>
-      <c r="AY11" s="2"/>
-      <c r="AZ11" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="BA11" s="2">
-        <v>3</v>
-      </c>
-      <c r="BB11" s="2">
-        <v>200</v>
-      </c>
-      <c r="BC11" s="2"/>
-      <c r="BD11" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="12" spans="1:56" x14ac:dyDescent="0.25">
+      <c r="AT11" s="2"/>
+      <c r="AU11" s="2"/>
+      <c r="AV11" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="AW11" s="2">
+        <v>4</v>
+      </c>
+      <c r="AX11" s="2">
+        <v>200</v>
+      </c>
+      <c r="AY11" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="12" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C12" s="2">
-        <v>1300</v>
+        <v>800</v>
       </c>
       <c r="D12" s="2"/>
       <c r="E12" s="2"/>
@@ -2767,117 +2607,110 @@
         <v>36</v>
       </c>
       <c r="M12" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N12" s="2">
-        <v>150</v>
-      </c>
-      <c r="O12" s="2"/>
+        <v>200</v>
+      </c>
+      <c r="O12" s="2" t="s">
+        <v>34</v>
+      </c>
       <c r="P12" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q12" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="R12" s="2"/>
-      <c r="S12" s="2"/>
-      <c r="T12" s="2"/>
-      <c r="U12" s="2"/>
-      <c r="V12" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
+      </c>
+      <c r="Q12" s="2">
+        <v>8</v>
+      </c>
+      <c r="R12" s="2">
+        <v>6</v>
+      </c>
+      <c r="S12" s="2">
+        <v>8</v>
+      </c>
+      <c r="T12" s="2">
+        <v>0</v>
+      </c>
+      <c r="U12" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="V12" s="2">
+        <v>3</v>
       </c>
       <c r="W12" s="2">
-        <v>4</v>
-      </c>
-      <c r="X12" s="2">
-        <v>150</v>
-      </c>
-      <c r="Y12" s="2"/>
-      <c r="Z12" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="AA12" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="AB12" s="2">
-        <v>13</v>
-      </c>
-      <c r="AC12" s="2">
-        <v>11</v>
-      </c>
-      <c r="AD12" s="2">
-        <v>13</v>
+        <v>200</v>
+      </c>
+      <c r="X12" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="Y12" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="Z12" s="2"/>
+      <c r="AA12" s="2"/>
+      <c r="AB12" s="2"/>
+      <c r="AC12" s="2"/>
+      <c r="AD12" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="AE12" s="2">
-        <v>0</v>
-      </c>
-      <c r="AF12" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="AG12" s="2">
-        <v>4</v>
-      </c>
-      <c r="AH12" s="2">
-        <v>150</v>
+        <v>3</v>
+      </c>
+      <c r="AF12" s="2">
+        <v>200</v>
+      </c>
+      <c r="AG12" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="AH12" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="AI12" s="2"/>
-      <c r="AJ12" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="AK12" s="2" t="s">
-        <v>35</v>
-      </c>
+      <c r="AJ12" s="2"/>
+      <c r="AK12" s="2"/>
       <c r="AL12" s="2"/>
-      <c r="AM12" s="2"/>
-      <c r="AN12" s="2"/>
-      <c r="AO12" s="2"/>
+      <c r="AM12" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="AN12" s="2">
+        <v>3</v>
+      </c>
+      <c r="AO12" s="2">
+        <v>200</v>
+      </c>
       <c r="AP12" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="AQ12" s="2">
-        <v>4</v>
-      </c>
-      <c r="AR12" s="2">
-        <v>150</v>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="AQ12" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="AR12" s="2"/>
       <c r="AS12" s="2"/>
-      <c r="AT12" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="AU12" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="AV12" s="2"/>
-      <c r="AW12" s="2"/>
-      <c r="AX12" s="2"/>
-      <c r="AY12" s="2"/>
-      <c r="AZ12" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="BA12" s="2">
-        <v>4</v>
-      </c>
-      <c r="BB12" s="2">
-        <v>150</v>
-      </c>
-      <c r="BC12" s="2"/>
-      <c r="BD12" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="13" spans="1:56" x14ac:dyDescent="0.25">
+      <c r="AT12" s="2"/>
+      <c r="AU12" s="2"/>
+      <c r="AV12" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="AW12" s="2">
+        <v>3</v>
+      </c>
+      <c r="AX12" s="2">
+        <v>200</v>
+      </c>
+      <c r="AY12" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="13" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C13" s="2">
-        <v>1000</v>
-      </c>
-      <c r="D13" s="2">
-        <v>1500</v>
-      </c>
+        <v>1300</v>
+      </c>
+      <c r="D13" s="2"/>
       <c r="E13" s="2"/>
       <c r="F13" s="2" t="s">
         <v>34</v>
@@ -2885,18 +2718,10 @@
       <c r="G13" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="H13" s="2">
-        <v>8</v>
-      </c>
-      <c r="I13" s="2">
-        <v>8</v>
-      </c>
-      <c r="J13" s="2">
-        <v>10</v>
-      </c>
-      <c r="K13" s="2">
-        <v>0</v>
-      </c>
+      <c r="H13" s="2"/>
+      <c r="I13" s="2"/>
+      <c r="J13" s="2"/>
+      <c r="K13" s="2"/>
       <c r="L13" s="2" t="s">
         <v>36</v>
       </c>
@@ -2904,120 +2729,105 @@
         <v>4</v>
       </c>
       <c r="N13" s="2">
-        <v>200</v>
-      </c>
-      <c r="O13" s="2"/>
+        <v>150</v>
+      </c>
+      <c r="O13" s="2" t="s">
+        <v>34</v>
+      </c>
       <c r="P13" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="Q13" s="2" t="s">
-        <v>35</v>
+        <v>35</v>
+      </c>
+      <c r="Q13" s="2">
+        <v>13</v>
       </c>
       <c r="R13" s="2">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="S13" s="2">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="T13" s="2">
-        <v>10</v>
-      </c>
-      <c r="U13" s="2">
         <v>0</v>
       </c>
-      <c r="V13" s="2" t="s">
-        <v>36</v>
+      <c r="U13" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="V13" s="2">
+        <v>4</v>
       </c>
       <c r="W13" s="2">
+        <v>150</v>
+      </c>
+      <c r="X13" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="Y13" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="Z13" s="2"/>
+      <c r="AA13" s="2"/>
+      <c r="AB13" s="2"/>
+      <c r="AC13" s="2"/>
+      <c r="AD13" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="AE13" s="2">
         <v>4</v>
       </c>
-      <c r="X13" s="2">
-        <v>200</v>
-      </c>
-      <c r="Y13" s="2"/>
-      <c r="Z13" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="AA13" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="AB13" s="2">
-        <v>10</v>
-      </c>
-      <c r="AC13" s="2">
-        <v>10</v>
-      </c>
-      <c r="AD13" s="2">
-        <v>10</v>
-      </c>
-      <c r="AE13" s="2">
-        <v>0</v>
-      </c>
-      <c r="AF13" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="AG13" s="2">
+      <c r="AF13" s="2">
+        <v>150</v>
+      </c>
+      <c r="AG13" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="AH13" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="AI13" s="2"/>
+      <c r="AJ13" s="2"/>
+      <c r="AK13" s="2"/>
+      <c r="AL13" s="2"/>
+      <c r="AM13" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="AN13" s="2">
         <v>4</v>
       </c>
-      <c r="AH13" s="2">
-        <v>200</v>
-      </c>
-      <c r="AI13" s="2">
-        <v>4500</v>
-      </c>
-      <c r="AJ13" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="AK13" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="AL13" s="2"/>
-      <c r="AM13" s="2"/>
-      <c r="AN13" s="2"/>
-      <c r="AO13" s="2"/>
+      <c r="AO13" s="2">
+        <v>150</v>
+      </c>
       <c r="AP13" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="AQ13" s="2">
+        <v>34</v>
+      </c>
+      <c r="AQ13" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="AR13" s="2"/>
+      <c r="AS13" s="2"/>
+      <c r="AT13" s="2"/>
+      <c r="AU13" s="2"/>
+      <c r="AV13" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="AW13" s="2">
         <v>4</v>
       </c>
-      <c r="AR13" s="2">
-        <v>200</v>
-      </c>
-      <c r="AS13" s="2"/>
-      <c r="AT13" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="AU13" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="AV13" s="2"/>
-      <c r="AW13" s="2"/>
-      <c r="AX13" s="2"/>
-      <c r="AY13" s="2"/>
-      <c r="AZ13" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="BA13" s="2">
-        <v>4</v>
-      </c>
-      <c r="BB13" s="2">
-        <v>200</v>
-      </c>
-      <c r="BC13" s="2"/>
-      <c r="BD13" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="14" spans="1:56" x14ac:dyDescent="0.25">
+      <c r="AX13" s="2">
+        <v>150</v>
+      </c>
+      <c r="AY13" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="14" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C14" s="2">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="D14" s="2">
         <v>1500</v>
@@ -3030,142 +2840,135 @@
         <v>35</v>
       </c>
       <c r="H14" s="2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I14" s="2">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="J14" s="2">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="K14" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L14" s="2" t="s">
         <v>36</v>
       </c>
       <c r="M14" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N14" s="2">
         <v>200</v>
       </c>
-      <c r="O14" s="2">
-        <v>2800</v>
+      <c r="O14" s="2" t="s">
+        <v>60</v>
       </c>
       <c r="P14" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="Q14" s="2" t="s">
-        <v>35</v>
+        <v>35</v>
+      </c>
+      <c r="Q14" s="2">
+        <v>10</v>
       </c>
       <c r="R14" s="2">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="S14" s="2">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T14" s="2">
-        <v>7</v>
-      </c>
-      <c r="U14" s="2">
+        <v>0</v>
+      </c>
+      <c r="U14" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="V14" s="2">
         <v>4</v>
       </c>
-      <c r="V14" s="2" t="s">
-        <v>36</v>
-      </c>
       <c r="W14" s="2">
-        <v>3</v>
-      </c>
-      <c r="X14" s="2">
-        <v>200</v>
-      </c>
-      <c r="Y14" s="2">
-        <v>2500</v>
-      </c>
-      <c r="Z14" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="AA14" s="2" t="s">
-        <v>35</v>
+        <v>200</v>
+      </c>
+      <c r="X14" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="Y14" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="Z14" s="2">
+        <v>8</v>
+      </c>
+      <c r="AA14" s="2">
+        <v>8</v>
       </c>
       <c r="AB14" s="2">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AC14" s="2">
-        <v>3</v>
-      </c>
-      <c r="AD14" s="2">
-        <v>7</v>
+        <v>0</v>
+      </c>
+      <c r="AD14" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="AE14" s="2">
-        <v>0</v>
-      </c>
-      <c r="AF14" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="AG14" s="2">
-        <v>3</v>
-      </c>
-      <c r="AH14" s="2">
-        <v>200</v>
+        <v>4</v>
+      </c>
+      <c r="AF14" s="2">
+        <v>200</v>
+      </c>
+      <c r="AG14" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="AH14" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="AI14" s="2"/>
-      <c r="AJ14" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="AK14" s="2" t="s">
-        <v>35</v>
-      </c>
+      <c r="AJ14" s="2"/>
+      <c r="AK14" s="2"/>
       <c r="AL14" s="2"/>
-      <c r="AM14" s="2"/>
-      <c r="AN14" s="2"/>
-      <c r="AO14" s="2"/>
+      <c r="AM14" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="AN14" s="2">
+        <v>4</v>
+      </c>
+      <c r="AO14" s="2">
+        <v>200</v>
+      </c>
       <c r="AP14" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="AQ14" s="2">
-        <v>3</v>
-      </c>
-      <c r="AR14" s="2">
-        <v>200</v>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="AQ14" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="AR14" s="2"/>
       <c r="AS14" s="2"/>
-      <c r="AT14" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="AU14" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="AV14" s="2"/>
-      <c r="AW14" s="2"/>
-      <c r="AX14" s="2"/>
-      <c r="AY14" s="2"/>
-      <c r="AZ14" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="BA14" s="2">
-        <v>3</v>
-      </c>
-      <c r="BB14" s="2">
-        <v>200</v>
-      </c>
-      <c r="BC14" s="2"/>
-      <c r="BD14" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="15" spans="1:56" x14ac:dyDescent="0.25">
+      <c r="AT14" s="2"/>
+      <c r="AU14" s="2"/>
+      <c r="AV14" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="AW14" s="2">
+        <v>4</v>
+      </c>
+      <c r="AX14" s="2">
+        <v>200</v>
+      </c>
+      <c r="AY14" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="15" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="C15" s="2">
         <v>800</v>
       </c>
-      <c r="D15" s="2"/>
+      <c r="D15" s="2">
+        <v>1500</v>
+      </c>
       <c r="E15" s="2"/>
       <c r="F15" s="2" t="s">
         <v>34</v>
@@ -3173,10 +2976,18 @@
       <c r="G15" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="H15" s="2"/>
-      <c r="I15" s="2"/>
-      <c r="J15" s="2"/>
-      <c r="K15" s="2"/>
+      <c r="H15" s="2">
+        <v>7</v>
+      </c>
+      <c r="I15" s="2">
+        <v>3</v>
+      </c>
+      <c r="J15" s="2">
+        <v>7</v>
+      </c>
+      <c r="K15" s="2">
+        <v>3</v>
+      </c>
       <c r="L15" s="2" t="s">
         <v>36</v>
       </c>
@@ -3186,112 +2997,113 @@
       <c r="N15" s="2">
         <v>200</v>
       </c>
-      <c r="O15" s="2"/>
+      <c r="O15" s="2" t="s">
+        <v>63</v>
+      </c>
       <c r="P15" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q15" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="R15" s="2"/>
-      <c r="S15" s="2"/>
-      <c r="T15" s="2"/>
-      <c r="U15" s="2"/>
-      <c r="V15" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
+      </c>
+      <c r="Q15" s="2">
+        <v>7</v>
+      </c>
+      <c r="R15" s="2">
+        <v>3</v>
+      </c>
+      <c r="S15" s="2">
+        <v>7</v>
+      </c>
+      <c r="T15" s="2">
+        <v>0</v>
+      </c>
+      <c r="U15" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="V15" s="2">
+        <v>3</v>
       </c>
       <c r="W15" s="2">
-        <v>3</v>
-      </c>
-      <c r="X15" s="2">
-        <v>200</v>
-      </c>
-      <c r="Y15" s="2"/>
-      <c r="Z15" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="AA15" s="2" t="s">
-        <v>35</v>
+        <v>200</v>
+      </c>
+      <c r="X15" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="Y15" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="Z15" s="2">
+        <v>7</v>
+      </c>
+      <c r="AA15" s="2">
+        <v>1</v>
       </c>
       <c r="AB15" s="2">
         <v>7</v>
       </c>
       <c r="AC15" s="2">
-        <v>1</v>
-      </c>
-      <c r="AD15" s="2">
-        <v>7</v>
+        <v>4</v>
+      </c>
+      <c r="AD15" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="AE15" s="2">
-        <v>4</v>
-      </c>
-      <c r="AF15" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="AG15" s="2">
         <v>3</v>
       </c>
-      <c r="AH15" s="2">
-        <v>200</v>
+      <c r="AF15" s="2">
+        <v>200</v>
+      </c>
+      <c r="AG15" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="AH15" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="AI15" s="2"/>
-      <c r="AJ15" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="AK15" s="2" t="s">
-        <v>35</v>
-      </c>
+      <c r="AJ15" s="2"/>
+      <c r="AK15" s="2"/>
       <c r="AL15" s="2"/>
-      <c r="AM15" s="2"/>
-      <c r="AN15" s="2"/>
-      <c r="AO15" s="2"/>
+      <c r="AM15" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="AN15" s="2">
+        <v>3</v>
+      </c>
+      <c r="AO15" s="2">
+        <v>200</v>
+      </c>
       <c r="AP15" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="AQ15" s="2">
+        <v>34</v>
+      </c>
+      <c r="AQ15" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="AR15" s="2"/>
+      <c r="AS15" s="2"/>
+      <c r="AT15" s="2"/>
+      <c r="AU15" s="2"/>
+      <c r="AV15" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="AW15" s="2">
         <v>3</v>
       </c>
-      <c r="AR15" s="2">
-        <v>200</v>
-      </c>
-      <c r="AS15" s="2"/>
-      <c r="AT15" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="AU15" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="AV15" s="2"/>
-      <c r="AW15" s="2"/>
-      <c r="AX15" s="2"/>
-      <c r="AY15" s="2"/>
-      <c r="AZ15" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="BA15" s="2">
-        <v>3</v>
-      </c>
-      <c r="BB15" s="2">
-        <v>200</v>
-      </c>
-      <c r="BC15" s="2"/>
-      <c r="BD15" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="16" spans="1:56" x14ac:dyDescent="0.25">
+      <c r="AX15" s="2">
+        <v>200</v>
+      </c>
+      <c r="AY15" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="16" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C16" s="2">
         <v>800</v>
       </c>
-      <c r="D16" s="2">
-        <v>1500</v>
-      </c>
+      <c r="D16" s="2"/>
       <c r="E16" s="2"/>
       <c r="F16" s="2" t="s">
         <v>34</v>
@@ -3299,18 +3111,10 @@
       <c r="G16" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="H16" s="2">
-        <v>7</v>
-      </c>
-      <c r="I16" s="2">
-        <v>1</v>
-      </c>
-      <c r="J16" s="2">
-        <v>7</v>
-      </c>
-      <c r="K16" s="2">
-        <v>4</v>
-      </c>
+      <c r="H16" s="2"/>
+      <c r="I16" s="2"/>
+      <c r="J16" s="2"/>
+      <c r="K16" s="2"/>
       <c r="L16" s="2" t="s">
         <v>36</v>
       </c>
@@ -3320,121 +3124,106 @@
       <c r="N16" s="2">
         <v>200</v>
       </c>
-      <c r="O16" s="2">
-        <v>3200</v>
+      <c r="O16" s="2" t="s">
+        <v>34</v>
       </c>
       <c r="P16" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="Q16" s="2" t="s">
-        <v>35</v>
+        <v>35</v>
+      </c>
+      <c r="Q16" s="2">
+        <v>7</v>
       </c>
       <c r="R16" s="2">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="S16" s="2">
         <v>7</v>
       </c>
       <c r="T16" s="2">
-        <v>7</v>
-      </c>
-      <c r="U16" s="2">
+        <v>4</v>
+      </c>
+      <c r="U16" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="V16" s="2">
         <v>3</v>
       </c>
-      <c r="V16" s="2" t="s">
-        <v>36</v>
-      </c>
       <c r="W16" s="2">
+        <v>200</v>
+      </c>
+      <c r="X16" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="Y16" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="Z16" s="2"/>
+      <c r="AA16" s="2"/>
+      <c r="AB16" s="2"/>
+      <c r="AC16" s="2"/>
+      <c r="AD16" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="AE16" s="2">
         <v>3</v>
       </c>
-      <c r="X16" s="2">
-        <v>200</v>
-      </c>
-      <c r="Y16" s="2">
-        <v>3200</v>
-      </c>
-      <c r="Z16" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="AA16" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="AB16" s="2">
-        <v>7</v>
-      </c>
-      <c r="AC16" s="2">
-        <v>7</v>
-      </c>
-      <c r="AD16" s="2">
-        <v>7</v>
-      </c>
-      <c r="AE16" s="2">
-        <v>0</v>
-      </c>
-      <c r="AF16" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="AG16" s="2">
+      <c r="AF16" s="2">
+        <v>200</v>
+      </c>
+      <c r="AG16" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="AH16" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="AI16" s="2"/>
+      <c r="AJ16" s="2"/>
+      <c r="AK16" s="2"/>
+      <c r="AL16" s="2"/>
+      <c r="AM16" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="AN16" s="2">
         <v>3</v>
       </c>
-      <c r="AH16" s="2">
-        <v>200</v>
-      </c>
-      <c r="AI16" s="2"/>
-      <c r="AJ16" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="AK16" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="AL16" s="2"/>
-      <c r="AM16" s="2"/>
-      <c r="AN16" s="2"/>
-      <c r="AO16" s="2"/>
+      <c r="AO16" s="2">
+        <v>200</v>
+      </c>
       <c r="AP16" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="AQ16" s="2">
+        <v>34</v>
+      </c>
+      <c r="AQ16" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="AR16" s="2"/>
+      <c r="AS16" s="2"/>
+      <c r="AT16" s="2"/>
+      <c r="AU16" s="2"/>
+      <c r="AV16" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="AW16" s="2">
         <v>3</v>
       </c>
-      <c r="AR16" s="2">
-        <v>200</v>
-      </c>
-      <c r="AS16" s="2"/>
-      <c r="AT16" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="AU16" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="AV16" s="2"/>
-      <c r="AW16" s="2"/>
-      <c r="AX16" s="2"/>
-      <c r="AY16" s="2"/>
-      <c r="AZ16" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="BA16" s="2">
-        <v>3</v>
-      </c>
-      <c r="BB16" s="2">
-        <v>200</v>
-      </c>
-      <c r="BC16" s="2"/>
-      <c r="BD16" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="17" spans="1:56" x14ac:dyDescent="0.25">
+      <c r="AX16" s="2">
+        <v>200</v>
+      </c>
+      <c r="AY16" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="17" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="C17" s="2"/>
+        <v>67</v>
+      </c>
+      <c r="C17" s="2">
+        <v>800</v>
+      </c>
       <c r="D17" s="2">
-        <v>1200</v>
+        <v>1500</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" s="2" t="s">
@@ -3444,16 +3233,16 @@
         <v>35</v>
       </c>
       <c r="H17" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I17" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J17" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K17" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L17" s="2" t="s">
         <v>36</v>
@@ -3464,123 +3253,112 @@
       <c r="N17" s="2">
         <v>200</v>
       </c>
-      <c r="O17" s="2">
-        <v>2700</v>
+      <c r="O17" s="2" t="s">
+        <v>65</v>
       </c>
       <c r="P17" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="Q17" s="2" t="s">
-        <v>35</v>
+        <v>35</v>
+      </c>
+      <c r="Q17" s="2">
+        <v>7</v>
       </c>
       <c r="R17" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="S17" s="2">
+        <v>7</v>
+      </c>
+      <c r="T17" s="2">
+        <v>0</v>
+      </c>
+      <c r="U17" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="V17" s="2">
         <v>3</v>
       </c>
-      <c r="T17" s="2">
-        <v>6</v>
-      </c>
-      <c r="U17" s="2">
+      <c r="W17" s="2">
+        <v>200</v>
+      </c>
+      <c r="X17" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="Y17" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="Z17" s="2">
+        <v>7</v>
+      </c>
+      <c r="AA17" s="2">
+        <v>7</v>
+      </c>
+      <c r="AB17" s="2">
+        <v>7</v>
+      </c>
+      <c r="AC17" s="2">
         <v>3</v>
       </c>
-      <c r="V17" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="W17" s="2">
+      <c r="AD17" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="AE17" s="2">
         <v>3</v>
       </c>
-      <c r="X17" s="2">
-        <v>200</v>
-      </c>
-      <c r="Y17" s="2">
-        <v>2700</v>
-      </c>
-      <c r="Z17" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="AA17" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="AB17" s="2">
-        <v>6</v>
-      </c>
-      <c r="AC17" s="2">
-        <v>0</v>
-      </c>
-      <c r="AD17" s="2">
-        <v>6</v>
-      </c>
-      <c r="AE17" s="2">
-        <v>0</v>
-      </c>
-      <c r="AF17" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="AG17" s="2">
+      <c r="AF17" s="2">
+        <v>200</v>
+      </c>
+      <c r="AG17" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="AH17" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="AI17" s="2"/>
+      <c r="AJ17" s="2"/>
+      <c r="AK17" s="2"/>
+      <c r="AL17" s="2"/>
+      <c r="AM17" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="AN17" s="2">
         <v>3</v>
       </c>
-      <c r="AH17" s="2">
-        <v>200</v>
-      </c>
-      <c r="AI17" s="2"/>
-      <c r="AJ17" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="AK17" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="AL17" s="2"/>
-      <c r="AM17" s="2"/>
-      <c r="AN17" s="2"/>
-      <c r="AO17" s="2"/>
+      <c r="AO17" s="2">
+        <v>200</v>
+      </c>
       <c r="AP17" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="AQ17" s="2">
+        <v>34</v>
+      </c>
+      <c r="AQ17" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="AR17" s="2"/>
+      <c r="AS17" s="2"/>
+      <c r="AT17" s="2"/>
+      <c r="AU17" s="2"/>
+      <c r="AV17" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="AW17" s="2">
         <v>3</v>
       </c>
-      <c r="AR17" s="2">
-        <v>200</v>
-      </c>
-      <c r="AS17" s="2"/>
-      <c r="AT17" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="AU17" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="AV17" s="2"/>
-      <c r="AW17" s="2"/>
-      <c r="AX17" s="2"/>
-      <c r="AY17" s="2"/>
-      <c r="AZ17" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="BA17" s="2">
-        <v>3</v>
-      </c>
-      <c r="BB17" s="2">
-        <v>200</v>
-      </c>
-      <c r="BC17" s="2"/>
-      <c r="BD17" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="18" spans="1:56" x14ac:dyDescent="0.25">
+      <c r="AX17" s="2">
+        <v>200</v>
+      </c>
+      <c r="AY17" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="18" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="C18" s="2">
+        <v>70</v>
+      </c>
+      <c r="C18" s="2"/>
+      <c r="D18" s="2">
         <v>1200</v>
-      </c>
-      <c r="D18" s="2">
-        <v>1500</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" s="2" t="s">
@@ -3590,135 +3368,128 @@
         <v>35</v>
       </c>
       <c r="H18" s="2">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="I18" s="2">
         <v>3</v>
       </c>
       <c r="J18" s="2">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="K18" s="2">
+        <v>3</v>
+      </c>
+      <c r="L18" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="M18" s="2">
+        <v>3</v>
+      </c>
+      <c r="N18" s="2">
+        <v>200</v>
+      </c>
+      <c r="O18" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="P18" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q18" s="2">
+        <v>6</v>
+      </c>
+      <c r="R18" s="2">
         <v>0</v>
       </c>
-      <c r="L18" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="M18" s="2">
-        <v>4</v>
-      </c>
-      <c r="N18" s="2">
-        <v>200</v>
-      </c>
-      <c r="O18" s="2"/>
-      <c r="P18" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="Q18" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="R18" s="2">
-        <v>12</v>
-      </c>
       <c r="S18" s="2">
+        <v>6</v>
+      </c>
+      <c r="T18" s="2">
+        <v>0</v>
+      </c>
+      <c r="U18" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="V18" s="2">
         <v>3</v>
       </c>
-      <c r="T18" s="2">
-        <v>12</v>
-      </c>
-      <c r="U18" s="2">
-        <v>11</v>
-      </c>
-      <c r="V18" s="2" t="s">
-        <v>36</v>
-      </c>
       <c r="W18" s="2">
-        <v>4</v>
-      </c>
-      <c r="X18" s="2">
-        <v>200</v>
-      </c>
-      <c r="Y18" s="2">
-        <v>3200</v>
-      </c>
-      <c r="Z18" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="AA18" s="2" t="s">
-        <v>35</v>
+        <v>200</v>
+      </c>
+      <c r="X18" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="Y18" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="Z18" s="2">
+        <v>6</v>
+      </c>
+      <c r="AA18" s="2">
+        <v>3</v>
       </c>
       <c r="AB18" s="2">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="AC18" s="2">
         <v>3</v>
       </c>
-      <c r="AD18" s="2">
-        <v>12</v>
+      <c r="AD18" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="AE18" s="2">
-        <v>0</v>
-      </c>
-      <c r="AF18" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="AG18" s="2">
-        <v>4</v>
-      </c>
-      <c r="AH18" s="2">
-        <v>200</v>
+        <v>3</v>
+      </c>
+      <c r="AF18" s="2">
+        <v>200</v>
+      </c>
+      <c r="AG18" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="AH18" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="AI18" s="2"/>
-      <c r="AJ18" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="AK18" s="2" t="s">
-        <v>35</v>
-      </c>
+      <c r="AJ18" s="2"/>
+      <c r="AK18" s="2"/>
       <c r="AL18" s="2"/>
-      <c r="AM18" s="2"/>
-      <c r="AN18" s="2"/>
-      <c r="AO18" s="2"/>
+      <c r="AM18" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="AN18" s="2">
+        <v>3</v>
+      </c>
+      <c r="AO18" s="2">
+        <v>200</v>
+      </c>
       <c r="AP18" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="AQ18" s="2">
-        <v>4</v>
-      </c>
-      <c r="AR18" s="2">
-        <v>200</v>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="AQ18" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="AR18" s="2"/>
       <c r="AS18" s="2"/>
-      <c r="AT18" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="AU18" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="AV18" s="2"/>
-      <c r="AW18" s="2"/>
-      <c r="AX18" s="2"/>
-      <c r="AY18" s="2"/>
-      <c r="AZ18" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="BA18" s="2">
-        <v>4</v>
-      </c>
-      <c r="BB18" s="2">
-        <v>200</v>
-      </c>
-      <c r="BC18" s="2"/>
-      <c r="BD18" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="19" spans="1:56" x14ac:dyDescent="0.25">
+      <c r="AT18" s="2"/>
+      <c r="AU18" s="2"/>
+      <c r="AV18" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="AW18" s="2">
+        <v>3</v>
+      </c>
+      <c r="AX18" s="2">
+        <v>200</v>
+      </c>
+      <c r="AY18" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="19" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C19" s="2">
         <v>1200</v>
@@ -3737,13 +3508,13 @@
         <v>12</v>
       </c>
       <c r="I19" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J19" s="2">
         <v>12</v>
       </c>
       <c r="K19" s="2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L19" s="2" t="s">
         <v>36</v>
@@ -3754,219 +3525,229 @@
       <c r="N19" s="2">
         <v>200</v>
       </c>
-      <c r="O19" s="2">
-        <v>3200</v>
+      <c r="O19" s="2" t="s">
+        <v>73</v>
       </c>
       <c r="P19" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="Q19" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="R19" s="2"/>
-      <c r="S19" s="2"/>
-      <c r="T19" s="2"/>
-      <c r="U19" s="2"/>
-      <c r="V19" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
+      </c>
+      <c r="Q19" s="2">
+        <v>12</v>
+      </c>
+      <c r="R19" s="2">
+        <v>3</v>
+      </c>
+      <c r="S19" s="2">
+        <v>12</v>
+      </c>
+      <c r="T19" s="2">
+        <v>0</v>
+      </c>
+      <c r="U19" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="V19" s="2">
+        <v>4</v>
       </c>
       <c r="W19" s="2">
+        <v>200</v>
+      </c>
+      <c r="X19" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="Y19" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="Z19" s="2">
+        <v>12</v>
+      </c>
+      <c r="AA19" s="2">
+        <v>3</v>
+      </c>
+      <c r="AB19" s="2">
+        <v>12</v>
+      </c>
+      <c r="AC19" s="2">
+        <v>11</v>
+      </c>
+      <c r="AD19" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="AE19" s="2">
         <v>4</v>
       </c>
-      <c r="X19" s="2">
-        <v>200</v>
-      </c>
-      <c r="Y19" s="2"/>
-      <c r="Z19" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="AA19" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="AB19" s="2"/>
-      <c r="AC19" s="2"/>
-      <c r="AD19" s="2"/>
-      <c r="AE19" s="2"/>
-      <c r="AF19" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="AG19" s="2">
+      <c r="AF19" s="2">
+        <v>200</v>
+      </c>
+      <c r="AG19" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="AH19" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="AI19" s="2"/>
+      <c r="AJ19" s="2"/>
+      <c r="AK19" s="2"/>
+      <c r="AL19" s="2"/>
+      <c r="AM19" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="AN19" s="2">
         <v>4</v>
       </c>
-      <c r="AH19" s="2">
-        <v>200</v>
-      </c>
-      <c r="AI19" s="2"/>
-      <c r="AJ19" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="AK19" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="AL19" s="2"/>
-      <c r="AM19" s="2"/>
-      <c r="AN19" s="2"/>
-      <c r="AO19" s="2"/>
+      <c r="AO19" s="2">
+        <v>200</v>
+      </c>
       <c r="AP19" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="AQ19" s="2">
+        <v>34</v>
+      </c>
+      <c r="AQ19" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="AR19" s="2"/>
+      <c r="AS19" s="2"/>
+      <c r="AT19" s="2"/>
+      <c r="AU19" s="2"/>
+      <c r="AV19" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="AW19" s="2">
         <v>4</v>
       </c>
-      <c r="AR19" s="2">
-        <v>200</v>
-      </c>
-      <c r="AS19" s="2"/>
-      <c r="AT19" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="AU19" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="AV19" s="2"/>
-      <c r="AW19" s="2"/>
-      <c r="AX19" s="2"/>
-      <c r="AY19" s="2"/>
-      <c r="AZ19" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="BA19" s="2">
-        <v>4</v>
-      </c>
-      <c r="BB19" s="2">
-        <v>200</v>
-      </c>
-      <c r="BC19" s="2"/>
-      <c r="BD19" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="20" spans="1:56" x14ac:dyDescent="0.25">
+      <c r="AX19" s="2">
+        <v>200</v>
+      </c>
+      <c r="AY19" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="20" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="C20" s="2"/>
-      <c r="D20" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="C20" s="2">
+        <v>1200</v>
+      </c>
+      <c r="D20" s="2">
+        <v>1500</v>
+      </c>
       <c r="E20" s="2"/>
       <c r="F20" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="G20" s="2"/>
+      <c r="G20" s="2" t="s">
+        <v>35</v>
+      </c>
       <c r="H20" s="2">
+        <v>12</v>
+      </c>
+      <c r="I20" s="2">
+        <v>0</v>
+      </c>
+      <c r="J20" s="2">
+        <v>12</v>
+      </c>
+      <c r="K20" s="2">
+        <v>10</v>
+      </c>
+      <c r="L20" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="M20" s="2">
         <v>4</v>
       </c>
-      <c r="I20" s="2">
-        <v>2</v>
-      </c>
-      <c r="J20" s="2">
+      <c r="N20" s="2">
+        <v>200</v>
+      </c>
+      <c r="O20" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="P20" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q20" s="2"/>
+      <c r="R20" s="2"/>
+      <c r="S20" s="2"/>
+      <c r="T20" s="2"/>
+      <c r="U20" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="V20" s="2">
         <v>4</v>
       </c>
-      <c r="K20" s="2">
-        <v>2</v>
-      </c>
-      <c r="L20" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="M20" s="2">
-        <v>2</v>
-      </c>
-      <c r="N20" s="2">
-        <v>200</v>
-      </c>
-      <c r="O20" s="2"/>
-      <c r="P20" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="Q20" s="2"/>
-      <c r="R20" s="2">
-        <v>4</v>
-      </c>
-      <c r="S20" s="2">
-        <v>2</v>
-      </c>
-      <c r="T20" s="2">
-        <v>4</v>
-      </c>
-      <c r="U20" s="2">
-        <v>2</v>
-      </c>
-      <c r="V20" s="2" t="s">
-        <v>36</v>
-      </c>
       <c r="W20" s="2">
-        <v>2</v>
-      </c>
-      <c r="X20" s="2">
-        <v>200</v>
-      </c>
-      <c r="Y20" s="2"/>
-      <c r="Z20" s="2" t="s">
-        <v>78</v>
-      </c>
+        <v>200</v>
+      </c>
+      <c r="X20" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="Y20" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="Z20" s="2"/>
       <c r="AA20" s="2"/>
       <c r="AB20" s="2"/>
       <c r="AC20" s="2"/>
-      <c r="AD20" s="2"/>
-      <c r="AE20" s="2"/>
-      <c r="AF20" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="AG20" s="2">
-        <v>2</v>
-      </c>
-      <c r="AH20" s="2">
-        <v>200</v>
+      <c r="AD20" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="AE20" s="2">
+        <v>4</v>
+      </c>
+      <c r="AF20" s="2">
+        <v>200</v>
+      </c>
+      <c r="AG20" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="AH20" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="AI20" s="2"/>
-      <c r="AJ20" s="2" t="s">
-        <v>34</v>
-      </c>
+      <c r="AJ20" s="2"/>
       <c r="AK20" s="2"/>
       <c r="AL20" s="2"/>
-      <c r="AM20" s="2"/>
-      <c r="AN20" s="2"/>
-      <c r="AO20" s="2"/>
+      <c r="AM20" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="AN20" s="2">
+        <v>4</v>
+      </c>
+      <c r="AO20" s="2">
+        <v>200</v>
+      </c>
       <c r="AP20" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="AQ20" s="2">
-        <v>2</v>
-      </c>
-      <c r="AR20" s="2">
-        <v>200</v>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="AQ20" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="AR20" s="2"/>
       <c r="AS20" s="2"/>
-      <c r="AT20" s="2" t="s">
-        <v>34</v>
-      </c>
+      <c r="AT20" s="2"/>
       <c r="AU20" s="2"/>
-      <c r="AV20" s="2"/>
-      <c r="AW20" s="2"/>
-      <c r="AX20" s="2"/>
-      <c r="AY20" s="2"/>
-      <c r="AZ20" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="BA20" s="2">
-        <v>2</v>
-      </c>
-      <c r="BB20" s="2">
-        <v>200</v>
-      </c>
-      <c r="BC20" s="2"/>
-      <c r="BD20" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="21" spans="1:56" x14ac:dyDescent="0.25">
+      <c r="AV20" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="AW20" s="2">
+        <v>4</v>
+      </c>
+      <c r="AX20" s="2">
+        <v>200</v>
+      </c>
+      <c r="AY20" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="21" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" s="2"/>
@@ -3996,97 +3777,92 @@
       <c r="N21" s="2">
         <v>200</v>
       </c>
-      <c r="O21" s="2"/>
-      <c r="P21" s="2" t="s">
+      <c r="O21" s="2" t="s">
         <v>78</v>
       </c>
+      <c r="P21" s="2"/>
       <c r="Q21" s="2"/>
-      <c r="R21" s="2">
+      <c r="R21" s="2"/>
+      <c r="S21" s="2"/>
+      <c r="T21" s="2"/>
+      <c r="U21" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="V21" s="2">
+        <v>2</v>
+      </c>
+      <c r="W21" s="2">
+        <v>200</v>
+      </c>
+      <c r="X21" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="Y21" s="2"/>
+      <c r="Z21" s="2">
         <v>4</v>
       </c>
-      <c r="S21" s="2">
+      <c r="AA21" s="2">
         <v>2</v>
       </c>
-      <c r="T21" s="2">
+      <c r="AB21" s="2">
         <v>4</v>
       </c>
-      <c r="U21" s="2">
+      <c r="AC21" s="2">
         <v>2</v>
       </c>
-      <c r="V21" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="W21" s="2">
+      <c r="AD21" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="AE21" s="2">
         <v>2</v>
       </c>
-      <c r="X21" s="2">
-        <v>200</v>
-      </c>
-      <c r="Y21" s="2"/>
-      <c r="Z21" s="2" t="s">
+      <c r="AF21" s="2">
+        <v>200</v>
+      </c>
+      <c r="AG21" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="AA21" s="2"/>
-      <c r="AB21" s="2"/>
-      <c r="AC21" s="2"/>
-      <c r="AD21" s="2"/>
-      <c r="AE21" s="2"/>
-      <c r="AF21" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="AG21" s="2">
-        <v>2</v>
-      </c>
-      <c r="AH21" s="2">
-        <v>200</v>
-      </c>
+      <c r="AH21" s="2"/>
       <c r="AI21" s="2"/>
-      <c r="AJ21" s="2" t="s">
-        <v>34</v>
-      </c>
+      <c r="AJ21" s="2"/>
       <c r="AK21" s="2"/>
       <c r="AL21" s="2"/>
-      <c r="AM21" s="2"/>
-      <c r="AN21" s="2"/>
-      <c r="AO21" s="2"/>
+      <c r="AM21" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="AN21" s="2">
+        <v>2</v>
+      </c>
+      <c r="AO21" s="2">
+        <v>200</v>
+      </c>
       <c r="AP21" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="AQ21" s="2">
+        <v>34</v>
+      </c>
+      <c r="AQ21" s="2"/>
+      <c r="AR21" s="2"/>
+      <c r="AS21" s="2"/>
+      <c r="AT21" s="2"/>
+      <c r="AU21" s="2"/>
+      <c r="AV21" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="AW21" s="2">
         <v>2</v>
       </c>
-      <c r="AR21" s="2">
-        <v>200</v>
-      </c>
-      <c r="AS21" s="2"/>
-      <c r="AT21" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="AU21" s="2"/>
-      <c r="AV21" s="2"/>
-      <c r="AW21" s="2"/>
-      <c r="AX21" s="2"/>
-      <c r="AY21" s="2"/>
-      <c r="AZ21" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="BA21" s="2">
-        <v>2</v>
-      </c>
-      <c r="BB21" s="2">
-        <v>200</v>
-      </c>
-      <c r="BC21" s="2"/>
-      <c r="BD21" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="22" spans="1:56" x14ac:dyDescent="0.25">
+      <c r="AX21" s="2">
+        <v>200</v>
+      </c>
+      <c r="AY21" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="22" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" s="2"/>
@@ -4116,104 +3892,229 @@
       <c r="N22" s="2">
         <v>200</v>
       </c>
-      <c r="O22" s="2"/>
-      <c r="P22" s="2" t="s">
+      <c r="O22" s="2" t="s">
         <v>78</v>
       </c>
+      <c r="P22" s="2"/>
       <c r="Q22" s="2"/>
-      <c r="R22" s="2">
+      <c r="R22" s="2"/>
+      <c r="S22" s="2"/>
+      <c r="T22" s="2"/>
+      <c r="U22" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="V22" s="2">
+        <v>2</v>
+      </c>
+      <c r="W22" s="2">
+        <v>200</v>
+      </c>
+      <c r="X22" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="Y22" s="2"/>
+      <c r="Z22" s="2">
         <v>4</v>
       </c>
-      <c r="S22" s="2">
+      <c r="AA22" s="2">
         <v>2</v>
       </c>
-      <c r="T22" s="2">
+      <c r="AB22" s="2">
         <v>4</v>
       </c>
-      <c r="U22" s="2">
+      <c r="AC22" s="2">
         <v>2</v>
       </c>
-      <c r="V22" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="W22" s="2">
+      <c r="AD22" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="AE22" s="2">
         <v>2</v>
       </c>
-      <c r="X22" s="2">
-        <v>200</v>
-      </c>
-      <c r="Y22" s="2"/>
-      <c r="Z22" s="2" t="s">
+      <c r="AF22" s="2">
+        <v>200</v>
+      </c>
+      <c r="AG22" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="AA22" s="2"/>
-      <c r="AB22" s="2"/>
-      <c r="AC22" s="2"/>
-      <c r="AD22" s="2"/>
-      <c r="AE22" s="2"/>
-      <c r="AF22" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="AG22" s="2">
-        <v>2</v>
-      </c>
-      <c r="AH22" s="2">
-        <v>200</v>
-      </c>
+      <c r="AH22" s="2"/>
       <c r="AI22" s="2"/>
-      <c r="AJ22" s="2" t="s">
-        <v>34</v>
-      </c>
+      <c r="AJ22" s="2"/>
       <c r="AK22" s="2"/>
       <c r="AL22" s="2"/>
-      <c r="AM22" s="2"/>
-      <c r="AN22" s="2"/>
-      <c r="AO22" s="2"/>
+      <c r="AM22" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="AN22" s="2">
+        <v>2</v>
+      </c>
+      <c r="AO22" s="2">
+        <v>200</v>
+      </c>
       <c r="AP22" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="AQ22" s="2">
+        <v>34</v>
+      </c>
+      <c r="AQ22" s="2"/>
+      <c r="AR22" s="2"/>
+      <c r="AS22" s="2"/>
+      <c r="AT22" s="2"/>
+      <c r="AU22" s="2"/>
+      <c r="AV22" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="AW22" s="2">
         <v>2</v>
       </c>
-      <c r="AR22" s="2">
-        <v>200</v>
-      </c>
-      <c r="AS22" s="2"/>
-      <c r="AT22" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="AU22" s="2"/>
-      <c r="AV22" s="2"/>
-      <c r="AW22" s="2"/>
-      <c r="AX22" s="2"/>
-      <c r="AY22" s="2"/>
-      <c r="AZ22" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="BA22" s="2">
+      <c r="AX22" s="2">
+        <v>200</v>
+      </c>
+      <c r="AY22" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="23" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="A23" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="C23" s="2"/>
+      <c r="D23" s="2"/>
+      <c r="E23" s="2"/>
+      <c r="F23" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="G23" s="2"/>
+      <c r="H23" s="2">
+        <v>4</v>
+      </c>
+      <c r="I23" s="2">
         <v>2</v>
       </c>
-      <c r="BB22" s="2">
-        <v>200</v>
-      </c>
-      <c r="BC22" s="2"/>
-      <c r="BD22" s="2" t="s">
+      <c r="J23" s="2">
+        <v>4</v>
+      </c>
+      <c r="K23" s="2">
+        <v>2</v>
+      </c>
+      <c r="L23" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="M23" s="2">
+        <v>2</v>
+      </c>
+      <c r="N23" s="2">
+        <v>200</v>
+      </c>
+      <c r="O23" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="P23" s="2"/>
+      <c r="Q23" s="2"/>
+      <c r="R23" s="2"/>
+      <c r="S23" s="2"/>
+      <c r="T23" s="2"/>
+      <c r="U23" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="V23" s="2">
+        <v>2</v>
+      </c>
+      <c r="W23" s="2">
+        <v>200</v>
+      </c>
+      <c r="X23" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="Y23" s="2"/>
+      <c r="Z23" s="2">
+        <v>4</v>
+      </c>
+      <c r="AA23" s="2">
+        <v>2</v>
+      </c>
+      <c r="AB23" s="2">
+        <v>4</v>
+      </c>
+      <c r="AC23" s="2">
+        <v>2</v>
+      </c>
+      <c r="AD23" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="AE23" s="2">
+        <v>2</v>
+      </c>
+      <c r="AF23" s="2">
+        <v>200</v>
+      </c>
+      <c r="AG23" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="AH23" s="2"/>
+      <c r="AI23" s="2"/>
+      <c r="AJ23" s="2"/>
+      <c r="AK23" s="2"/>
+      <c r="AL23" s="2"/>
+      <c r="AM23" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="AN23" s="2">
+        <v>2</v>
+      </c>
+      <c r="AO23" s="2">
+        <v>200</v>
+      </c>
+      <c r="AP23" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="AQ23" s="2"/>
+      <c r="AR23" s="2"/>
+      <c r="AS23" s="2"/>
+      <c r="AT23" s="2"/>
+      <c r="AU23" s="2"/>
+      <c r="AV23" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="AW23" s="2">
+        <v>2</v>
+      </c>
+      <c r="AX23" s="2">
+        <v>200</v>
+      </c>
+      <c r="AY23" s="2" t="s">
         <v>34</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
-    <mergeCell ref="G1:P1"/>
-    <mergeCell ref="Q1:Z1"/>
-    <mergeCell ref="AA1:AJ1"/>
-    <mergeCell ref="AK1:AT1"/>
-    <mergeCell ref="AU1:BD1"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:F2"/>
+  <mergeCells count="26">
+    <mergeCell ref="G1:O1"/>
+    <mergeCell ref="P1:X1"/>
+    <mergeCell ref="Y1:AG1"/>
+    <mergeCell ref="AH1:AP1"/>
+    <mergeCell ref="AQ1:AY1"/>
+    <mergeCell ref="A1:A3"/>
+    <mergeCell ref="B1:B3"/>
+    <mergeCell ref="C1:C3"/>
+    <mergeCell ref="D1:D3"/>
+    <mergeCell ref="E1:E3"/>
+    <mergeCell ref="F1:F3"/>
+    <mergeCell ref="G2:K2"/>
+    <mergeCell ref="L2:N2"/>
+    <mergeCell ref="P2:T2"/>
+    <mergeCell ref="U2:W2"/>
+    <mergeCell ref="Y2:AC2"/>
+    <mergeCell ref="AD2:AF2"/>
+    <mergeCell ref="AH2:AL2"/>
+    <mergeCell ref="AM2:AO2"/>
+    <mergeCell ref="AQ2:AU2"/>
+    <mergeCell ref="AV2:AX2"/>
+    <mergeCell ref="O2:O3"/>
+    <mergeCell ref="X2:X3"/>
+    <mergeCell ref="AG2:AG3"/>
+    <mergeCell ref="AP2:AP3"/>
+    <mergeCell ref="AY2:AY3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -4261,7 +4162,7 @@
         <v>84</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="M1" s="1" t="s">
         <v>17</v>
@@ -5003,7 +4904,7 @@
         <v>83</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="K1" s="1" t="s">
         <v>17</v>
